--- a/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
+++ b/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated:      2026-10-01 10:39:28</t>
+          <t>Generated:      2026-10-08 11:01:50</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Instrument_Match_Method         Resolution path: exact / suffix-strip / normalized / normalized-item-strip / UNMATCHED</t>
+          <t>Instrument_Match_Method         Resolution path: class-category-term / exact / suffix-strip / normalized / normalized-item-strip / UNMATCHED</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Instrument NCIt populated:       260 (71.6%)</t>
+          <t>Instrument NCIt populated:       363 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Both populated:                  256 (70.5%)</t>
+          <t>Both populated:                  359 (98.9%)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Instrument UMLS CUI populated:   113 (31.1%)</t>
+          <t>Instrument UMLS CUI populated:   155 (42.7%)</t>
         </is>
       </c>
     </row>
@@ -815,186 +815,224 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  exact:                  206</t>
+          <t xml:space="preserve">  class-category-term:    362</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  suffix-strip:            44</t>
+          <t xml:space="preserve">  exact:                    1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized:              10</t>
+          <t xml:space="preserve">  suffix-strip:             0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized-item-strip:    0</t>
+          <t xml:space="preserve">  normalized:               0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  UNMATCHED:              103</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+          <t xml:space="preserve">  normalized-item-strip:    0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UNMATCHED:                0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>DESIGN DECISIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
+          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
+          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
           <t>column separation names the gap rather than hiding it.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="n"/>
-    </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
-        </is>
-      </c>
+      <c r="A60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
+          <t>Class category term first. SDTM CT QSCAT / FTCAT / CCCAT carry one term per instrument;</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>normalized match get UNMATCHED with empty Instrument_NCIt_* columns.</t>
+          <t>its CDISC synonym + "TC" is the codelist submission value and its code the instrument</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>concept. Name matching is the fallback.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
-        </is>
-      </c>
+      <c r="A64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>SDTM_Instrument_Test_Identity.xlsx, joinable via Codelist_TESTCD.</t>
+          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>COLOR CONVENTION</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>normalized match get UNMATCHED with empty Instrument_NCIt_* columns.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
-        </is>
-      </c>
+      <c r="A68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
+          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
+          <t>SDTM_Instrument_Test_Identity.xlsx, joinable via Codelist_TESTCD.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Yellow (#FFD700)          — COSMoS Dataset Specialization layer (consumer files)</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>COLOR CONVENTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>KNOWN LIMITATIONS</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>1. Instrument identity (C20993) is name-based — fragile for versioned variants,</t>
+          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   respondent forms, and disease-specific modules. See Instrument_Match_Method.</t>
+          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
+          <t>Yellow (#FFD700)          — COSMoS Dataset Specialization layer (consumer files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN LIMITATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>1. Where no class category term exists, instrument identity (C20993) is name-based —</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   fragile for versioned variants, respondent forms, and disease-specific modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   See Instrument_Match_Method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
           <t>2. C211913 containers spanning multiple codelists (1:many) are excluded.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>3. Codelists with Domain == ?? are TAUG-origin (outside SDTMIG v3.4 scope).</t>
         </is>
@@ -1181,7 +1219,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
@@ -1233,15 +1271,35 @@
           <t>112</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr"/>
-      <c r="G3" s="11" t="inlineStr"/>
-      <c r="H3" s="11" t="inlineStr"/>
-      <c r="I3" s="11" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>C214447</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Assessment Scale-Cognitive Date 30th June 2015 Version Functional Test</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>ADAS-COG 30JUN2015 | ADAS-COG Date 30th June 2015 Version | ADC1</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>The June 30, 2015 version of a standardized 11-task assessment tool, originally published by Mohs et al. in 1983, that assesses cognitive functions that are typically impaired in Alzheimer's disease in the domains of memory, language, and praxis.</t>
+        </is>
+      </c>
       <c r="J3" s="11" t="inlineStr"/>
-      <c r="K3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>CL1944039</t>
+        </is>
+      </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
@@ -1293,15 +1351,35 @@
           <t>111</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>C100762</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>ADAS-COG | ADC</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>The CDISC version of the Alzheimer's Disease Assessment Scale-Cognitive (CDISC ADAS-Cog) containing 15 summary-level tests. This version is based on combining the total pool of ADAS-Cog tests that were observed during a review of multiple case report forms administered in clinical trials of Alzheimer's disease, as well as the CRF administered in the Alzheimer's Disease Neuroimaging Initiative (ADNI) observational study.  (Modified from Mohs RC, Rosen WG, Davis KL. The Alzheimer's disease assessment scale: an instrument for assessing treatment efficacy. Psychopharmacol Bull 1983;19(3):448-450. Rosen WG, Mohs RC, Davis KL. A new rating scale for Alzheimer's disease. Am J Psychiatry 1984;141(11):1356-1364. Mohs RC, Knopman D, Petersen RC et al. Development of cognitive instruments for use in clinical trials of antidementia drugs: additions to the Alzheimer's Disease Assessment Scale that broaden its scope. The Alzheimer's Disease Cooperative Study. Alzheimer Dis Assoc Disord 1997;11 Suppl 2:S13-S21. Wouters H, van Gool WA, Schmand B, Lindeboom R. Revising the ADAS-cog for a more accurate assessment of cognitive impairment. Alzheimer Dis Assoc Disord 2008;22(3):236-244.).</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>C3539026</t>
+        </is>
+      </c>
       <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -1353,15 +1431,35 @@
           <t>138</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>C102112</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Neuroimaging Initiative Auditory Verbal Learning Test Functional Test</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>ADNI-AVLT | AVL01 | AVLT</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>The Alzheimer's Disease Neuroimaging Initiative's (ADNI) version of the Auditory Verbal Learning Test (AVLT Version A). This version is modified from A. Rey in 1964 and is used to evaluate verbal learning and memory abilities in both children and adults. The test format consists of a list of 15 words that the patient recalls during 5 separate trials. A second list with 15 new words is read and the patient must recall the words in one trial. Immediately following this task, the patient must recall the words from the first list; then recall them again 30 minutes later. The total number of words and intrusions is tallied for each trial.</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>C3640516</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -1413,15 +1511,35 @@
           <t>36</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>C123668</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Rey Auditory Verbal Learning Functional Test</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>AVL02 | AVLT-REY | AVLT-REY</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale modified from A. Rey in 1964 and Ceffen et al in 1994, which is used to evaluate verbal learning and memory abilities in both children and adults. The questionnaire contains 36 items and assesses overall memory performance, immediate span of memory for words, acquisition rate, interference effects, and recognition.</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>C4054062</t>
+        </is>
+      </c>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
@@ -1501,7 +1619,7 @@
       <c r="K7" s="11" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1581,7 +1699,7 @@
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
@@ -1661,7 +1779,7 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1741,7 +1859,7 @@
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -1821,7 +1939,7 @@
       <c r="K11" s="11" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1901,7 +2019,7 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1953,15 +2071,35 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr"/>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>C74982</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Mini-Mental Status Exam</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Folstein Mini-Mental Status Exam | MMS1 | MMSE | MMSE | Mini-Mental State Examination Questionnaire</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>A standardized and structured interview originally developed by Marshal Folstein, Susan Folstein and Paul McHugh (Journal of Psychiatric Research, 1975), which is used to evaluate an individual's cognitive function.</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>C0451306</t>
+        </is>
+      </c>
       <c r="K13" s="11" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -2041,7 +2179,7 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -2093,15 +2231,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>C115791</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Nine-Hole Peg Functional Test</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>NHPT | NHPT | NHPT01</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Mathiowetz et al in 1985 to measure unilateral finger dexterity to determine the extent of fine motor impairment in people experiencing difficulties with functional performance. This functional test requires the use of both dominant and non-dominant hands, and assesses fine motor and hand/eye coordination, as well as ability to follow simple directions. Scoring of this test is based on the average of 4 trials.</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>C3891812</t>
+        </is>
+      </c>
       <c r="K15" s="11" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -2153,15 +2311,35 @@
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-      <c r="J16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>C115792</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Paced Auditory Serial Addition Functional Test</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>PASAT | PASAT | PASAT1</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by DMA Gronwall et al in 1977 to assess auditory information processing speed and flexibility, as well as calculation ability. It is also used as a cognitive function test to evaluate sustained and divided attention. The test involves the presentation of single digits every 3 seconds and a study subject must add each new digit to the one immediately prior to it. Scoring of this test is based on the total number correct out of 60 possible answers.</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>C3898036</t>
+        </is>
+      </c>
       <c r="K16" s="9" t="inlineStr"/>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -2241,7 +2419,7 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -2293,15 +2471,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>C138334</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Performance of the Upper Limb Module for DMD 1.2 Functional Test</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>PUL 1.2 | PUL V1.2 | PUL01</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>A 22-item assessment scale developed by an international clinical outcomes group in 2011 to measure motor performance of the upper limb in patients with Duchenne muscular dystrophy (DMD). Functional tasks are subdivided into three dimensions that reflect disease progression from proximal to distal weakness, and from ambulatory to non-ambulatory.</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>CL525828</t>
+        </is>
+      </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2353,15 +2551,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr"/>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>C138335</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Performance of the Upper Limb Module for DMD 2.0 Functional Test</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>PUL 2.0 | PUL V2.0 | PUL02</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>A revised version of the Performance of the Upper Limb Module for DMD 1.2 Functional Test, which was developed by an international clinical outcomes group in 2011 to measure motor performance of the upper limb in patients with Duchenne muscular dystrophy (DMD). Functional tasks are subdivided into three dimensions that reflect disease progression from proximal to distal weakness, and from ambulatory to non-ambulatory.</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>CL525827</t>
+        </is>
+      </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -2441,7 +2659,7 @@
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -2521,7 +2739,7 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -2573,15 +2791,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr"/>
-      <c r="J22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>C115793</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Symbol Digit Modalities Functional Test</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>SDMT | SDMT | SDMT01</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Aaron Smith in 1982, which is used to identify individuals with neurological impairment, as well as to assess divided attention, visual scanning and motor speed. This functional test measures the time to pair abstract symbols with specific numbers with a 90 second time limit. Scoring of this test is based on the total number of correctly coded items from 0-110 in 90 seconds.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>C3891405</t>
+        </is>
+      </c>
       <c r="K22" s="9" t="inlineStr"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
@@ -2661,7 +2899,7 @@
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -2741,7 +2979,7 @@
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
@@ -2793,15 +3031,35 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="11" t="inlineStr"/>
-      <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>C115794</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Timed 25-Foot Walk Functional Test</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>T25FW | T25FW | T25FW1</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed to measure walking ability through gait speed. This functional test is a quantitative mobility and leg function performance test where a study subject is asked to walk 25 feet from a marked starting point. The time is calculated from the initiation to the end of walking when the patient has reached the 25-foot mark. Scoring of this test is based on the average of two completed trials.</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>C3897356</t>
+        </is>
+      </c>
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -2881,7 +3139,7 @@
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
@@ -2933,15 +3191,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="11" t="inlineStr"/>
-      <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>C92205</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Trail Making Test</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>TMT | TMT | TMT01</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>A neuropsychological test of visual attention and task switching that requires a subject to connect a sequence of 25 consecutive targets. It provides an easy to administer and reliable assessment of attention, sequencing, cognition, visual search, and motor function.</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>C0040604</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr"/>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2993,15 +3271,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
-      <c r="J28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>C115795</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Timed Up and Go Functional Test</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>TUG | TUG | TUG01</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Mathias et al in 1986 which is used to test basic mobility skills in frail elderly persons and other populations such as people with arthritis, stroke, and vertigo. This functional test measures the time in seconds for a person to stand up from a standard armchair, walk 3 meters, turn, walk back to the chair, and sit down again. Scoring of this test is based on the average of multiple completed and timed trials.</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>C1319201</t>
+        </is>
+      </c>
       <c r="K28" s="9" t="inlineStr"/>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
@@ -3053,15 +3351,35 @@
           <t>79</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr"/>
-      <c r="G29" s="11" t="inlineStr"/>
-      <c r="H29" s="11" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr"/>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>C105166</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Cooperative Study Activities of Daily Living Inventory Questionnaire</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>ADCS-ADL | ADCS-ADL | ADL01</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>A standardized questionnaire developed by Galasko et al in 1997 as part of the Alzheimer's disease cooperative study, which is used to measure the performance of activities of daily living by patients diagnosed with Alzheimer's disease. The questionnaire contains 23 items (and a number of sub-items within the 23 main items) with a range of preset answers that are assigned points based on performance.</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>C3641947</t>
+        </is>
+      </c>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3113,15 +3431,35 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>C106889</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Cooperative Study-Activities of Daily Living Inventory Severe Dementia Questionnaire</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>ADCS-ADL SEVERE DEMENTIA | ADCS-ADL Severe Dementia | ADL02</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>A standardized questionnaire developed by Galasko et al in 1997 as part of the Alzheimer's disease cooperative study, which is used to measure the performance of activities of daily living by patients diagnosed with advanced stage or severe Alzheimer's disease. The questionnaire contains 19 items (and a number of sub-items within the 19 main items) with a range of preset answers that are assigned points based on performance.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>C3827034</t>
+        </is>
+      </c>
       <c r="K30" s="9" t="inlineStr"/>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
@@ -3173,15 +3511,35 @@
           <t>92</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="11" t="inlineStr"/>
-      <c r="H31" s="11" t="inlineStr"/>
-      <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>C106888</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease Cooperative Study-Activities of Daily Living Inventory Mild Cognitive Impairment Questionnaire</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>ADCS-ADL MCI | ADCS-ADL MCI | ADL03</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>A standardized questionnaire developed by Galasko et al in 1997 as part of the Alzheimer's disease cooperative study, which is used to measure the performance of activities of daily living by patients diagnosed with Alzheimer's disease, exhibiting evidence of mild cognitive impairment (MCI). The questionnaire contains 24 items (and a number of sub-items within the 24 main items) with a range of preset answers that are assigned points based on performance.</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>C3827035</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -3261,7 +3619,7 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -3313,15 +3671,35 @@
           <t>11</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="11" t="inlineStr"/>
-      <c r="H33" s="11" t="inlineStr"/>
-      <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>C119097</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Alcohol Use Disorder Identification Test Self-Report Version Questionnaire</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>ADT01 | AUDIT | AUDIT-SR</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by the World Health Organization (WHO) to screen for excessive, hazardous or harmful alcohol consumption. The questionnaire contains 10 questions and evaluates the frequency and amount of alcohol use, alcohol-dependence symptoms and alcohol-related problems.</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>C0450985</t>
+        </is>
+      </c>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -3373,15 +3751,35 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-      <c r="I34" s="9" t="inlineStr"/>
-      <c r="J34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>C119098</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Alcohol Use Disorder Identification Test Alcohol Consumption Questions Questionnaire</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>ADTC01 | AUDIT-C | AUDIT-C</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by the World Health Organization (WHO), which is a modified version of the original Alcohol Use Disorder Identification Test (ADUIT). The questionnaire contains 3 questions, and is used to identify patients who are hazardous drinkers or have active alcohol use disorders.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>C3871151</t>
+        </is>
+      </c>
       <c r="K34" s="9" t="inlineStr"/>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
@@ -3457,7 +3855,7 @@
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
@@ -3529,7 +3927,7 @@
       <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
@@ -3605,7 +4003,7 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
@@ -3685,7 +4083,7 @@
       <c r="K38" s="9" t="inlineStr"/>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
@@ -3761,7 +4159,7 @@
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -3837,7 +4235,7 @@
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -3917,7 +4315,7 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -3969,15 +4367,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr"/>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-      <c r="I42" s="9" t="inlineStr"/>
-      <c r="J42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>C113872</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Borg Category-Ratio 10 Scale Questionnaire</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>BCR101 | BORG CR10 | Borg CR10</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Gunnar Borg in 1998, which is used primarily in clinical diagnosis to measure perceived exertion or intensities of most kinds of experiences and feelings, such as breathlessness. The questionnaire contains 1 item which is scored ranging from 0 (nothing at all) to infinity.</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>C3827029</t>
+        </is>
+      </c>
       <c r="K42" s="9" t="inlineStr"/>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
@@ -4057,7 +4475,7 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4137,7 +4555,7 @@
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
@@ -4217,7 +4635,7 @@
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4297,7 +4715,7 @@
       <c r="K46" s="9" t="inlineStr"/>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -4377,7 +4795,7 @@
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4457,7 +4875,7 @@
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
@@ -4537,7 +4955,7 @@
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -4617,7 +5035,7 @@
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -4697,7 +5115,7 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -4777,7 +5195,7 @@
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
@@ -4829,15 +5247,35 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr"/>
-      <c r="G53" s="11" t="inlineStr"/>
-      <c r="H53" s="11" t="inlineStr"/>
-      <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr"/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>C117995</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Craig Handicap Assessment and Reporting Technique-Short Form Interview Version Questionnaire</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>CHART-SF | CHART-SF INTERVIEW VERSION | CHSF1</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale originally developed by Whiteneck et al in 1992 and modified in 2000, which is used to measure the degree to which impairments and disabilities result in handicaps in the years after initial rehabilitation. The questionnaire contains 19 questions and generates 6 subscales: physical independence, cognitive independence, mobility, occupation, social integration and economic self-sufficiency.</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>C3896682</t>
+        </is>
+      </c>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -4917,7 +5355,7 @@
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
@@ -4997,7 +5435,7 @@
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -5077,7 +5515,7 @@
       <c r="K56" s="9" t="inlineStr"/>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M56" s="10" t="inlineStr">
@@ -5157,7 +5595,7 @@
       <c r="K57" s="11" t="inlineStr"/>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -5237,7 +5675,7 @@
       <c r="K58" s="9" t="inlineStr"/>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
@@ -5317,7 +5755,7 @@
       <c r="K59" s="11" t="inlineStr"/>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
@@ -5397,7 +5835,7 @@
       <c r="K60" s="9" t="inlineStr"/>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
@@ -5449,15 +5887,35 @@
           <t>51</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr"/>
-      <c r="G61" s="11" t="inlineStr"/>
-      <c r="H61" s="11" t="inlineStr"/>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr"/>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>C105164</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Columbia-Suicide Severity Rating Scale Baseline/Screening Version Phase 1 Study 1/14/09 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>C-SSRS BASELINE/SCREENING VERSION PHASE 1 STUDY | C-SSRS Baseline/Screening Version Phase 1 Study 1/14/09 | CSS03</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Posner et al (version 1/14/09), which is used to determine the presence of suicidal ideation or behavior. The baseline/screening version phase 1 study questionnaire contains 23 items across 4 domains; suicidal ideation, intensity of ideation, suicidal behavior and actual attempts.</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>C3641945</t>
+        </is>
+      </c>
       <c r="K61" s="11" t="inlineStr"/>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -5537,7 +5995,7 @@
       <c r="K62" s="9" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
@@ -5617,7 +6075,7 @@
       <c r="K63" s="11" t="inlineStr"/>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
@@ -5697,7 +6155,7 @@
       <c r="K64" s="9" t="inlineStr"/>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M64" s="10" t="inlineStr">
@@ -5777,7 +6235,7 @@
       <c r="K65" s="11" t="inlineStr"/>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
@@ -5857,7 +6315,7 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M66" s="10" t="inlineStr">
@@ -5937,7 +6395,7 @@
       <c r="K67" s="11" t="inlineStr"/>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
@@ -6017,7 +6475,7 @@
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M68" s="10" t="inlineStr">
@@ -6097,7 +6555,7 @@
       <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
@@ -6177,7 +6635,7 @@
       <c r="K70" s="9" t="inlineStr"/>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr">
@@ -6257,7 +6715,7 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
@@ -6337,7 +6795,7 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr">
@@ -6417,7 +6875,7 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
@@ -6469,15 +6927,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr"/>
-      <c r="G74" s="9" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr"/>
-      <c r="I74" s="9" t="inlineStr"/>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>C183575</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Diary for Irritable Bowel Syndrome Symptoms-Constipation Version 1.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>DIBC01 | DIBSS-C V1.0 | DIBSS-C Version 1.0</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>The first version of a standardized questionnaire developed by Fehnel et al. 2017 that assesses severity of the core bowel movement and abdominal signs and symptoms associated with Irritable Bowel Syndrome-Constipation.</t>
+        </is>
+      </c>
       <c r="J74" s="9" t="inlineStr"/>
-      <c r="K74" s="9" t="inlineStr"/>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>CL1771820</t>
+        </is>
+      </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
@@ -6557,7 +7035,7 @@
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
@@ -6637,7 +7115,7 @@
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
@@ -6713,7 +7191,7 @@
       <c r="K77" s="11" t="inlineStr"/>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -6789,7 +7267,7 @@
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
@@ -6869,7 +7347,7 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
@@ -6923,33 +7401,33 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>C176836</t>
+          <t>C161654</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>EORTC Quality of Life Questionnaire-Core 30</t>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Core 30 Version 3.0</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>EORTC-QLQ-C30 | European Organisation for the Research and Treatment of Cancer Quality of Life Questionnaire - Core 30 | QLQ-C30 | Quality of Life Questionnaire-Core 30</t>
+          <t>EOR01 | EORTC QLQ-C30 V3.0 | EORTC QLQ-C30 Version 3</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>An integrated system for assessing the quality of life of cancer patients participating in clinical trials and other types of research. It incorporates five functional scales: Physical, Role, Cognitive, Emotional, and Social Functioning; three symptom scales: Fatigue, Pain, and Nausea/Vomiting; a Global Health Status/QoL scale; and six single item scales: Dyspnea, Insomnia, Appetite Loss, Constipation, Diarrhea, and Financial Difficulties.</t>
+          <t>A standardized 30-item self-administered quality of life questionnaire, developed by the European Organization for the Research and Treatment of Cancer Quality of Life Group in 1995 as an update to the European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Core 36 (EORTC QLQ-C36), which was originally developed in 1987 and then modified to become EORTC QLQ-C30 in 1993. EORTC QLQ-C30 V3.0 utilizes a four-point response scale to assess functional, symptom, and global health status/quality of life scales, as well as five additional single symptoms and perceived financial impact, and a seven-point response scale to assess overall health and quality of life.</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>CL1642595</t>
+          <t>CL970287</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
@@ -7001,15 +7479,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F81" s="11" t="inlineStr"/>
-      <c r="G81" s="11" t="inlineStr"/>
-      <c r="H81" s="11" t="inlineStr"/>
-      <c r="I81" s="11" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>C161653</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Palliative Care Version 1.0</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>EOR02 | EORTC QLQ-C15-PAL V1.0 | EORTC QLQ-C15-PAL Version 1</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 15-item questionnaire, developed in 2006 by the European Organization for Research and Treatment of Cancer as an abbreviated version of the cancer-specific quality of life questionnaire European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Core 30 (EORTC QLQ-C30), that utilizes a four-point response scale to assess the symptoms and problems for which patients are frequently treated in palliative care, and a seven-point response scale to assess overall quality of life.</t>
+        </is>
+      </c>
       <c r="J81" s="11" t="inlineStr"/>
-      <c r="K81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>CL970288</t>
+        </is>
+      </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
@@ -7089,7 +7587,7 @@
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
@@ -7141,15 +7639,35 @@
           <t>35</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr"/>
-      <c r="G83" s="11" t="inlineStr"/>
-      <c r="H83" s="11" t="inlineStr"/>
-      <c r="I83" s="11" t="inlineStr"/>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>C170644</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Colorectal Cancer Version 2.1 29 Items</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>EOR06 | EORTC QLQ-CR29 V2.1 | EORTC QLQ-CR29 Version 2.1</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>An updated modular supplement to the European Organization for the Research and Treatment of Cancer Core Quality of Life Questionnaire (EORTC QLQ-C30) that was developed in 2007 and is used to assess quality of life in patients with colorectal cancer. The patient-report questionnaire utilizes a four point rating scale to assess symptoms or problems experienced over the last week.</t>
+        </is>
+      </c>
       <c r="J83" s="11" t="inlineStr"/>
-      <c r="K83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>CL1382830</t>
+        </is>
+      </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
@@ -7201,15 +7719,35 @@
           <t>35</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr"/>
-      <c r="G84" s="9" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
-      <c r="I84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>C220251</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Head &amp; Neck Cancer Version 1 35 Items</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>EOR11 | EORTC QLQ-H and N35 Version 1 | EORTC QLQ-H&amp;N35 V1</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Version 1.0 of a standardized 35-item questionnaire module, published by the European Organisation for Research and Treatment of Cancer (EORTC) in 1994, that is designed to supplement the EORTC QLQ-C30 core questionnaire in assessing health-related quality of life in head and neck cancer patients.</t>
+        </is>
+      </c>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr"/>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>CL1953463</t>
+        </is>
+      </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
@@ -7285,7 +7823,7 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
@@ -7365,7 +7903,7 @@
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
@@ -7417,15 +7955,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr"/>
-      <c r="G87" s="11" t="inlineStr"/>
-      <c r="H87" s="11" t="inlineStr"/>
-      <c r="I87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>C168555</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Lung Cancer 13 Items</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>EOR18 | EORTC QLQ Lung Cancer Module | EORTC QLQ-LC13 | EORTC QLQ-LC13 | EORTC Study Group on Quality of Life 13-item Lung Cancer-Specific Questionnaire | European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Lung Cancer Module</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>A modular supplement to the EORTC Core Quality of Life Questionnaire (QLQ-C30) for use in lung cancer clinical trials.</t>
+        </is>
+      </c>
       <c r="J87" s="11" t="inlineStr"/>
-      <c r="K87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>CL972883</t>
+        </is>
+      </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
@@ -7477,15 +8035,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr"/>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>C122694</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>Quality of Life Questionnaire-Multiple Myeloma 20</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>EOR19 | EORTC Multiple Myeloma Module | EORTC Multiple Myeloma Module (QLQ-MY20) | EORTC QLQ-MY20 | EORTC QLQ-MY20 | QLQ-MY20</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>A questionnaire developed by the European Organisation for Research and Treatment of Cancer (EORTC) consisting of 20 questions designed to assess quality of life in multiple myeloma patients.</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>C4054140</t>
+        </is>
+      </c>
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
@@ -7537,15 +8115,35 @@
           <t>18</t>
         </is>
       </c>
-      <c r="F89" s="11" t="inlineStr"/>
-      <c r="G89" s="11" t="inlineStr"/>
-      <c r="H89" s="11" t="inlineStr"/>
-      <c r="I89" s="11" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>C183588</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Esophageal Cancer 18 Items</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>EOR20 | EORTC QLQ-OES18 | EORTC QLQ-OES18</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 18-item questionnaire module developed by the European Organisation for Research and Treatment of Cancer (EORTC) in 2003 that is designed to supplement the EORTC QLQ-C30 core questionnaire in assessing quality of life in patients with esophageal cancer. This module was updated from the EORTC QLQ-OE24 that was developed in 1996.</t>
+        </is>
+      </c>
       <c r="J89" s="11" t="inlineStr"/>
-      <c r="K89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>CL1771825</t>
+        </is>
+      </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
@@ -7625,7 +8223,7 @@
       </c>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
@@ -7705,7 +8303,7 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
@@ -7757,15 +8355,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr"/>
-      <c r="G92" s="9" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
-      <c r="I92" s="9" t="inlineStr"/>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>C125719</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>Quality of Life Questionnaire - Chemotherapy-Induced Peripheral Neuropathy 20 Items</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>CIPN20 Questionnaire | EOR25 | EORTC QLQ-CIPN20 | EORTC QLQ-CIPN20</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>A questionnaire developed by the European Organisation for Research and Treatment of Cancer (EORTC) consisting of 20 questions designed to assess quality of life related to symptoms and functional limitations in patients with Chemotherapy-Induced Peripheral Neuropathy (CIPN).</t>
+        </is>
+      </c>
       <c r="J92" s="9" t="inlineStr"/>
-      <c r="K92" s="9" t="inlineStr"/>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>CL504375</t>
+        </is>
+      </c>
       <c r="L92" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
@@ -7841,7 +8459,7 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
@@ -7893,15 +8511,35 @@
           <t>17</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
-      <c r="I94" s="9" t="inlineStr"/>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>C183595</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Chronic Lymphocytic Leukemia 17 Items</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>EOR29 | EORTC QLQ-CLL17 | EORTC QLQ-CLL17</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 17-item questionnaire module developed by the European Organisation for Research and Treatment of Cancer (EORTC) in 2017 that is designed to supplement the EORTC QLQ-C30 core questionnaire in assessing the quality of life in patients with chronic lymphocytic leukemia.</t>
+        </is>
+      </c>
       <c r="J94" s="9" t="inlineStr"/>
-      <c r="K94" s="9" t="inlineStr"/>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>CL1771832</t>
+        </is>
+      </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
@@ -7953,15 +8591,35 @@
           <t>27</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr"/>
-      <c r="G95" s="11" t="inlineStr"/>
-      <c r="H95" s="11" t="inlineStr"/>
-      <c r="I95" s="11" t="inlineStr"/>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>C183596</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Anal Cancer 27 Items</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>EOR30 | EORTC QLQ-ANL27 | EORTC QLQ-ANL27</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 27-item questionnaire module developed in 2018 to supplement the European Organisation for Research and Treatment of Cancer (EORTC) QLQ-C30 core questionnaire in assessing the quality of life in patients with anal cancer. It consists of four health-related quality of life domains: pain, bowel, and sexual and stoma care problems, and five single items: frequent urination, keeping clean, proximity to toilet, lower limb oedema, and planning activities.</t>
+        </is>
+      </c>
       <c r="J95" s="11" t="inlineStr"/>
-      <c r="K95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>CL1771833</t>
+        </is>
+      </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
@@ -8041,7 +8699,7 @@
       </c>
       <c r="L96" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
@@ -8121,7 +8779,7 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
@@ -8201,7 +8859,7 @@
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
@@ -8281,7 +8939,7 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
@@ -8333,15 +8991,35 @@
           <t>22</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr"/>
-      <c r="G100" s="9" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
-      <c r="I100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>C127368</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Expanded Prostate Cancer Index Composite for Clinical Practice Questionnaire</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>EPIC-CP | EPIC-CP | EPIC2</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Chang et al in 2011, which is used to measure urinary incontinence, urinary irritation, and the bowel, sexual and hormonal health related quality of life in patients with prostate cancer. This instrument contains 16 items.</t>
+        </is>
+      </c>
       <c r="J100" s="9" t="inlineStr"/>
-      <c r="K100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>CL508757</t>
+        </is>
+      </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
@@ -8421,7 +9099,7 @@
       <c r="K101" s="11" t="inlineStr"/>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
@@ -8501,7 +9179,7 @@
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
@@ -8581,7 +9259,7 @@
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
@@ -8661,7 +9339,7 @@
       <c r="K104" s="9" t="inlineStr"/>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
@@ -8713,15 +9391,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="F105" s="11" t="inlineStr"/>
-      <c r="G105" s="11" t="inlineStr"/>
-      <c r="H105" s="11" t="inlineStr"/>
-      <c r="I105" s="11" t="inlineStr"/>
-      <c r="J105" s="11" t="inlineStr"/>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>C127369</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Functional Assessment of Cancer Therapy-General Version 4 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>FAC001 | FACT-G V4 | FACT-G Version 4</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale originally developed by Cella et al in 1993, which is used for general measurements of quality of life in patients with any form of cancer, or other chronic illness condition. The version 4 of this instrument contains 27 items which are divided into four domains: physical well-being, social/family well-being, emotional well-being, and functional well-being.</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>C3533310</t>
+        </is>
+      </c>
       <c r="K105" s="11" t="inlineStr"/>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
@@ -8801,7 +9499,7 @@
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
@@ -8881,7 +9579,7 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
@@ -8961,7 +9659,7 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
@@ -9041,7 +9739,7 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
@@ -9121,7 +9819,7 @@
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
@@ -9201,7 +9899,7 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
@@ -9281,7 +9979,7 @@
       </c>
       <c r="L112" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
@@ -9361,7 +10059,7 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr"/>
@@ -9399,33 +10097,33 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>C103832</t>
+          <t>C127371</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>FACT-P Questionnaire</t>
+          <t>Functional Assessment of Cancer Therapy-Prostate Version 4 Questionnaire</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>FACT-P | FACT-P | Functional Assessment of Cancer Therapy- Prostate | Functional Assessment of Cancer Therapy- Prostate (FACT-P version 4)</t>
+          <t>FAC023 | FACT-P V4 | FACT-P Version 4</t>
         </is>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>The FACT-P is a multidimensional, self-report quality of life instrument specifically designed for use with prostate cancer patients. It consists of 27 core items which assess patient function in four domains: Physical, Social/Family, Emotional, and Functional well-being, which is further supplemented by 12 site specific items to assess for prostate related symptoms (from GEM website https://www.gem-beta.org/public/MeasureDetail.aspx?mid=1074&amp;cat=2)</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>C3641634</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr"/>
+          <t>A standardized rating scale originally developed by Cella et al in 1993 and modified by Esper et al in 1997, which includes a 12-item prostate cancer subscale (PCS) in addition to the original 27 items from FACT-G. FACT-P contains 39 items and measures both general health-related quality of life as well as prostate cancer-specific quality of life; the total score is based on both FACT-G and PCS.</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr"/>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>CL509738</t>
+        </is>
+      </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
@@ -9505,7 +10203,7 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
@@ -9585,7 +10283,7 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
@@ -9665,7 +10363,7 @@
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
@@ -9741,7 +10439,7 @@
       <c r="K118" s="9" t="inlineStr"/>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
@@ -9817,7 +10515,7 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
@@ -9869,15 +10567,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
-      <c r="I120" s="9" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr"/>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>C118498</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>FKSI-15 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>FAC039 | FKSI-15 | FKSI-15 | Functional Assessment for Cancer Therapy-Kidney Symptom Index</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>A 15 item questionnaire developed to assess the symptom burden for patients with kidney cancer.</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>C3899166</t>
+        </is>
+      </c>
       <c r="K120" s="9" t="inlineStr"/>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
@@ -9957,7 +10675,7 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
@@ -10037,7 +10755,7 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
@@ -10117,7 +10835,7 @@
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
@@ -10197,7 +10915,7 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
@@ -10277,7 +10995,7 @@
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
@@ -10329,15 +11047,35 @@
           <t>17</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="9" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
-      <c r="I126" s="9" t="inlineStr"/>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>C127370</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>National Comprehensive Cancer Network/Functional Assessment of Cancer Therapy-Prostate Symptom Index 17 Version 2 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>FAC052 | NCCN-FACT FPSI-17 V2 | NCCN-FACT-FPSI 17 Version 2</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale modified from FACT-G and FACT-P and developed by Victorson et al in 2011, based on the recommendations of the National Comprehensive Cancer Network (NCCN). This instrument contains 17 items, and is used to examine the effectiveness of noncurative treatments in patients with advanced prostate cancer.</t>
+        </is>
+      </c>
       <c r="J126" s="9" t="inlineStr"/>
-      <c r="K126" s="9" t="inlineStr"/>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>CL509284</t>
+        </is>
+      </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
@@ -10417,7 +11155,7 @@
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
@@ -10497,7 +11235,7 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
@@ -10577,7 +11315,7 @@
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
@@ -10657,7 +11395,7 @@
       <c r="K130" s="9" t="inlineStr"/>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
@@ -10737,7 +11475,7 @@
       <c r="K131" s="11" t="inlineStr"/>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
@@ -10817,7 +11555,7 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
@@ -10897,7 +11635,7 @@
       <c r="K133" s="11" t="inlineStr"/>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
@@ -10977,7 +11715,7 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
@@ -11057,7 +11795,7 @@
       <c r="K135" s="11" t="inlineStr"/>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
@@ -11137,7 +11875,7 @@
       <c r="K136" s="9" t="inlineStr"/>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
@@ -11217,7 +11955,7 @@
       <c r="K137" s="11" t="inlineStr"/>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
@@ -11297,7 +12035,7 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
@@ -11377,7 +12115,7 @@
       </c>
       <c r="L139" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr">
@@ -11457,7 +12195,7 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
@@ -11581,15 +12319,35 @@
           <t>58</t>
         </is>
       </c>
-      <c r="F142" s="9" t="inlineStr"/>
-      <c r="G142" s="9" t="inlineStr"/>
-      <c r="H142" s="9" t="inlineStr"/>
-      <c r="I142" s="9" t="inlineStr"/>
-      <c r="J142" s="9" t="inlineStr"/>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>C112521</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Functional Assessment of Multiple Sclerosis Questionnaire</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>FAMS | FAMS | FAMS | FAMS Questionnaire | FAMS01</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>A standardized, disease-specific rating scale developed by Cella et al in 1996 to assess quality of life and functional status of individuals with multiple sclerosis. The questionnaire contains 58 items across 7 categories; mobility, symptoms, emotional well-being, general contentment, thinking and fatigue, family/social well-being, and additional concerns. The scoring algorithm for this questionnaire assigns a value from 0 (not at all) to 4 (very much) to each item in the response categories, and the total score ranges between 0 and 176.</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>C3827008</t>
+        </is>
+      </c>
       <c r="K142" s="9" t="inlineStr"/>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
@@ -11669,7 +12427,7 @@
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M143" s="11" t="inlineStr">
@@ -11749,7 +12507,7 @@
       <c r="K144" s="9" t="inlineStr"/>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
@@ -11801,15 +12559,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F145" s="11" t="inlineStr"/>
-      <c r="G145" s="11" t="inlineStr"/>
-      <c r="H145" s="11" t="inlineStr"/>
-      <c r="I145" s="11" t="inlineStr"/>
-      <c r="J145" s="11" t="inlineStr"/>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>C100766</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Faces Pain Scale Revised Questionnaire</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>FPSR | FPSR1</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed and copyrighted by the International Association for the Study of Pain (IASP) in 2001 but is available for non-commercial clinical, educational and research use in the journal Pain (Hicks CL, von Baeyer CL, Spafford P, van Korlaar I, Goodenough B. The Faces Pain Scale - Revised: Toward a common metric in pediatric pain measurement. Pain 2001;93:173-183). This instrument is used to evaluate the severity of pain in an individual who is unable to use a numerical scale alone such as a child. The scale consists of six facial expression representing varying levels of pain which correspond to a number between 0 and 10 where the 0 face represents 'no pain' and the 10 face represents 'very much pain'.</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>C3639711</t>
+        </is>
+      </c>
       <c r="K145" s="11" t="inlineStr"/>
       <c r="L145" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M145" s="11" t="inlineStr">
@@ -11889,7 +12667,7 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
@@ -11969,7 +12747,7 @@
       </c>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr">
@@ -12021,15 +12799,35 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F148" s="9" t="inlineStr"/>
-      <c r="G148" s="9" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
-      <c r="I148" s="9" t="inlineStr"/>
-      <c r="J148" s="9" t="inlineStr"/>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>C106621</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>Fatigue Severity Scale</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>FSS | FSS | FSS01</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>A numeric scale to assess the severity of an individual's fatigue over the past week while performing a variety of usual tasks.</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>C3813323</t>
+        </is>
+      </c>
       <c r="K148" s="9" t="inlineStr"/>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
@@ -12109,7 +12907,7 @@
       </c>
       <c r="L149" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M149" s="11" t="inlineStr">
@@ -12189,7 +12987,7 @@
       <c r="K150" s="9" t="inlineStr"/>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
@@ -12269,7 +13067,7 @@
       </c>
       <c r="L151" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M151" s="11" t="inlineStr">
@@ -12349,7 +13147,7 @@
       <c r="K152" s="9" t="inlineStr"/>
       <c r="L152" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M152" s="10" t="inlineStr">
@@ -12429,7 +13227,7 @@
       <c r="K153" s="11" t="inlineStr"/>
       <c r="L153" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M153" s="11" t="inlineStr">
@@ -12485,15 +13283,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F154" s="9" t="inlineStr"/>
-      <c r="G154" s="9" t="inlineStr"/>
-      <c r="H154" s="9" t="inlineStr"/>
-      <c r="I154" s="9" t="inlineStr"/>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>C163814</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>The Glucose Monitoring Satisfaction Survey Version: Type 1 Diabetes Questionnaire</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>GMSS VERSION TYPE 1 DIABETES | GMSS Version Type 1 Diabetes | GMSS01</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>A 15-item self-administered questionnaire, published by Polonsky et al. in 2015, that utilizes a five-point rating scale to assess patient treatment satisfaction with glucose monitoring devices for type 1 diabetes; the instrument includes four subscales that address openness, emotional burden, behavioral burden, and trust.</t>
+        </is>
+      </c>
       <c r="J154" s="9" t="inlineStr"/>
-      <c r="K154" s="9" t="inlineStr"/>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>CL977162</t>
+        </is>
+      </c>
       <c r="L154" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M154" s="10" t="inlineStr">
@@ -12573,7 +13391,7 @@
       <c r="K155" s="11" t="inlineStr"/>
       <c r="L155" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M155" s="11" t="inlineStr">
@@ -12625,15 +13443,31 @@
           <t>11</t>
         </is>
       </c>
-      <c r="F156" s="9" t="inlineStr"/>
-      <c r="G156" s="9" t="inlineStr"/>
-      <c r="H156" s="9" t="inlineStr"/>
-      <c r="I156" s="9" t="inlineStr"/>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>C228435</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>General Self-Efficacy Scale 1995</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SELF-EFFICACY SCALE 1995 | GSE 1995 | GSE01</t>
+        </is>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 10-item assessment tool, published in 1995 by Schwarzer et al. that utilizes a four-point rating scale to assess perceived self-efficacy to predict coping with daily hassles as well as adaptation after experiencing stressful life events.</t>
+        </is>
+      </c>
       <c r="J156" s="9" t="inlineStr"/>
       <c r="K156" s="9" t="inlineStr"/>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M156" s="10" t="inlineStr">
@@ -12709,7 +13543,7 @@
       <c r="K157" s="11" t="inlineStr"/>
       <c r="L157" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M157" s="11" t="inlineStr">
@@ -12761,15 +13595,35 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F158" s="9" t="inlineStr"/>
-      <c r="G158" s="9" t="inlineStr"/>
-      <c r="H158" s="9" t="inlineStr"/>
-      <c r="I158" s="9" t="inlineStr"/>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>C130314</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>Hamilton Depression Rating Scale 6 Self-Report Version Questionnaire</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>HAM-D6 Self-Report Version | HAMD 6 SELF-REPORT VERSION | HAMDS1</t>
+        </is>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 6-item self-report rating scale for the assessment of symptoms in patients diagnosed with depression. The original 17-item Hamilton Depression Scale, developed by Max Hamilton at the University of Leeds in 1960, was independently modified by Bech et al in 1975, using Rasch models, to create a melancholia subscale that contains six variables.</t>
+        </is>
+      </c>
       <c r="J158" s="9" t="inlineStr"/>
-      <c r="K158" s="9" t="inlineStr"/>
+      <c r="K158" s="9" t="inlineStr">
+        <is>
+          <t>CL513956</t>
+        </is>
+      </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
@@ -12849,7 +13703,7 @@
       <c r="K159" s="11" t="inlineStr"/>
       <c r="L159" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M159" s="11" t="inlineStr">
@@ -12929,7 +13783,7 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
@@ -13009,7 +13863,7 @@
       </c>
       <c r="L161" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M161" s="11" t="inlineStr">
@@ -13089,7 +13943,7 @@
       </c>
       <c r="L162" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
@@ -13169,7 +14023,7 @@
       </c>
       <c r="L163" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M163" s="11" t="inlineStr">
@@ -13249,7 +14103,7 @@
       <c r="K164" s="9" t="inlineStr"/>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
@@ -13329,7 +14183,7 @@
       </c>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M165" s="11" t="inlineStr">
@@ -13409,7 +14263,7 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
@@ -13461,15 +14315,35 @@
           <t>27</t>
         </is>
       </c>
-      <c r="F167" s="11" t="inlineStr"/>
-      <c r="G167" s="11" t="inlineStr"/>
-      <c r="H167" s="11" t="inlineStr"/>
-      <c r="I167" s="11" t="inlineStr"/>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>C141691</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>International Physical Activity Questionnaire (August 2002) Long Last 7 Days Self-Administered Format</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr">
+        <is>
+          <t>IPAQ Long Last 7 Days Self-Administered Format Version | IPAQ-LF SELF-ADMINISTERED VERSION | IPAQ03</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>A standardized self-administered 31-item questionnaire, developed by Booth et al. in 2000, that assesses physical activity lasting at least 10 minutes during the past seven days.</t>
+        </is>
+      </c>
       <c r="J167" s="11" t="inlineStr"/>
-      <c r="K167" s="11" t="inlineStr"/>
+      <c r="K167" s="11" t="inlineStr">
+        <is>
+          <t>CL539751</t>
+        </is>
+      </c>
       <c r="L167" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M167" s="11" t="inlineStr">
@@ -13549,7 +14423,7 @@
       </c>
       <c r="L168" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M168" s="10" t="inlineStr">
@@ -13629,7 +14503,7 @@
       <c r="K169" s="11" t="inlineStr"/>
       <c r="L169" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M169" s="11" t="inlineStr">
@@ -13709,7 +14583,7 @@
       <c r="K170" s="9" t="inlineStr"/>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M170" s="10" t="inlineStr">
@@ -13789,7 +14663,7 @@
       </c>
       <c r="L171" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M171" s="11" t="inlineStr">
@@ -13869,7 +14743,7 @@
       </c>
       <c r="L172" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M172" s="10" t="inlineStr">
@@ -13921,15 +14795,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="11" t="inlineStr"/>
-      <c r="H173" s="11" t="inlineStr"/>
-      <c r="I173" s="11" t="inlineStr"/>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>C138333</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>The Lansky Play-Performance Scale for Children Questionnaire</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr">
+        <is>
+          <t>LPPS SCALE | LPPSS1 | LPSS | PPSC | Play-Performance Status Scale</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>A parent-rated questionnaire created by Lansky et al. in 1985 to assess play activity over the past week in children ages 1 to 16 with cancer as an indicator of level of performance. Level of performance is scored from 0 to 100 based on active play, quiet play, degree of physical limitation, and degree of independence; with the interpretation ranging from fully active, normal performance (100), to moderately restricted (50 to 60), to completely disabled (10 or less).</t>
+        </is>
+      </c>
       <c r="J173" s="11" t="inlineStr"/>
-      <c r="K173" s="11" t="inlineStr"/>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>CL526970</t>
+        </is>
+      </c>
       <c r="L173" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M173" s="11" t="inlineStr">
@@ -14009,7 +14903,7 @@
       </c>
       <c r="L174" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M174" s="10" t="inlineStr"/>
@@ -14073,7 +14967,7 @@
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M175" s="11" t="inlineStr">
@@ -14153,7 +15047,7 @@
       <c r="K176" s="9" t="inlineStr"/>
       <c r="L176" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M176" s="10" t="inlineStr">
@@ -14233,7 +15127,7 @@
       <c r="K177" s="11" t="inlineStr"/>
       <c r="L177" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M177" s="11" t="inlineStr">
@@ -14313,7 +15207,7 @@
       <c r="K178" s="9" t="inlineStr"/>
       <c r="L178" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M178" s="10" t="inlineStr">
@@ -14393,7 +15287,7 @@
       <c r="K179" s="11" t="inlineStr"/>
       <c r="L179" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M179" s="11" t="inlineStr">
@@ -14473,7 +15367,7 @@
       <c r="K180" s="9" t="inlineStr"/>
       <c r="L180" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M180" s="10" t="inlineStr">
@@ -14553,7 +15447,7 @@
       </c>
       <c r="L181" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M181" s="11" t="inlineStr">
@@ -14605,15 +15499,35 @@
           <t>153</t>
         </is>
       </c>
-      <c r="F182" s="9" t="inlineStr"/>
-      <c r="G182" s="9" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr"/>
-      <c r="I182" s="9" t="inlineStr"/>
-      <c r="J182" s="9" t="inlineStr"/>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>C100772</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>Neuropsychiatric Inventory - 12 Item Version Questionnaire</t>
+        </is>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>NPI | NPI-12 | NPI-Q | NPI1 | Neuropsychiatric Inventory-Questionnaire</t>
+        </is>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale originally developed and copyrighted by Jeffrey L. Cummings in 1994 as well as published in the journal Neurology (Cummings J.L., The Neuropsychiatric Inventory: Assessing psychopathology in dementia patients. Neurology May 1997 48:10S-16S) which is used to assess the severity of an individual's neuropathic behaviors based on a observations made by the patient's caregiver. This instrument contains 12 neuropsychiatric areas associated with dementia such as delusions, anxiety, motor disturbances, and appetite. Each behavior is evaluated only if the individual displays the behavior. For these behaviors, the frequency is assessed on a scale of 0-4 with 0 being occasionally and 4 being very frequently, the severity is assessed on a scale of 1-3 with 1 being mild and 3 being marked, and the level of distress each behavior inflicts on the caregiver is assessed on a scale of 0-5 with 0 being not distressing and 5 being extremely distressing.</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr">
+        <is>
+          <t>C3539727</t>
+        </is>
+      </c>
       <c r="K182" s="9" t="inlineStr"/>
       <c r="L182" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M182" s="10" t="inlineStr">
@@ -14665,15 +15579,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F183" s="11" t="inlineStr"/>
-      <c r="G183" s="11" t="inlineStr"/>
-      <c r="H183" s="11" t="inlineStr"/>
-      <c r="I183" s="11" t="inlineStr"/>
-      <c r="J183" s="11" t="inlineStr"/>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>C103522</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>Neuropathic Pain Scale Questionnaire</t>
+        </is>
+      </c>
+      <c r="H183" s="11" t="inlineStr">
+        <is>
+          <t>NPS | NPS | NPS01</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="inlineStr">
+        <is>
+          <t>A standardized survey developed and copyrighted by Brad Galer and Mark Jensen in 1997 and published in the journal Neurology (BS Galer and MP Jensen. Development and preliminary validation of a pain measure specific to neuropathic pain: The Neuropathic Pain Scale. Neurology. 1997, 48:332-338.) which is used to assess specific pain qualities associated with neuropathic pain. This instrument consists of 10 items that can be completed by the patient. Each item is rated on a scale of 0-10 with 0 representing none and 10 representing the worst. However, one item is multi-level with open ended responses.</t>
+        </is>
+      </c>
+      <c r="J183" s="11" t="inlineStr">
+        <is>
+          <t>C3538803</t>
+        </is>
+      </c>
       <c r="K183" s="11" t="inlineStr"/>
       <c r="L183" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M183" s="11" t="inlineStr">
@@ -14753,7 +15687,7 @@
       </c>
       <c r="L184" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M184" s="10" t="inlineStr">
@@ -14833,7 +15767,7 @@
       </c>
       <c r="L185" s="11" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M185" s="11" t="inlineStr">
@@ -14913,7 +15847,7 @@
       <c r="K186" s="9" t="inlineStr"/>
       <c r="L186" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M186" s="10" t="inlineStr">
@@ -14993,7 +15927,7 @@
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M187" s="11" t="inlineStr">
@@ -15073,7 +16007,7 @@
       <c r="K188" s="9" t="inlineStr"/>
       <c r="L188" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M188" s="10" t="inlineStr">
@@ -15153,7 +16087,7 @@
       </c>
       <c r="L189" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M189" s="11" t="inlineStr">
@@ -15205,15 +16139,35 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F190" s="9" t="inlineStr"/>
-      <c r="G190" s="9" t="inlineStr"/>
-      <c r="H190" s="9" t="inlineStr"/>
-      <c r="I190" s="9" t="inlineStr"/>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>C202501</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>PROMIS Item Bank Version 2.0 Cognitive Function Short Form 6a Questionnaire</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>PA016 | PROMIS IB V2.0 COGNITIVE FUNCTION SF 6A | PROMIS IB Version 2.0 Cognitive Function SF 6a</t>
+        </is>
+      </c>
+      <c r="I190" s="9" t="inlineStr">
+        <is>
+          <t>The second version of a standardized six-item subset of the PROMIS Cognitive Function item bank, published in 2010, that utilizes a five-point rating scale to assess patient-perceived cognitive deficits.</t>
+        </is>
+      </c>
       <c r="J190" s="9" t="inlineStr"/>
-      <c r="K190" s="9" t="inlineStr"/>
+      <c r="K190" s="9" t="inlineStr">
+        <is>
+          <t>CL1921799</t>
+        </is>
+      </c>
       <c r="L190" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M190" s="10" t="inlineStr">
@@ -15265,15 +16219,35 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F191" s="11" t="inlineStr"/>
-      <c r="G191" s="11" t="inlineStr"/>
-      <c r="H191" s="11" t="inlineStr"/>
-      <c r="I191" s="11" t="inlineStr"/>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>C208540</t>
+        </is>
+      </c>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>PROMIS Item Bank v2.0 - Cognitive Function - Abilities Subset - Short Form 6a Questionnaire</t>
+        </is>
+      </c>
+      <c r="H191" s="11" t="inlineStr">
+        <is>
+          <t>PA020 | PROMIS IB V2.0 COGNITIVE FUNCTION ABILITIES SF 6A | PROMIS IB Version 2.0 Cognitive Function Abilities Subset SF 6a</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>The second version of a standardized six-item questionnaire that is derived from the subset of the PROMIS Cognitive Function item bank, published in 2010, that utilizes a five-point rating scale to assess how patient-perceived cognitive deficits impact daily functioning.</t>
+        </is>
+      </c>
       <c r="J191" s="11" t="inlineStr"/>
-      <c r="K191" s="11" t="inlineStr"/>
+      <c r="K191" s="11" t="inlineStr">
+        <is>
+          <t>CL1935269</t>
+        </is>
+      </c>
       <c r="L191" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M191" s="11" t="inlineStr">
@@ -15325,15 +16299,35 @@
           <t>7</t>
         </is>
       </c>
-      <c r="F192" s="9" t="inlineStr"/>
-      <c r="G192" s="9" t="inlineStr"/>
-      <c r="H192" s="9" t="inlineStr"/>
-      <c r="I192" s="9" t="inlineStr"/>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>C202502</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="inlineStr">
+        <is>
+          <t>PROMIS Item Bank Version 1.0 Fatigue Short Form 7a Questionnaire</t>
+        </is>
+      </c>
+      <c r="H192" s="9" t="inlineStr">
+        <is>
+          <t>PA136 | PROMIS IB V1.0 FATIGUE SF 7A | PROMIS IB Version 1.0 Fatigue SF 7a</t>
+        </is>
+      </c>
+      <c r="I192" s="9" t="inlineStr">
+        <is>
+          <t>The first version of a standardized seven-item subset of the PROMIS Item bank, published in 2010 by Cella et al., that utilizes a five-point rating scale to assess patient-reported symptoms of fatigue.</t>
+        </is>
+      </c>
       <c r="J192" s="9" t="inlineStr"/>
-      <c r="K192" s="9" t="inlineStr"/>
+      <c r="K192" s="9" t="inlineStr">
+        <is>
+          <t>CL1921800</t>
+        </is>
+      </c>
       <c r="L192" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M192" s="10" t="inlineStr">
@@ -15413,7 +16407,7 @@
       </c>
       <c r="L193" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M193" s="11" t="inlineStr">
@@ -15493,7 +16487,7 @@
       </c>
       <c r="L194" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M194" s="10" t="inlineStr">
@@ -15573,7 +16567,7 @@
       </c>
       <c r="L195" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M195" s="11" t="inlineStr">
@@ -15653,7 +16647,7 @@
       </c>
       <c r="L196" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M196" s="10" t="inlineStr">
@@ -15733,7 +16727,7 @@
       <c r="K197" s="11" t="inlineStr"/>
       <c r="L197" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M197" s="11" t="inlineStr">
@@ -15813,7 +16807,7 @@
       </c>
       <c r="L198" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M198" s="10" t="inlineStr">
@@ -15893,7 +16887,7 @@
       <c r="K199" s="11" t="inlineStr"/>
       <c r="L199" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M199" s="11" t="inlineStr">
@@ -15973,7 +16967,7 @@
       <c r="K200" s="9" t="inlineStr"/>
       <c r="L200" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M200" s="10" t="inlineStr">
@@ -16053,7 +17047,7 @@
       </c>
       <c r="L201" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M201" s="11" t="inlineStr">
@@ -16133,7 +17127,7 @@
       <c r="K202" s="9" t="inlineStr"/>
       <c r="L202" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M202" s="10" t="inlineStr">
@@ -16185,15 +17179,35 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F203" s="11" t="inlineStr"/>
-      <c r="G203" s="11" t="inlineStr"/>
-      <c r="H203" s="11" t="inlineStr"/>
-      <c r="I203" s="11" t="inlineStr"/>
+      <c r="F203" s="11" t="inlineStr">
+        <is>
+          <t>C191043</t>
+        </is>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>The Patient Health Questionnaire - 8 Item</t>
+        </is>
+      </c>
+      <c r="H203" s="11" t="inlineStr">
+        <is>
+          <t>PHQ-8 | PHQ-8 | PHQ05</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="inlineStr">
+        <is>
+          <t>A standardized self-report questionnaire, derived from the Patient Health Questionnaire-9 items and published in 2002, that includes nine items from the diagnostic criteria for MDD in the Diagnostic and Statistical Manual of Mental Disorders, Fourth Edition (DSM-IV) and is used to measure depression severity.</t>
+        </is>
+      </c>
       <c r="J203" s="11" t="inlineStr"/>
-      <c r="K203" s="11" t="inlineStr"/>
+      <c r="K203" s="11" t="inlineStr">
+        <is>
+          <t>CL1630893</t>
+        </is>
+      </c>
       <c r="L203" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M203" s="11" t="inlineStr">
@@ -16245,15 +17259,35 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F204" s="9" t="inlineStr"/>
-      <c r="G204" s="9" t="inlineStr"/>
-      <c r="H204" s="9" t="inlineStr"/>
-      <c r="I204" s="9" t="inlineStr"/>
-      <c r="J204" s="9" t="inlineStr"/>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>C105167</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="inlineStr">
+        <is>
+          <t>STANDARDS Pain Intensity Questionnaire</t>
+        </is>
+      </c>
+      <c r="H204" s="9" t="inlineStr">
+        <is>
+          <t>PI | PI | PI01</t>
+        </is>
+      </c>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>Version 1 (2012-08-07) of the pain intensity questionnaire created by the STANDARDS (Standardized Analgesic Database for Research, Discovery, and Submissions) committee and sponsored by ACTTION (Analgesic Clinical Trial Translations, Innovations, Opportunities, and Networks).</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="inlineStr">
+        <is>
+          <t>C3539772</t>
+        </is>
+      </c>
       <c r="K204" s="9" t="inlineStr"/>
       <c r="L204" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M204" s="10" t="inlineStr">
@@ -16333,7 +17367,7 @@
       </c>
       <c r="L205" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M205" s="11" t="inlineStr">
@@ -16413,7 +17447,7 @@
       </c>
       <c r="L206" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M206" s="10" t="inlineStr">
@@ -16493,7 +17527,7 @@
       </c>
       <c r="L207" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M207" s="11" t="inlineStr">
@@ -16545,15 +17579,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F208" s="9" t="inlineStr"/>
-      <c r="G208" s="9" t="inlineStr"/>
-      <c r="H208" s="9" t="inlineStr"/>
-      <c r="I208" s="9" t="inlineStr"/>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>C138355</t>
+        </is>
+      </c>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Young Adult Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT | PQL01 | PedsQL Neuromuscular Module Version 3.0 Young Adult Report</t>
+        </is>
+      </c>
+      <c r="I208" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past month in patients ages 18 to 25 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J208" s="9" t="inlineStr"/>
-      <c r="K208" s="9" t="inlineStr"/>
+      <c r="K208" s="9" t="inlineStr">
+        <is>
+          <t>CL525817</t>
+        </is>
+      </c>
       <c r="L208" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M208" s="10" t="inlineStr">
@@ -16605,15 +17659,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F209" s="11" t="inlineStr"/>
-      <c r="G209" s="11" t="inlineStr"/>
-      <c r="H209" s="11" t="inlineStr"/>
-      <c r="I209" s="11" t="inlineStr"/>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>C138352</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Parent Report for Young Adults Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H209" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT PARENT REPORT | PQL02 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Adults Report</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past month in individuals ages 18 to 25 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J209" s="11" t="inlineStr"/>
-      <c r="K209" s="11" t="inlineStr"/>
+      <c r="K209" s="11" t="inlineStr">
+        <is>
+          <t>CL525812</t>
+        </is>
+      </c>
       <c r="L209" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M209" s="11" t="inlineStr">
@@ -16665,15 +17739,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F210" s="9" t="inlineStr"/>
-      <c r="G210" s="9" t="inlineStr"/>
-      <c r="H210" s="9" t="inlineStr"/>
-      <c r="I210" s="9" t="inlineStr"/>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>C138354</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Teen Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN | PQL03 | PedsQL Neuromuscular Module Version 3.0 Teen Report</t>
+        </is>
+      </c>
+      <c r="I210" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past month in children ages 13 to 18 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J210" s="9" t="inlineStr"/>
-      <c r="K210" s="9" t="inlineStr"/>
+      <c r="K210" s="9" t="inlineStr">
+        <is>
+          <t>CL525818</t>
+        </is>
+      </c>
       <c r="L210" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M210" s="10" t="inlineStr">
@@ -16725,15 +17819,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F211" s="11" t="inlineStr"/>
-      <c r="G211" s="11" t="inlineStr"/>
-      <c r="H211" s="11" t="inlineStr"/>
-      <c r="I211" s="11" t="inlineStr"/>
+      <c r="F211" s="11" t="inlineStr">
+        <is>
+          <t>C138351</t>
+        </is>
+      </c>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Parent Report for Teen Questionnaire</t>
+        </is>
+      </c>
+      <c r="H211" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN PARENT REPORT | PQL04 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Teen</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past month in children ages 13 to 18 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J211" s="11" t="inlineStr"/>
-      <c r="K211" s="11" t="inlineStr"/>
+      <c r="K211" s="11" t="inlineStr">
+        <is>
+          <t>CL525813</t>
+        </is>
+      </c>
       <c r="L211" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M211" s="11" t="inlineStr">
@@ -16785,15 +17899,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F212" s="9" t="inlineStr"/>
-      <c r="G212" s="9" t="inlineStr"/>
-      <c r="H212" s="9" t="inlineStr"/>
-      <c r="I212" s="9" t="inlineStr"/>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>C138348</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Child Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD | PQL05 | PedsQL Neuromuscular Module Version 3.0 Child Report</t>
+        </is>
+      </c>
+      <c r="I212" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past month in children ages 8 to 12 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J212" s="9" t="inlineStr"/>
-      <c r="K212" s="9" t="inlineStr"/>
+      <c r="K212" s="9" t="inlineStr">
+        <is>
+          <t>CL525808</t>
+        </is>
+      </c>
       <c r="L212" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M212" s="10" t="inlineStr">
@@ -16845,15 +17979,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F213" s="11" t="inlineStr"/>
-      <c r="G213" s="11" t="inlineStr"/>
-      <c r="H213" s="11" t="inlineStr"/>
-      <c r="I213" s="11" t="inlineStr"/>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>C138350</t>
+        </is>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Parent Report for Child Questionnaire</t>
+        </is>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD PARENT REPORT | PQL06 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Child</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past month in children ages 8 to 12 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J213" s="11" t="inlineStr"/>
-      <c r="K213" s="11" t="inlineStr"/>
+      <c r="K213" s="11" t="inlineStr">
+        <is>
+          <t>CL525814</t>
+        </is>
+      </c>
       <c r="L213" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M213" s="11" t="inlineStr">
@@ -16905,15 +18059,35 @@
           <t>17</t>
         </is>
       </c>
-      <c r="F214" s="9" t="inlineStr"/>
-      <c r="G214" s="9" t="inlineStr"/>
-      <c r="H214" s="9" t="inlineStr"/>
-      <c r="I214" s="9" t="inlineStr"/>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>C138356</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Young Child Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD | PQL07 | PedsQL Neuromuscular Module Version 3.0 Young Child Report</t>
+        </is>
+      </c>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>A 17-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure one dimension of patient reported health related quality of life over the past month in children ages 5 to 7 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J214" s="9" t="inlineStr"/>
-      <c r="K214" s="9" t="inlineStr"/>
+      <c r="K214" s="9" t="inlineStr">
+        <is>
+          <t>CL525816</t>
+        </is>
+      </c>
       <c r="L214" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M214" s="10" t="inlineStr">
@@ -16965,15 +18139,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F215" s="11" t="inlineStr"/>
-      <c r="G215" s="11" t="inlineStr"/>
-      <c r="H215" s="11" t="inlineStr"/>
-      <c r="I215" s="11" t="inlineStr"/>
+      <c r="F215" s="11" t="inlineStr">
+        <is>
+          <t>C138353</t>
+        </is>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Parent Report for Young Child Questionnaire</t>
+        </is>
+      </c>
+      <c r="H215" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD PARENT REPORT | PQL08 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Child</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past month in children ages 5 to 7 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J215" s="11" t="inlineStr"/>
-      <c r="K215" s="11" t="inlineStr"/>
+      <c r="K215" s="11" t="inlineStr">
+        <is>
+          <t>CL525819</t>
+        </is>
+      </c>
       <c r="L215" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M215" s="11" t="inlineStr">
@@ -17025,15 +18219,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F216" s="9" t="inlineStr"/>
-      <c r="G216" s="9" t="inlineStr"/>
-      <c r="H216" s="9" t="inlineStr"/>
-      <c r="I216" s="9" t="inlineStr"/>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>C138349</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Version 3.0 Parent of Toddler Questionnaire</t>
+        </is>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TODDLER PARENT REPORT | PQL09 | PedsQL Neuromuscular Module Version 3.0 Parent of Toddler</t>
+        </is>
+      </c>
+      <c r="I216" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past month in children ages 2 to 4 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J216" s="9" t="inlineStr"/>
-      <c r="K216" s="9" t="inlineStr"/>
+      <c r="K216" s="9" t="inlineStr">
+        <is>
+          <t>CL525815</t>
+        </is>
+      </c>
       <c r="L216" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M216" s="10" t="inlineStr">
@@ -17085,15 +18299,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F217" s="11" t="inlineStr"/>
-      <c r="G217" s="11" t="inlineStr"/>
-      <c r="H217" s="11" t="inlineStr"/>
-      <c r="I217" s="11" t="inlineStr"/>
+      <c r="F217" s="11" t="inlineStr">
+        <is>
+          <t>C138346</t>
+        </is>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Young Adult Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H217" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT | PQL10 | PedsQL Neuromuscular Module Acute Version 3.0 Young Adult Report</t>
+        </is>
+      </c>
+      <c r="I217" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past seven days in individuals ages 18 to 25 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J217" s="11" t="inlineStr"/>
-      <c r="K217" s="11" t="inlineStr"/>
+      <c r="K217" s="11" t="inlineStr">
+        <is>
+          <t>CL525810</t>
+        </is>
+      </c>
       <c r="L217" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M217" s="11" t="inlineStr">
@@ -17145,15 +18379,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr"/>
-      <c r="G218" s="9" t="inlineStr"/>
-      <c r="H218" s="9" t="inlineStr"/>
-      <c r="I218" s="9" t="inlineStr"/>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>C138343</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Parent Report for Young Adults Questionnaire</t>
+        </is>
+      </c>
+      <c r="H218" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT PARENT REPORT | PQL11 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Adults</t>
+        </is>
+      </c>
+      <c r="I218" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease-specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past seven days in individuals ages 18 to 25 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J218" s="9" t="inlineStr"/>
-      <c r="K218" s="9" t="inlineStr"/>
+      <c r="K218" s="9" t="inlineStr">
+        <is>
+          <t>CL525805</t>
+        </is>
+      </c>
       <c r="L218" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M218" s="10" t="inlineStr">
@@ -17205,15 +18459,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F219" s="11" t="inlineStr"/>
-      <c r="G219" s="11" t="inlineStr"/>
-      <c r="H219" s="11" t="inlineStr"/>
-      <c r="I219" s="11" t="inlineStr"/>
+      <c r="F219" s="11" t="inlineStr">
+        <is>
+          <t>C138345</t>
+        </is>
+      </c>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Teen Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H219" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN | PQL12 | PedsQL Neuromuscular Module Acute Version 3.0 Teen Report</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease-specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past seven days in children ages 13 to 18 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J219" s="11" t="inlineStr"/>
-      <c r="K219" s="11" t="inlineStr"/>
+      <c r="K219" s="11" t="inlineStr">
+        <is>
+          <t>CL525811</t>
+        </is>
+      </c>
       <c r="L219" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M219" s="11" t="inlineStr">
@@ -17265,15 +18539,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F220" s="9" t="inlineStr"/>
-      <c r="G220" s="9" t="inlineStr"/>
-      <c r="H220" s="9" t="inlineStr"/>
-      <c r="I220" s="9" t="inlineStr"/>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>C138342</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Parent Report for Teen Questionnaire</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN PARENT REPORT | PQL13 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Teen</t>
+        </is>
+      </c>
+      <c r="I220" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease-specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past seven days in children ages 13 to 18 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J220" s="9" t="inlineStr"/>
-      <c r="K220" s="9" t="inlineStr"/>
+      <c r="K220" s="9" t="inlineStr">
+        <is>
+          <t>CL525806</t>
+        </is>
+      </c>
       <c r="L220" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M220" s="10" t="inlineStr">
@@ -17325,15 +18619,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F221" s="11" t="inlineStr"/>
-      <c r="G221" s="11" t="inlineStr"/>
-      <c r="H221" s="11" t="inlineStr"/>
-      <c r="I221" s="11" t="inlineStr"/>
+      <c r="F221" s="11" t="inlineStr">
+        <is>
+          <t>C138339</t>
+        </is>
+      </c>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Child Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H221" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD | PQL14 | PedsQL Neuromuscular Module Acute Version 3.0 Child Report</t>
+        </is>
+      </c>
+      <c r="I221" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of patient reported health related quality of life over the past seven days in children ages 8 to 12 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J221" s="11" t="inlineStr"/>
-      <c r="K221" s="11" t="inlineStr"/>
+      <c r="K221" s="11" t="inlineStr">
+        <is>
+          <t>CL525830</t>
+        </is>
+      </c>
       <c r="L221" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M221" s="11" t="inlineStr">
@@ -17385,15 +18699,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F222" s="9" t="inlineStr"/>
-      <c r="G222" s="9" t="inlineStr"/>
-      <c r="H222" s="9" t="inlineStr"/>
-      <c r="I222" s="9" t="inlineStr"/>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>C138341</t>
+        </is>
+      </c>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Parent Report for Child Questionnaire</t>
+        </is>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD PARENT REPORT | PQL15 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Child</t>
+        </is>
+      </c>
+      <c r="I222" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease-specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past seven days in children ages 8 to 12 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J222" s="9" t="inlineStr"/>
-      <c r="K222" s="9" t="inlineStr"/>
+      <c r="K222" s="9" t="inlineStr">
+        <is>
+          <t>CL525807</t>
+        </is>
+      </c>
       <c r="L222" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M222" s="10" t="inlineStr">
@@ -17445,15 +18779,35 @@
           <t>17</t>
         </is>
       </c>
-      <c r="F223" s="11" t="inlineStr"/>
-      <c r="G223" s="11" t="inlineStr"/>
-      <c r="H223" s="11" t="inlineStr"/>
-      <c r="I223" s="11" t="inlineStr"/>
+      <c r="F223" s="11" t="inlineStr">
+        <is>
+          <t>C138347</t>
+        </is>
+      </c>
+      <c r="G223" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Young Child Report Questionnaire</t>
+        </is>
+      </c>
+      <c r="H223" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD | PQL16 | PedsQL Neuromuscular Module Acute Version 3.0 Young Child Report</t>
+        </is>
+      </c>
+      <c r="I223" s="11" t="inlineStr">
+        <is>
+          <t>A 17-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure one dimension of patient reported health related quality of life over the past seven days in children ages 5 to 7 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J223" s="11" t="inlineStr"/>
-      <c r="K223" s="11" t="inlineStr"/>
+      <c r="K223" s="11" t="inlineStr">
+        <is>
+          <t>CL525809</t>
+        </is>
+      </c>
       <c r="L223" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M223" s="11" t="inlineStr">
@@ -17505,15 +18859,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F224" s="9" t="inlineStr"/>
-      <c r="G224" s="9" t="inlineStr"/>
-      <c r="H224" s="9" t="inlineStr"/>
-      <c r="I224" s="9" t="inlineStr"/>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>C138344</t>
+        </is>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Parent Report for Young Child Questionnaire</t>
+        </is>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD PARENT REPORT | PQL17 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Child</t>
+        </is>
+      </c>
+      <c r="I224" s="9" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past seven days in children ages 5 to 7 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J224" s="9" t="inlineStr"/>
-      <c r="K224" s="9" t="inlineStr"/>
+      <c r="K224" s="9" t="inlineStr">
+        <is>
+          <t>CL525804</t>
+        </is>
+      </c>
       <c r="L224" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M224" s="10" t="inlineStr">
@@ -17565,15 +18939,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F225" s="11" t="inlineStr"/>
-      <c r="G225" s="11" t="inlineStr"/>
-      <c r="H225" s="11" t="inlineStr"/>
-      <c r="I225" s="11" t="inlineStr"/>
+      <c r="F225" s="11" t="inlineStr">
+        <is>
+          <t>C138340</t>
+        </is>
+      </c>
+      <c r="G225" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Quality of Life Neuromuscular Module Acute Version 3.0 Parent of Toddler Questionnaire</t>
+        </is>
+      </c>
+      <c r="H225" s="11" t="inlineStr">
+        <is>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TODDLER PARENT REPORT | PQL18 | PedsQL Neuromuscular Module Acute Version 3.0 Parent of Toddler</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="inlineStr">
+        <is>
+          <t>A 25-item disease specific complement to the Pediatric Quality of Life Inventory instrument published by Sarah Davis et al. in 2010 that utilizes a 5-point Likert scale to measure three dimensions of parent reported health related quality of life over the past seven days in children ages 2 to 4 years with neuromuscular disorders.</t>
+        </is>
+      </c>
       <c r="J225" s="11" t="inlineStr"/>
-      <c r="K225" s="11" t="inlineStr"/>
+      <c r="K225" s="11" t="inlineStr">
+        <is>
+          <t>CL525829</t>
+        </is>
+      </c>
       <c r="L225" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M225" s="11" t="inlineStr">
@@ -17625,15 +19019,35 @@
           <t>11</t>
         </is>
       </c>
-      <c r="F226" s="9" t="inlineStr"/>
-      <c r="G226" s="9" t="inlineStr"/>
-      <c r="H226" s="9" t="inlineStr"/>
-      <c r="I226" s="9" t="inlineStr"/>
-      <c r="J226" s="9" t="inlineStr"/>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>C105168</t>
+        </is>
+      </c>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>STANDARDS Pain Relief Questionnaire</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>PR | PR | PR01</t>
+        </is>
+      </c>
+      <c r="I226" s="9" t="inlineStr">
+        <is>
+          <t>Version 1 (2012-08-07) of the pain relief questionnaire created by the STANDARDS (Standardized Analgesic Database for Research, Discovery, and Submissions) committee and sponsored by ACTTION (Analgesic Clinical Trial Translations, Innovations, Opportunities, and Networks).</t>
+        </is>
+      </c>
+      <c r="J226" s="9" t="inlineStr">
+        <is>
+          <t>C3538934</t>
+        </is>
+      </c>
       <c r="K226" s="9" t="inlineStr"/>
       <c r="L226" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M226" s="10" t="inlineStr">
@@ -17685,15 +19099,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F227" s="11" t="inlineStr"/>
-      <c r="G227" s="11" t="inlineStr"/>
-      <c r="H227" s="11" t="inlineStr"/>
-      <c r="I227" s="11" t="inlineStr"/>
+      <c r="F227" s="11" t="inlineStr">
+        <is>
+          <t>C127372</t>
+        </is>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>Prostate Cancer Specific Quality of Life Instrument Questionnaire</t>
+        </is>
+      </c>
+      <c r="H227" s="11" t="inlineStr">
+        <is>
+          <t>PROS01 | PROSQOLI | PROSQOLI</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Stockler et al in 1999 which is used to assess health-related quality of life in patients with advanced hormone-resistant prostate cancer. The instrument contains 9 linear analogue self-assessment scales measuring symptoms, function, and overall well-being, and a six-point ordinal adjectival scale of present pain intensity from the McGill Pain Questionnaire.</t>
+        </is>
+      </c>
       <c r="J227" s="11" t="inlineStr"/>
-      <c r="K227" s="11" t="inlineStr"/>
+      <c r="K227" s="11" t="inlineStr">
+        <is>
+          <t>CL509295</t>
+        </is>
+      </c>
       <c r="L227" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M227" s="11" t="inlineStr">
@@ -17773,7 +19207,7 @@
       </c>
       <c r="L228" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M228" s="10" t="inlineStr">
@@ -17853,7 +19287,7 @@
       </c>
       <c r="L229" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M229" s="11" t="inlineStr">
@@ -17933,7 +19367,7 @@
       </c>
       <c r="L230" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M230" s="10" t="inlineStr">
@@ -18013,7 +19447,7 @@
       </c>
       <c r="L231" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M231" s="11" t="inlineStr">
@@ -18093,7 +19527,7 @@
       </c>
       <c r="L232" s="9" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M232" s="10" t="inlineStr">
@@ -18145,15 +19579,35 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F233" s="11" t="inlineStr"/>
-      <c r="G233" s="11" t="inlineStr"/>
-      <c r="H233" s="11" t="inlineStr"/>
-      <c r="I233" s="11" t="inlineStr"/>
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>C199519</t>
+        </is>
+      </c>
+      <c r="G233" s="11" t="inlineStr">
+        <is>
+          <t>Brief Questionnaire of Smoking Urges</t>
+        </is>
+      </c>
+      <c r="H233" s="11" t="inlineStr">
+        <is>
+          <t>QSU-BRIEF | QSU-Brief | QSUB01</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="inlineStr">
+        <is>
+          <t>A standardized self-administered 10-item questionnaire, developed in 2001 by Cox et al. as an abbreviated version of the original Questionnaire of Smoking Urges, that utilizes a seven-point rating scale to assess the respondent's feelings and thoughts about his or her desire to smoke cigarettes.</t>
+        </is>
+      </c>
       <c r="J233" s="11" t="inlineStr"/>
-      <c r="K233" s="11" t="inlineStr"/>
+      <c r="K233" s="11" t="inlineStr">
+        <is>
+          <t>CL1906874</t>
+        </is>
+      </c>
       <c r="L233" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M233" s="11" t="inlineStr">
@@ -18233,7 +19687,7 @@
       <c r="K234" s="9" t="inlineStr"/>
       <c r="L234" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M234" s="10" t="inlineStr">
@@ -18313,7 +19767,7 @@
       <c r="K235" s="11" t="inlineStr"/>
       <c r="L235" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M235" s="11" t="inlineStr">
@@ -18365,15 +19819,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F236" s="9" t="inlineStr"/>
-      <c r="G236" s="9" t="inlineStr"/>
-      <c r="H236" s="9" t="inlineStr"/>
-      <c r="I236" s="9" t="inlineStr"/>
-      <c r="J236" s="9" t="inlineStr"/>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>C119103</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>Rivermead Post-Concussion Symptoms Questionnaire</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>RPQ | RPQ | RPQ01</t>
+        </is>
+      </c>
+      <c r="I236" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale originally developed by King et al in 1995, which is used to measure the severity of symptoms following a mild or moderate traumatic brain injury (TBI). The questionnaire requires a subject to rate the severity of 16 different cognitive, somatic, and emotional symptoms after a TBI on a scale of 0 to 4: not experienced at all (0), no more of a problem (1), a mild problem (2), a moderate problem (3), or a severe problem (4).</t>
+        </is>
+      </c>
+      <c r="J236" s="9" t="inlineStr">
+        <is>
+          <t>C3897695</t>
+        </is>
+      </c>
       <c r="K236" s="9" t="inlineStr"/>
       <c r="L236" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M236" s="10" t="inlineStr">
@@ -18453,7 +19927,7 @@
       </c>
       <c r="L237" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M237" s="11" t="inlineStr">
@@ -18533,7 +20007,7 @@
       <c r="K238" s="9" t="inlineStr"/>
       <c r="L238" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M238" s="10" t="inlineStr">
@@ -18613,7 +20087,7 @@
       </c>
       <c r="L239" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M239" s="11" t="inlineStr">
@@ -18693,7 +20167,7 @@
       </c>
       <c r="L240" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M240" s="10" t="inlineStr">
@@ -18773,7 +20247,7 @@
       </c>
       <c r="L241" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M241" s="11" t="inlineStr">
@@ -18853,7 +20327,7 @@
       </c>
       <c r="L242" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M242" s="10" t="inlineStr">
@@ -18933,7 +20407,7 @@
       </c>
       <c r="L243" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M243" s="11" t="inlineStr">
@@ -19013,7 +20487,7 @@
       </c>
       <c r="L244" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M244" s="10" t="inlineStr">
@@ -19065,15 +20539,35 @@
           <t>57</t>
         </is>
       </c>
-      <c r="F245" s="11" t="inlineStr"/>
-      <c r="G245" s="11" t="inlineStr"/>
-      <c r="H245" s="11" t="inlineStr"/>
-      <c r="I245" s="11" t="inlineStr"/>
-      <c r="J245" s="11" t="inlineStr"/>
+      <c r="F245" s="11" t="inlineStr">
+        <is>
+          <t>C100775</t>
+        </is>
+      </c>
+      <c r="G245" s="11" t="inlineStr">
+        <is>
+          <t>Short Form 36 Health Survey Standard, US Version 1.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H245" s="11" t="inlineStr">
+        <is>
+          <t>SF36 V1.0 STANDARD | SF36 v1.0 Standard | SF361</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="inlineStr">
+        <is>
+          <t>A standardized, multipurpose, general health survey developed by John E. Ware and copyrighted by Medical Outcomes Trust and Quality Metric Inc. in 1988 and 2002 which is used to assess the patient's functional health and overall well-being. This instrument contains 36 questions to be completed by the patient. For each question the patient must choose from five different responses.</t>
+        </is>
+      </c>
+      <c r="J245" s="11" t="inlineStr">
+        <is>
+          <t>C3639718</t>
+        </is>
+      </c>
       <c r="K245" s="11" t="inlineStr"/>
       <c r="L245" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M245" s="11" t="inlineStr">
@@ -19125,15 +20619,35 @@
           <t>57</t>
         </is>
       </c>
-      <c r="F246" s="9" t="inlineStr"/>
-      <c r="G246" s="9" t="inlineStr"/>
-      <c r="H246" s="9" t="inlineStr"/>
-      <c r="I246" s="9" t="inlineStr"/>
-      <c r="J246" s="9" t="inlineStr"/>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>C102120</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>Short Form 36 Health Survey Acute, US Version 1.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H246" s="9" t="inlineStr">
+        <is>
+          <t>SF36 V1.0 ACUTE | SF36 v1.0 Acute | SF362</t>
+        </is>
+      </c>
+      <c r="I246" s="9" t="inlineStr">
+        <is>
+          <t>A standardized, multipurpose, general health survey developed by John E. Ware and copyrighted by the Medical Outcomes Trust and Quality Metric Inc. in 1988 and 2002, which is used to assess the patient's functional health and overall well-being. This first version contains 36 questions that refer to the patient's symptoms or status within the past week and can be completed by the patient. For each question the patient must choose from five different responses.</t>
+        </is>
+      </c>
+      <c r="J246" s="9" t="inlineStr">
+        <is>
+          <t>C3640519</t>
+        </is>
+      </c>
       <c r="K246" s="9" t="inlineStr"/>
       <c r="L246" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M246" s="10" t="inlineStr">
@@ -19185,15 +20699,35 @@
           <t>62</t>
         </is>
       </c>
-      <c r="F247" s="11" t="inlineStr"/>
-      <c r="G247" s="11" t="inlineStr"/>
-      <c r="H247" s="11" t="inlineStr"/>
-      <c r="I247" s="11" t="inlineStr"/>
-      <c r="J247" s="11" t="inlineStr"/>
+      <c r="F247" s="11" t="inlineStr">
+        <is>
+          <t>C102122</t>
+        </is>
+      </c>
+      <c r="G247" s="11" t="inlineStr">
+        <is>
+          <t>Short Form 36 Health Survey Standard, US Version 2.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H247" s="11" t="inlineStr">
+        <is>
+          <t>Medical Outcomes Survey 36-Item Short-Form Health Survey | SF36 V2.0 STANDARD | SF36 v2.0 Standard | SF363 | Short Form 36 Health Survey</t>
+        </is>
+      </c>
+      <c r="I247" s="11" t="inlineStr">
+        <is>
+          <t>A standardized, multipurpose, general health survey developed by John E. Ware and copyrighted by Quality Metric Inc. and the Medical Outcomes Trust in 1996 and 2000 which is used to assess the patient's functional health and overall well-being. This second version contains 36 questions that refer to the patient's symptoms or status within the past four weeks and can be completed by the patient. For each question the patient must choose from five different responses.</t>
+        </is>
+      </c>
+      <c r="J247" s="11" t="inlineStr">
+        <is>
+          <t>C3640521</t>
+        </is>
+      </c>
       <c r="K247" s="11" t="inlineStr"/>
       <c r="L247" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M247" s="11" t="inlineStr">
@@ -19245,15 +20779,35 @@
           <t>62</t>
         </is>
       </c>
-      <c r="F248" s="9" t="inlineStr"/>
-      <c r="G248" s="9" t="inlineStr"/>
-      <c r="H248" s="9" t="inlineStr"/>
-      <c r="I248" s="9" t="inlineStr"/>
-      <c r="J248" s="9" t="inlineStr"/>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>C102121</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>Short Form 36 Health Survey Acute, US Version 2.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>SF36 V2.0 ACUTE | SF36 v2.0 Acute | SF364</t>
+        </is>
+      </c>
+      <c r="I248" s="9" t="inlineStr">
+        <is>
+          <t>A standardized, multipurpose, general health survey developed by John E. Ware and copyrighted by Quality Metric Inc. and the Medical Outcomes Trust in 1996 and 2000, which is used to assess the patient's functional health and overall well-being. This second version contains 36 questions that refer to the patient's symptoms or status within the past week and can be completed by the patient. For each question the patient must choose from five different responses.</t>
+        </is>
+      </c>
+      <c r="J248" s="9" t="inlineStr">
+        <is>
+          <t>C3640520</t>
+        </is>
+      </c>
       <c r="K248" s="9" t="inlineStr"/>
       <c r="L248" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M248" s="10" t="inlineStr">
@@ -19333,7 +20887,7 @@
       </c>
       <c r="L249" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M249" s="11" t="inlineStr">
@@ -19413,7 +20967,7 @@
       </c>
       <c r="L250" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M250" s="10" t="inlineStr">
@@ -19493,7 +21047,7 @@
       </c>
       <c r="L251" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M251" s="11" t="inlineStr">
@@ -19573,7 +21127,7 @@
       </c>
       <c r="L252" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M252" s="10" t="inlineStr">
@@ -19653,7 +21207,7 @@
       <c r="K253" s="11" t="inlineStr"/>
       <c r="L253" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M253" s="11" t="inlineStr">
@@ -19733,7 +21287,7 @@
       <c r="K254" s="9" t="inlineStr"/>
       <c r="L254" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M254" s="10" t="inlineStr">
@@ -19813,7 +21367,7 @@
       <c r="K255" s="11" t="inlineStr"/>
       <c r="L255" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M255" s="11" t="inlineStr">
@@ -19865,15 +21419,35 @@
           <t>41</t>
         </is>
       </c>
-      <c r="F256" s="9" t="inlineStr"/>
-      <c r="G256" s="9" t="inlineStr"/>
-      <c r="H256" s="9" t="inlineStr"/>
-      <c r="I256" s="9" t="inlineStr"/>
-      <c r="J256" s="9" t="inlineStr"/>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>C106890</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>St. George's Respiratory Questionnaire for Chronic Obstructive Pulmonary Disease Patients</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>SGRQ-C | SGRQ-C | SGRQC1</t>
+        </is>
+      </c>
+      <c r="I256" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Jones et al in 1992, which is a shorter version derived from the original SGRQ, and used to measure health impairment and perceived well-being (quality of life) in patients with asthma and chronic obstructive pulmonary disease (COPD). It has also been used in patients with bronchiectasis, post tuberculosis, kyphoscoliosis and sarcoidosis. The questionnaire contains 2 parts of 14 questions. Part 1 comprises questions 1 to 7 and addresses the frequency of a subject's respiratory symptoms. Part 2 has questions 8 to 14 and addresses the patient's current state.</t>
+        </is>
+      </c>
+      <c r="J256" s="9" t="inlineStr">
+        <is>
+          <t>C3826872</t>
+        </is>
+      </c>
       <c r="K256" s="9" t="inlineStr"/>
       <c r="L256" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M256" s="10" t="inlineStr">
@@ -19953,7 +21527,7 @@
       </c>
       <c r="L257" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M257" s="11" t="inlineStr">
@@ -20005,15 +21579,35 @@
           <t>26</t>
         </is>
       </c>
-      <c r="F258" s="9" t="inlineStr"/>
-      <c r="G258" s="9" t="inlineStr"/>
-      <c r="H258" s="9" t="inlineStr"/>
-      <c r="I258" s="9" t="inlineStr"/>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>C150921</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr">
+        <is>
+          <t>Suicidal Ideation Questionnaire-Junior</t>
+        </is>
+      </c>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>SIQ-JR | SIQ-JR | SIQ02</t>
+        </is>
+      </c>
+      <c r="I258" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 15-item self-report questionnaire developed by William M. Reynolds in 1987 that utilizes a seven-point rating scale to assess the frequency of suicidal thoughts in adolescents grades 7 to 9.</t>
+        </is>
+      </c>
       <c r="J258" s="9" t="inlineStr"/>
-      <c r="K258" s="9" t="inlineStr"/>
+      <c r="K258" s="9" t="inlineStr">
+        <is>
+          <t>CL552766</t>
+        </is>
+      </c>
       <c r="L258" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M258" s="10" t="inlineStr">
@@ -20093,7 +21687,7 @@
       <c r="K259" s="11" t="inlineStr"/>
       <c r="L259" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M259" s="11" t="inlineStr">
@@ -20173,7 +21767,7 @@
       </c>
       <c r="L260" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M260" s="10" t="inlineStr">
@@ -20225,15 +21819,35 @@
           <t>26</t>
         </is>
       </c>
-      <c r="F261" s="11" t="inlineStr"/>
-      <c r="G261" s="11" t="inlineStr"/>
-      <c r="H261" s="11" t="inlineStr"/>
-      <c r="I261" s="11" t="inlineStr"/>
-      <c r="J261" s="11" t="inlineStr"/>
+      <c r="F261" s="11" t="inlineStr">
+        <is>
+          <t>C100777</t>
+        </is>
+      </c>
+      <c r="G261" s="11" t="inlineStr">
+        <is>
+          <t>Screener and Opioid Assessment for Patients with Pain Revised Questionnaire</t>
+        </is>
+      </c>
+      <c r="H261" s="11" t="inlineStr">
+        <is>
+          <t>SOAPP-R | SOAPR1</t>
+        </is>
+      </c>
+      <c r="I261" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed and copyrighted by Inflexxicon, Inc. which is used to aid clinicians in screening a patient's potential for long-term opioid use in the treatment of pain. This revised version consists of 24 questions which can be completed by the patient. Each question is rated on a scale of 0-4 with 0 being 'never' and 4 being 'very often'. A score equal to or greater than 18 indicates that the patient has a high risk of misusing opioids.</t>
+        </is>
+      </c>
+      <c r="J261" s="11" t="inlineStr">
+        <is>
+          <t>C3639720</t>
+        </is>
+      </c>
       <c r="K261" s="11" t="inlineStr"/>
       <c r="L261" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M261" s="11" t="inlineStr">
@@ -20313,7 +21927,7 @@
       <c r="K262" s="9" t="inlineStr"/>
       <c r="L262" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M262" s="10" t="inlineStr">
@@ -20393,7 +22007,7 @@
       </c>
       <c r="L263" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M263" s="11" t="inlineStr">
@@ -20473,7 +22087,7 @@
       <c r="K264" s="9" t="inlineStr"/>
       <c r="L264" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M264" s="10" t="inlineStr">
@@ -20553,7 +22167,7 @@
       </c>
       <c r="L265" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M265" s="11" t="inlineStr">
@@ -20633,7 +22247,7 @@
       </c>
       <c r="L266" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M266" s="10" t="inlineStr">
@@ -20713,7 +22327,7 @@
       </c>
       <c r="L267" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M267" s="11" t="inlineStr">
@@ -20793,7 +22407,7 @@
       <c r="K268" s="9" t="inlineStr"/>
       <c r="L268" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M268" s="10" t="inlineStr">
@@ -20873,7 +22487,7 @@
       <c r="K269" s="11" t="inlineStr"/>
       <c r="L269" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M269" s="11" t="inlineStr">
@@ -20925,15 +22539,35 @@
           <t>42</t>
         </is>
       </c>
-      <c r="F270" s="9" t="inlineStr"/>
-      <c r="G270" s="9" t="inlineStr"/>
-      <c r="H270" s="9" t="inlineStr"/>
-      <c r="I270" s="9" t="inlineStr"/>
-      <c r="J270" s="9" t="inlineStr"/>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>C112527</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr">
+        <is>
+          <t>Visual Functioning Questionnaire 25-Interviewer Administered Format Version 2000</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr">
+        <is>
+          <t>VFQ-25 INTERVIEWER ADMINISTERED | VFQ1 | VFQ25-Interviewer Administered Format</t>
+        </is>
+      </c>
+      <c r="I270" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by RAND and sponsored by the National Eye Institute (NEI) to assess the dimensions of self-reported vision-targeted health status that are most important for individuals with chronic eye disease. It also measures the influence of visual disability and symptoms on emotional well-being, mental health, social and daily visual functioning. This questionnaire is in the Interviewer Administered Format and contains 25 multiple choice questions across 3 domains; general health and vision, difficulty with activates, and response to vision problems. It also includes an appendix of additional 13 questions researchers can use to expand the scales up to 38 total items.</t>
+        </is>
+      </c>
+      <c r="J270" s="9" t="inlineStr">
+        <is>
+          <t>C3826864</t>
+        </is>
+      </c>
       <c r="K270" s="9" t="inlineStr"/>
       <c r="L270" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M270" s="10" t="inlineStr">
@@ -20985,15 +22619,35 @@
           <t>42</t>
         </is>
       </c>
-      <c r="F271" s="11" t="inlineStr"/>
-      <c r="G271" s="11" t="inlineStr"/>
-      <c r="H271" s="11" t="inlineStr"/>
-      <c r="I271" s="11" t="inlineStr"/>
-      <c r="J271" s="11" t="inlineStr"/>
+      <c r="F271" s="11" t="inlineStr">
+        <is>
+          <t>C112528</t>
+        </is>
+      </c>
+      <c r="G271" s="11" t="inlineStr">
+        <is>
+          <t>Visual Functioning Questionnaire 25-Self Administered Format Version 2000</t>
+        </is>
+      </c>
+      <c r="H271" s="11" t="inlineStr">
+        <is>
+          <t>VFQ-25 SELF ADMINISTERED | VFQ2 | VFQ25-Self Administered Format</t>
+        </is>
+      </c>
+      <c r="I271" s="11" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by RAND and sponsored by the National Eye Institute (NEI) to assess the dimensions of self-reported vision-targeted health status that are most important for individuals with chronic eye disease. It also measures the influence of visual disability and symptoms on emotional well-being, mental health, social and daily visual functioning. This questionnaire is in the Self or Patient Administered Format and contains 25 multiple choice questions across 3 domains; general health and vision, difficulty with activates, and response to vision problems. It also includes an appendix of additional 13 questions researchers can use to expand the scales up to 38 total items.</t>
+        </is>
+      </c>
+      <c r="J271" s="11" t="inlineStr">
+        <is>
+          <t>C3826863</t>
+        </is>
+      </c>
       <c r="K271" s="11" t="inlineStr"/>
       <c r="L271" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M271" s="11" t="inlineStr">
@@ -21073,7 +22727,7 @@
       <c r="K272" s="9" t="inlineStr"/>
       <c r="L272" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M272" s="10" t="inlineStr">
@@ -21125,15 +22779,35 @@
           <t>21</t>
         </is>
       </c>
-      <c r="F273" s="11" t="inlineStr"/>
-      <c r="G273" s="11" t="inlineStr"/>
-      <c r="H273" s="11" t="inlineStr"/>
-      <c r="I273" s="11" t="inlineStr"/>
+      <c r="F273" s="11" t="inlineStr">
+        <is>
+          <t>C130322</t>
+        </is>
+      </c>
+      <c r="G273" s="11" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 12-item Version Interviewer-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H273" s="11" t="inlineStr">
+        <is>
+          <t>WD1 | WHODAS 2.0 - 12-ITEM INTERVIEWER | WHODAS 2.0 12-item Version Interviewer-administered</t>
+        </is>
+      </c>
+      <c r="I273" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 12-item interviewer-administered questionnaire that utilizes a 5-point rating scale to provide a brief assessment of an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J273" s="11" t="inlineStr"/>
-      <c r="K273" s="11" t="inlineStr"/>
+      <c r="K273" s="11" t="inlineStr">
+        <is>
+          <t>CL513531</t>
+        </is>
+      </c>
       <c r="L273" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M273" s="11" t="inlineStr">
@@ -21185,15 +22859,35 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F274" s="9" t="inlineStr"/>
-      <c r="G274" s="9" t="inlineStr"/>
-      <c r="H274" s="9" t="inlineStr"/>
-      <c r="I274" s="9" t="inlineStr"/>
+      <c r="F274" s="9" t="inlineStr">
+        <is>
+          <t>C130323</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 12-item Version Proxy-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H274" s="9" t="inlineStr">
+        <is>
+          <t>WD2 | WHODAS 2.0 - 12-ITEM PROXY | WHODAS 2.0 12-item Version Proxy-administered</t>
+        </is>
+      </c>
+      <c r="I274" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 12-item questionnaire, administered by a friend, relative, or caretaker, that utilizes a 5-point rating scale to provide a brief assessment of an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J274" s="9" t="inlineStr"/>
-      <c r="K274" s="9" t="inlineStr"/>
+      <c r="K274" s="9" t="inlineStr">
+        <is>
+          <t>CL513548</t>
+        </is>
+      </c>
       <c r="L274" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M274" s="10" t="inlineStr">
@@ -21245,15 +22939,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F275" s="11" t="inlineStr"/>
-      <c r="G275" s="11" t="inlineStr"/>
-      <c r="H275" s="11" t="inlineStr"/>
-      <c r="I275" s="11" t="inlineStr"/>
+      <c r="F275" s="11" t="inlineStr">
+        <is>
+          <t>C130324</t>
+        </is>
+      </c>
+      <c r="G275" s="11" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 12-item Version Self-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H275" s="11" t="inlineStr">
+        <is>
+          <t>WD3 | WHODAS 2.0 - 12-ITEM SELF | WHODAS 2.0 12-item Version Self-administered</t>
+        </is>
+      </c>
+      <c r="I275" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 12-item self-report questionnaire that utilizes a 5-point rating scale to provide a brief assessment of an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J275" s="11" t="inlineStr"/>
-      <c r="K275" s="11" t="inlineStr"/>
+      <c r="K275" s="11" t="inlineStr">
+        <is>
+          <t>CL513564</t>
+        </is>
+      </c>
       <c r="L275" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M275" s="11" t="inlineStr">
@@ -21305,15 +23019,35 @@
           <t>49</t>
         </is>
       </c>
-      <c r="F276" s="9" t="inlineStr"/>
-      <c r="G276" s="9" t="inlineStr"/>
-      <c r="H276" s="9" t="inlineStr"/>
-      <c r="I276" s="9" t="inlineStr"/>
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>C130325</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 12+24-item Version Interviewer-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H276" s="9" t="inlineStr">
+        <is>
+          <t>WD4 | WHODAS 2.0 - 12 + 24-ITEM INTERVIEWER | WHODAS 2.0 12+24-item Version Interviewer-administered</t>
+        </is>
+      </c>
+      <c r="I276" s="9" t="inlineStr">
+        <is>
+          <t>A standardized interviewer-administered or computer-adaptive testing (CAT) questionnaire that utilizes a 5-point rating scale to assess an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire is initially administered as 12 items to screen for problematic domains of functioning. Up to 24 items are then added based on the initial responses. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J276" s="9" t="inlineStr"/>
-      <c r="K276" s="9" t="inlineStr"/>
+      <c r="K276" s="9" t="inlineStr">
+        <is>
+          <t>CL513614</t>
+        </is>
+      </c>
       <c r="L276" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M276" s="10" t="inlineStr">
@@ -21365,15 +23099,35 @@
           <t>49</t>
         </is>
       </c>
-      <c r="F277" s="11" t="inlineStr"/>
-      <c r="G277" s="11" t="inlineStr"/>
-      <c r="H277" s="11" t="inlineStr"/>
-      <c r="I277" s="11" t="inlineStr"/>
+      <c r="F277" s="11" t="inlineStr">
+        <is>
+          <t>C130319</t>
+        </is>
+      </c>
+      <c r="G277" s="11" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 36-item Version Interviewer-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H277" s="11" t="inlineStr">
+        <is>
+          <t>WD5 | WHODAS 2.0 - 36-ITEM INTERVIEWER | WHODAS 2.0 36-item Version Interviewer-administered</t>
+        </is>
+      </c>
+      <c r="I277" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 36-item interviewer-administered questionnaire that utilizes a 5-point rating scale to assess an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J277" s="11" t="inlineStr"/>
-      <c r="K277" s="11" t="inlineStr"/>
+      <c r="K277" s="11" t="inlineStr">
+        <is>
+          <t>CL513664</t>
+        </is>
+      </c>
       <c r="L277" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M277" s="11" t="inlineStr">
@@ -21425,15 +23179,35 @@
           <t>40</t>
         </is>
       </c>
-      <c r="F278" s="9" t="inlineStr"/>
-      <c r="G278" s="9" t="inlineStr"/>
-      <c r="H278" s="9" t="inlineStr"/>
-      <c r="I278" s="9" t="inlineStr"/>
+      <c r="F278" s="9" t="inlineStr">
+        <is>
+          <t>C130320</t>
+        </is>
+      </c>
+      <c r="G278" s="9" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 36-item Version Proxy-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H278" s="9" t="inlineStr">
+        <is>
+          <t>WD6 | WHODAS 2.0 - 36-ITEM PROXY | WHODAS 2.0 36-item Version Proxy-administered</t>
+        </is>
+      </c>
+      <c r="I278" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 36-item questionnaire, administered by a friend, relative, or caretaker, that utilizes a 5-point rating scale to assess an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J278" s="9" t="inlineStr"/>
-      <c r="K278" s="9" t="inlineStr"/>
+      <c r="K278" s="9" t="inlineStr">
+        <is>
+          <t>CL513705</t>
+        </is>
+      </c>
       <c r="L278" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M278" s="10" t="inlineStr">
@@ -21485,15 +23259,35 @@
           <t>39</t>
         </is>
       </c>
-      <c r="F279" s="11" t="inlineStr"/>
-      <c r="G279" s="11" t="inlineStr"/>
-      <c r="H279" s="11" t="inlineStr"/>
-      <c r="I279" s="11" t="inlineStr"/>
+      <c r="F279" s="11" t="inlineStr">
+        <is>
+          <t>C130321</t>
+        </is>
+      </c>
+      <c r="G279" s="11" t="inlineStr">
+        <is>
+          <t>World Health Organization Disability Assessment Schedule 2.0 36-item Version Self-administered Questionnaire</t>
+        </is>
+      </c>
+      <c r="H279" s="11" t="inlineStr">
+        <is>
+          <t>WD7 | WHODAS 2.0 - 36-ITEM SELF | WHODAS 2.0 36-item Version Self-administered</t>
+        </is>
+      </c>
+      <c r="I279" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 36-item self-report questionnaire that utilizes a 5-point rating scale to assess an individual's ability to perform activities in six domains of functioning over the 30 days prior to evaluation in order to calculate a global disability score. The questionnaire was developed in 2010 by the World Health Organization (WHO) Classification, Terminology and Standards team, within the framework of the WHO/National Institutes of Health (NIH) Joint Project on Assessment and Classification of Disability.</t>
+        </is>
+      </c>
       <c r="J279" s="11" t="inlineStr"/>
-      <c r="K279" s="11" t="inlineStr"/>
+      <c r="K279" s="11" t="inlineStr">
+        <is>
+          <t>CL513745</t>
+        </is>
+      </c>
       <c r="L279" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M279" s="11" t="inlineStr">
@@ -21545,15 +23339,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F280" s="9" t="inlineStr"/>
-      <c r="G280" s="9" t="inlineStr"/>
-      <c r="H280" s="9" t="inlineStr"/>
-      <c r="I280" s="9" t="inlineStr"/>
-      <c r="J280" s="9" t="inlineStr"/>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>C100779</t>
+        </is>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>Work Productivity and Activity Impairment Specific Health Problems Version 2.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H280" s="9" t="inlineStr">
+        <is>
+          <t>WPAI-SHP V2.0 | WPAI01</t>
+        </is>
+      </c>
+      <c r="I280" s="9" t="inlineStr">
+        <is>
+          <t>The second version of a standardized survey originally developed by Margaret C. Reilly in 1993 which is used to evaluate the extent to which a patient's specific health problems effect their ability to work and perform daily activities. This instrument consist of 6 questions which can be completed by the patient or in an interview format.</t>
+        </is>
+      </c>
+      <c r="J280" s="9" t="inlineStr">
+        <is>
+          <t>C3639722</t>
+        </is>
+      </c>
       <c r="K280" s="9" t="inlineStr"/>
       <c r="L280" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M280" s="10" t="inlineStr">
@@ -21605,15 +23419,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F281" s="11" t="inlineStr"/>
-      <c r="G281" s="11" t="inlineStr"/>
-      <c r="H281" s="11" t="inlineStr"/>
-      <c r="I281" s="11" t="inlineStr"/>
-      <c r="J281" s="11" t="inlineStr"/>
+      <c r="F281" s="11" t="inlineStr">
+        <is>
+          <t>C123285</t>
+        </is>
+      </c>
+      <c r="G281" s="11" t="inlineStr">
+        <is>
+          <t>Work Productivity and Activity Impairment General Health V2.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="H281" s="11" t="inlineStr">
+        <is>
+          <t>WPAI-GH V2.0 | WPAI-GH Version 2 | WPAI02 | WPAI:GH | Work Productivity and Activity Impairment General Health V2.0 Questionnaire (WPAI:GH) | Work Productivity and Activity Impairment General Health Version 2.0 Questionnaire</t>
+        </is>
+      </c>
+      <c r="I281" s="11" t="inlineStr">
+        <is>
+          <t>The second version of a standardized survey originally developed by Margaret C. Reilly in 1993 which is used to evaluate the extent to which a patient's general health problems effects their ability to work and perform daily activities. This instrument consists of 6 questions which can be completed by the patient or in an interview format.</t>
+        </is>
+      </c>
+      <c r="J281" s="11" t="inlineStr">
+        <is>
+          <t>C4053845</t>
+        </is>
+      </c>
       <c r="K281" s="11" t="inlineStr"/>
       <c r="L281" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M281" s="11" t="inlineStr">
@@ -21693,7 +23527,7 @@
       <c r="K282" s="9" t="inlineStr"/>
       <c r="L282" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M282" s="10" t="inlineStr">
@@ -21773,7 +23607,7 @@
       <c r="K283" s="11" t="inlineStr"/>
       <c r="L283" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M283" s="11" t="inlineStr">
@@ -21825,15 +23659,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F284" s="9" t="inlineStr"/>
-      <c r="G284" s="9" t="inlineStr"/>
-      <c r="H284" s="9" t="inlineStr"/>
-      <c r="I284" s="9" t="inlineStr"/>
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>C125755</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr">
+        <is>
+          <t>AJCC Cancer Staging Manual 7th Edition</t>
+        </is>
+      </c>
+      <c r="H284" s="9" t="inlineStr">
+        <is>
+          <t>7th | AJCC V7 | AJCC v7 | AJCC1 | AJCC7 | Seventh Edition (2010)</t>
+        </is>
+      </c>
+      <c r="I284" s="9" t="inlineStr">
+        <is>
+          <t>The 7th edition of the criteria developed by the American Joint Committee on Cancer (AJCC) in 2010, used for the classification and staging of neoplastic diseases.</t>
+        </is>
+      </c>
       <c r="J284" s="9" t="inlineStr"/>
-      <c r="K284" s="9" t="inlineStr"/>
+      <c r="K284" s="9" t="inlineStr">
+        <is>
+          <t>CL504410</t>
+        </is>
+      </c>
       <c r="L284" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M284" s="10" t="inlineStr">
@@ -21913,7 +23767,7 @@
       <c r="K285" s="11" t="inlineStr"/>
       <c r="L285" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M285" s="11" t="inlineStr">
@@ -21993,7 +23847,7 @@
       </c>
       <c r="L286" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M286" s="10" t="inlineStr">
@@ -22073,7 +23927,7 @@
       <c r="K287" s="11" t="inlineStr"/>
       <c r="L287" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M287" s="11" t="inlineStr">
@@ -22153,7 +24007,7 @@
       <c r="K288" s="9" t="inlineStr"/>
       <c r="L288" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M288" s="10" t="inlineStr">
@@ -22233,7 +24087,7 @@
       </c>
       <c r="L289" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M289" s="11" t="inlineStr">
@@ -22313,7 +24167,7 @@
       </c>
       <c r="L290" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M290" s="10" t="inlineStr">
@@ -22393,7 +24247,7 @@
       <c r="K291" s="11" t="inlineStr"/>
       <c r="L291" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M291" s="11" t="inlineStr">
@@ -22473,7 +24327,7 @@
       <c r="K292" s="9" t="inlineStr"/>
       <c r="L292" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M292" s="10" t="inlineStr">
@@ -22553,7 +24407,7 @@
       <c r="K293" s="11" t="inlineStr"/>
       <c r="L293" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M293" s="11" t="inlineStr">
@@ -22633,7 +24487,7 @@
       </c>
       <c r="L294" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M294" s="10" t="inlineStr">
@@ -22713,7 +24567,7 @@
       <c r="K295" s="11" t="inlineStr"/>
       <c r="L295" s="11" t="inlineStr">
         <is>
-          <t>normalized</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M295" s="11" t="inlineStr">
@@ -22793,7 +24647,7 @@
       </c>
       <c r="L296" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M296" s="10" t="inlineStr">
@@ -22873,7 +24727,7 @@
       <c r="K297" s="11" t="inlineStr"/>
       <c r="L297" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M297" s="11" t="inlineStr">
@@ -22953,7 +24807,7 @@
       </c>
       <c r="L298" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M298" s="10" t="inlineStr">
@@ -23033,7 +24887,7 @@
       </c>
       <c r="L299" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M299" s="11" t="inlineStr">
@@ -23113,7 +24967,7 @@
       </c>
       <c r="L300" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M300" s="10" t="inlineStr">
@@ -23193,7 +25047,7 @@
       <c r="K301" s="11" t="inlineStr"/>
       <c r="L301" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M301" s="11" t="inlineStr">
@@ -23273,7 +25127,7 @@
       </c>
       <c r="L302" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M302" s="10" t="inlineStr">
@@ -23349,7 +25203,7 @@
       <c r="K303" s="11" t="inlineStr"/>
       <c r="L303" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M303" s="11" t="inlineStr">
@@ -23425,7 +25279,7 @@
       </c>
       <c r="L304" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M304" s="10" t="inlineStr">
@@ -23505,7 +25359,7 @@
       <c r="K305" s="11" t="inlineStr"/>
       <c r="L305" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M305" s="11" t="inlineStr">
@@ -23585,7 +25439,7 @@
       </c>
       <c r="L306" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M306" s="10" t="inlineStr">
@@ -23665,7 +25519,7 @@
       <c r="K307" s="11" t="inlineStr"/>
       <c r="L307" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M307" s="11" t="inlineStr">
@@ -23745,7 +25599,7 @@
       <c r="K308" s="9" t="inlineStr"/>
       <c r="L308" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M308" s="10" t="inlineStr">
@@ -23825,7 +25679,7 @@
       <c r="K309" s="11" t="inlineStr"/>
       <c r="L309" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M309" s="11" t="inlineStr">
@@ -23905,7 +25759,7 @@
       <c r="K310" s="9" t="inlineStr"/>
       <c r="L310" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M310" s="10" t="inlineStr">
@@ -23985,7 +25839,7 @@
       <c r="K311" s="11" t="inlineStr"/>
       <c r="L311" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M311" s="11" t="inlineStr">
@@ -24065,7 +25919,7 @@
       <c r="K312" s="9" t="inlineStr"/>
       <c r="L312" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M312" s="10" t="inlineStr">
@@ -24145,7 +25999,7 @@
       <c r="K313" s="11" t="inlineStr"/>
       <c r="L313" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M313" s="11" t="inlineStr">
@@ -24225,7 +26079,7 @@
       </c>
       <c r="L314" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M314" s="10" t="inlineStr">
@@ -24305,7 +26159,7 @@
       <c r="K315" s="11" t="inlineStr"/>
       <c r="L315" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M315" s="11" t="inlineStr">
@@ -24357,15 +26211,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F316" s="9" t="inlineStr"/>
-      <c r="G316" s="9" t="inlineStr"/>
-      <c r="H316" s="9" t="inlineStr"/>
-      <c r="I316" s="9" t="inlineStr"/>
-      <c r="J316" s="9" t="inlineStr"/>
+      <c r="F316" s="9" t="inlineStr">
+        <is>
+          <t>C111382</t>
+        </is>
+      </c>
+      <c r="G316" s="9" t="inlineStr">
+        <is>
+          <t>Functional Assessment Questionnaire-NACC UDS Version 2.0 Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H316" s="9" t="inlineStr">
+        <is>
+          <t>FAQ-NACC UDS V2.0 | FAQ-NACC UDS Version 2.0 | FAQNA1</t>
+        </is>
+      </c>
+      <c r="I316" s="9" t="inlineStr">
+        <is>
+          <t>A standardized questionnaire developed by Pfeiffer et al in 1982 and adapted by National Alzheimer's Coordinating Center (NACC), which is used to measure instrumental activities of daily living such as preparing meals and managing personal finances in older adults with dementia. The questionnaire contains 10 items. For each activity, five levels of scores are specified: 'not applicable' (scored 8), 'normal' (scored 0), 'has difficulty, but does by self' (scored 1), 'requires assistance' (scored 2), and 'dependent' (scored 3).</t>
+        </is>
+      </c>
+      <c r="J316" s="9" t="inlineStr">
+        <is>
+          <t>C3827006</t>
+        </is>
+      </c>
       <c r="K316" s="9" t="inlineStr"/>
       <c r="L316" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M316" s="10" t="inlineStr">
@@ -24445,7 +26319,7 @@
       </c>
       <c r="L317" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M317" s="11" t="inlineStr">
@@ -24525,7 +26399,7 @@
       <c r="K318" s="9" t="inlineStr"/>
       <c r="L318" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M318" s="10" t="inlineStr">
@@ -24577,15 +26451,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F319" s="11" t="inlineStr"/>
-      <c r="G319" s="11" t="inlineStr"/>
-      <c r="H319" s="11" t="inlineStr"/>
-      <c r="I319" s="11" t="inlineStr"/>
-      <c r="J319" s="11" t="inlineStr"/>
+      <c r="F319" s="11" t="inlineStr">
+        <is>
+          <t>C105169</t>
+        </is>
+      </c>
+      <c r="G319" s="11" t="inlineStr">
+        <is>
+          <t>STANDARDS General Clinical Global Impressions Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H319" s="11" t="inlineStr">
+        <is>
+          <t>GCGI | GCGI | GCGI01</t>
+        </is>
+      </c>
+      <c r="I319" s="11" t="inlineStr">
+        <is>
+          <t>Version 1 (2012-08-07) of the general clinical global impression of pain questionnaire created by the STANDARDS (Standardized Analgesic Database for Research, Discovery, and Submissions) committee and sponsored by ACTTION (Analgesic Clinical Trial Translations, Innovations, Opportunities, and Networks).</t>
+        </is>
+      </c>
+      <c r="J319" s="11" t="inlineStr">
+        <is>
+          <t>C3641948</t>
+        </is>
+      </c>
       <c r="K319" s="11" t="inlineStr"/>
       <c r="L319" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M319" s="11" t="inlineStr">
@@ -24637,15 +26531,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F320" s="9" t="inlineStr"/>
-      <c r="G320" s="9" t="inlineStr"/>
-      <c r="H320" s="9" t="inlineStr"/>
-      <c r="I320" s="9" t="inlineStr"/>
-      <c r="J320" s="9" t="inlineStr"/>
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>C124710</t>
+        </is>
+      </c>
+      <c r="G320" s="9" t="inlineStr">
+        <is>
+          <t>Glasgow Coma Scale-NINDS Version 1.0 Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H320" s="9" t="inlineStr">
+        <is>
+          <t>GCS NINDS V1.0 | GCS NINDS Version 1.0 | GCS01</t>
+        </is>
+      </c>
+      <c r="I320" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by Teasdale and Jennett in 1974, which is a classification system used to assess the level of consciousness. The NINDS version measures eye opening, motor and verbal responses.</t>
+        </is>
+      </c>
+      <c r="J320" s="9" t="inlineStr">
+        <is>
+          <t>C4086362</t>
+        </is>
+      </c>
       <c r="K320" s="9" t="inlineStr"/>
       <c r="L320" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M320" s="10" t="inlineStr">
@@ -24725,7 +26639,7 @@
       <c r="K321" s="11" t="inlineStr"/>
       <c r="L321" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M321" s="11" t="inlineStr">
@@ -24777,15 +26691,35 @@
           <t>19</t>
         </is>
       </c>
-      <c r="F322" s="9" t="inlineStr"/>
-      <c r="G322" s="9" t="inlineStr"/>
-      <c r="H322" s="9" t="inlineStr"/>
-      <c r="I322" s="9" t="inlineStr"/>
-      <c r="J322" s="9" t="inlineStr"/>
+      <c r="F322" s="9" t="inlineStr">
+        <is>
+          <t>C100767</t>
+        </is>
+      </c>
+      <c r="G322" s="9" t="inlineStr">
+        <is>
+          <t>Hamilton Depression Rating Scale 17 Item Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H322" s="9" t="inlineStr">
+        <is>
+          <t>HAMD 17 | HAMD1</t>
+        </is>
+      </c>
+      <c r="I322" s="9" t="inlineStr">
+        <is>
+          <t>A standardized rating scale developed by M. Hamilton in 1960 which is used to evaluate the severity of an individual's depression. This instrument contains 17 questions or types of symptoms associated with depression such as anxiety, mood, insomnia, and somatic symptoms experienced within the past week and is completed during a semi-structured interview. Each symptom is rated on a scale of 0-2, 0-3, or 0-4 with 0 being absent and 2, 3, or 4 being the most severe. A score of 0-7 is considered normal while a score equal to or greater than 20 qualifies an individual for a clinical trial.</t>
+        </is>
+      </c>
+      <c r="J322" s="9" t="inlineStr">
+        <is>
+          <t>C3639712</t>
+        </is>
+      </c>
       <c r="K322" s="9" t="inlineStr"/>
       <c r="L322" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M322" s="10" t="inlineStr">
@@ -24865,7 +26799,7 @@
       <c r="K323" s="11" t="inlineStr"/>
       <c r="L323" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M323" s="11" t="inlineStr">
@@ -24917,15 +26851,35 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F324" s="9" t="inlineStr"/>
-      <c r="G324" s="9" t="inlineStr"/>
-      <c r="H324" s="9" t="inlineStr"/>
-      <c r="I324" s="9" t="inlineStr"/>
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>C130307</t>
+        </is>
+      </c>
+      <c r="G324" s="9" t="inlineStr">
+        <is>
+          <t>Hamilton Depression Rating Scale-24 Item Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H324" s="9" t="inlineStr">
+        <is>
+          <t>HAMD 24 | HAMD 24 | HAMD3</t>
+        </is>
+      </c>
+      <c r="I324" s="9" t="inlineStr">
+        <is>
+          <t>A standardized 24-item rating scale for the assessment of symptoms in patients diagnosed with depression. The original 17-item Hamilton Depression Scale, developed by Max Hamilton at the University of Leeds in 1960, was later modified to include 24 variables.</t>
+        </is>
+      </c>
       <c r="J324" s="9" t="inlineStr"/>
-      <c r="K324" s="9" t="inlineStr"/>
+      <c r="K324" s="9" t="inlineStr">
+        <is>
+          <t>CL513957</t>
+        </is>
+      </c>
       <c r="L324" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M324" s="10" t="inlineStr">
@@ -24977,15 +26931,35 @@
           <t>7</t>
         </is>
       </c>
-      <c r="F325" s="11" t="inlineStr"/>
-      <c r="G325" s="11" t="inlineStr"/>
-      <c r="H325" s="11" t="inlineStr"/>
-      <c r="I325" s="11" t="inlineStr"/>
+      <c r="F325" s="11" t="inlineStr">
+        <is>
+          <t>C130306</t>
+        </is>
+      </c>
+      <c r="G325" s="11" t="inlineStr">
+        <is>
+          <t>Hamilton Depression Rating Scale 6 Clinician Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H325" s="11" t="inlineStr">
+        <is>
+          <t>HAM-D6 Clinician Version | HAMD 6 CLINICIAN VERSION | HAMD4</t>
+        </is>
+      </c>
+      <c r="I325" s="11" t="inlineStr">
+        <is>
+          <t>A standardized 6-item clinician rating scale for the assessment of symptoms in patients diagnosed with depression. The original 17-item Hamilton Depression Scale, developed by Max Hamilton at the University of Leeds in 1960, was independently modified by Bech, et al. in 1975, using Rasch models, to create a subscale that contains six variables.</t>
+        </is>
+      </c>
       <c r="J325" s="11" t="inlineStr"/>
-      <c r="K325" s="11" t="inlineStr"/>
+      <c r="K325" s="11" t="inlineStr">
+        <is>
+          <t>CL513955</t>
+        </is>
+      </c>
       <c r="L325" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M325" s="11" t="inlineStr">
@@ -25065,7 +27039,7 @@
       </c>
       <c r="L326" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M326" s="10" t="inlineStr">
@@ -25145,7 +27119,7 @@
       </c>
       <c r="L327" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M327" s="11" t="inlineStr">
@@ -25225,7 +27199,7 @@
       </c>
       <c r="L328" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M328" s="10" t="inlineStr">
@@ -25305,7 +27279,7 @@
       </c>
       <c r="L329" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M329" s="11" t="inlineStr">
@@ -25385,7 +27359,7 @@
       </c>
       <c r="L330" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M330" s="10" t="inlineStr">
@@ -25465,7 +27439,7 @@
       <c r="K331" s="11" t="inlineStr"/>
       <c r="L331" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M331" s="11" t="inlineStr">
@@ -25545,7 +27519,7 @@
       <c r="K332" s="9" t="inlineStr"/>
       <c r="L332" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M332" s="10" t="inlineStr">
@@ -25625,7 +27599,7 @@
       </c>
       <c r="L333" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M333" s="11" t="inlineStr">
@@ -25705,7 +27679,7 @@
       <c r="K334" s="9" t="inlineStr"/>
       <c r="L334" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M334" s="10" t="inlineStr">
@@ -25785,7 +27759,7 @@
       </c>
       <c r="L335" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M335" s="11" t="inlineStr"/>
@@ -25849,7 +27823,7 @@
       <c r="K336" s="9" t="inlineStr"/>
       <c r="L336" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M336" s="10" t="inlineStr">
@@ -25929,7 +27903,7 @@
       </c>
       <c r="L337" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M337" s="11" t="inlineStr">
@@ -26009,7 +27983,7 @@
       </c>
       <c r="L338" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M338" s="10" t="inlineStr">
@@ -26089,7 +28063,7 @@
       <c r="K339" s="11" t="inlineStr"/>
       <c r="L339" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M339" s="11" t="inlineStr">
@@ -26169,7 +28143,7 @@
       </c>
       <c r="L340" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M340" s="10" t="inlineStr">
@@ -26249,7 +28223,7 @@
       <c r="K341" s="11" t="inlineStr"/>
       <c r="L341" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M341" s="11" t="inlineStr">
@@ -26301,15 +28275,35 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F342" s="9" t="inlineStr"/>
-      <c r="G342" s="9" t="inlineStr"/>
-      <c r="H342" s="9" t="inlineStr"/>
-      <c r="I342" s="9" t="inlineStr"/>
+      <c r="F342" s="9" t="inlineStr">
+        <is>
+          <t>C179972</t>
+        </is>
+      </c>
+      <c r="G342" s="9" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Feldman Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H342" s="9" t="inlineStr">
+        <is>
+          <t>PASI FELDMAN | PASI Feldman Version | PASI02</t>
+        </is>
+      </c>
+      <c r="I342" s="9" t="inlineStr">
+        <is>
+          <t>A standardized survey developed by Feldman and Krueger in 2005 to calculate the intensity and extent of psoriatic lesions before, during, and after treatment in chronic plaquetype psoriasis. The instrument utilizes a 5-point rating scale to measure intensity and assigns a numerical score for the percentage of anatomical involvement.</t>
+        </is>
+      </c>
       <c r="J342" s="9" t="inlineStr"/>
-      <c r="K342" s="9" t="inlineStr"/>
+      <c r="K342" s="9" t="inlineStr">
+        <is>
+          <t>CL1662719</t>
+        </is>
+      </c>
       <c r="L342" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M342" s="10" t="inlineStr">
@@ -26361,15 +28355,35 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F343" s="11" t="inlineStr"/>
-      <c r="G343" s="11" t="inlineStr"/>
-      <c r="H343" s="11" t="inlineStr"/>
-      <c r="I343" s="11" t="inlineStr"/>
+      <c r="F343" s="11" t="inlineStr">
+        <is>
+          <t>C191040</t>
+        </is>
+      </c>
+      <c r="G343" s="11" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H343" s="11" t="inlineStr">
+        <is>
+          <t>PASI FREDRIKSSON | PASI Fredriksson Version | PASI03</t>
+        </is>
+      </c>
+      <c r="I343" s="11" t="inlineStr">
+        <is>
+          <t>A standardized index developed in 1978 by Fredriksson et al. that combines psoriasis disease severity (measured as erythema, infiltration, and desquamation) and body surface area involvement over 4 body regions (head, trunk, upper and lower extremities) to assess progress during treatment.</t>
+        </is>
+      </c>
       <c r="J343" s="11" t="inlineStr"/>
-      <c r="K343" s="11" t="inlineStr"/>
+      <c r="K343" s="11" t="inlineStr">
+        <is>
+          <t>CL1799471</t>
+        </is>
+      </c>
       <c r="L343" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M343" s="11" t="inlineStr">
@@ -26421,15 +28435,35 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F344" s="9" t="inlineStr"/>
-      <c r="G344" s="9" t="inlineStr"/>
-      <c r="H344" s="9" t="inlineStr"/>
-      <c r="I344" s="9" t="inlineStr"/>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>C191041</t>
+        </is>
+      </c>
+      <c r="G344" s="9" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index European Medical Agency Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H344" s="9" t="inlineStr">
+        <is>
+          <t>PASI EMA | PASI EMA Version | PASI04</t>
+        </is>
+      </c>
+      <c r="I344" s="9" t="inlineStr">
+        <is>
+          <t>A standardized index developed in 2004 by the Committee for Medicinal Products for Human Use (CHMP) that combines psoriasis disease severity (measured as erythema, infiltration, and desquamation) and body surface area involvement over 4 body regions (head, trunk, upper and lower extremities) to assess progress during treatment.</t>
+        </is>
+      </c>
       <c r="J344" s="9" t="inlineStr"/>
-      <c r="K344" s="9" t="inlineStr"/>
+      <c r="K344" s="9" t="inlineStr">
+        <is>
+          <t>CL1799472</t>
+        </is>
+      </c>
       <c r="L344" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M344" s="10" t="inlineStr">
@@ -26481,15 +28515,35 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F345" s="11" t="inlineStr"/>
-      <c r="G345" s="11" t="inlineStr"/>
-      <c r="H345" s="11" t="inlineStr"/>
-      <c r="I345" s="11" t="inlineStr"/>
+      <c r="F345" s="11" t="inlineStr">
+        <is>
+          <t>C191042</t>
+        </is>
+      </c>
+      <c r="G345" s="11" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Bozek Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H345" s="11" t="inlineStr">
+        <is>
+          <t>PASI BOZEK | PASI Bozek Version | PASI05</t>
+        </is>
+      </c>
+      <c r="I345" s="11" t="inlineStr">
+        <is>
+          <t>A standardized index developed in 2017 by Bozek et al. that combines psoriasis disease severity (measured as erythema, infiltration, and desquamation) and body surface area involvement over 4 body regions (head, trunk, upper and lower extremities) to assess progress during treatment.</t>
+        </is>
+      </c>
       <c r="J345" s="11" t="inlineStr"/>
-      <c r="K345" s="11" t="inlineStr"/>
+      <c r="K345" s="11" t="inlineStr">
+        <is>
+          <t>CL1799466</t>
+        </is>
+      </c>
       <c r="L345" s="11" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M345" s="11" t="inlineStr">
@@ -26569,7 +28623,7 @@
       </c>
       <c r="L346" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M346" s="10" t="inlineStr">
@@ -26649,7 +28703,7 @@
       </c>
       <c r="L347" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M347" s="11" t="inlineStr">
@@ -26729,7 +28783,7 @@
       <c r="K348" s="9" t="inlineStr"/>
       <c r="L348" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M348" s="10" t="inlineStr">
@@ -26809,7 +28863,7 @@
       </c>
       <c r="L349" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M349" s="11" t="inlineStr">
@@ -26889,7 +28943,7 @@
       </c>
       <c r="L350" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M350" s="10" t="inlineStr">
@@ -26969,7 +29023,7 @@
       </c>
       <c r="L351" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M351" s="11" t="inlineStr">
@@ -27021,15 +29075,35 @@
           <t>7</t>
         </is>
       </c>
-      <c r="F352" s="9" t="inlineStr"/>
-      <c r="G352" s="9" t="inlineStr"/>
-      <c r="H352" s="9" t="inlineStr"/>
-      <c r="I352" s="9" t="inlineStr"/>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>C204319</t>
+        </is>
+      </c>
+      <c r="G352" s="9" t="inlineStr">
+        <is>
+          <t>Sepsis-related Organ Failure Assessment 1996 Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H352" s="9" t="inlineStr">
+        <is>
+          <t>SOFA 1996 | SOFA 1996 Version | SOFA01 | Sequential Organ Failure Assessment 1996</t>
+        </is>
+      </c>
+      <c r="I352" s="9" t="inlineStr">
+        <is>
+          <t>A standardized questionnaire, developed in 1994 at a Consensus Conference of the Working Group on Sepsis-Related Problems of the European Society of Intensive Care Medicine in Versailles, published in 1996, and renamed to the Sequential Organ Failure Assessment questionnaire, that assesses and scores the function of several body organ systems in patients with sepsis and critically ill patients without sepsis.</t>
+        </is>
+      </c>
       <c r="J352" s="9" t="inlineStr"/>
-      <c r="K352" s="9" t="inlineStr"/>
+      <c r="K352" s="9" t="inlineStr">
+        <is>
+          <t>CL1674407</t>
+        </is>
+      </c>
       <c r="L352" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M352" s="10" t="inlineStr">
@@ -27109,7 +29183,7 @@
       <c r="K353" s="11" t="inlineStr"/>
       <c r="L353" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M353" s="11" t="inlineStr">
@@ -27189,7 +29263,7 @@
       <c r="K354" s="9" t="inlineStr"/>
       <c r="L354" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M354" s="10" t="inlineStr">
@@ -27269,7 +29343,7 @@
       <c r="K355" s="11" t="inlineStr"/>
       <c r="L355" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M355" s="11" t="inlineStr">
@@ -27349,7 +29423,7 @@
       <c r="K356" s="9" t="inlineStr"/>
       <c r="L356" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M356" s="10" t="inlineStr">
@@ -27429,7 +29503,7 @@
       <c r="K357" s="11" t="inlineStr"/>
       <c r="L357" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M357" s="11" t="inlineStr">
@@ -27481,15 +29555,35 @@
           <t>112</t>
         </is>
       </c>
-      <c r="F358" s="9" t="inlineStr"/>
-      <c r="G358" s="9" t="inlineStr"/>
-      <c r="H358" s="9" t="inlineStr"/>
-      <c r="I358" s="9" t="inlineStr"/>
+      <c r="F358" s="9" t="inlineStr">
+        <is>
+          <t>C155324</t>
+        </is>
+      </c>
+      <c r="G358" s="9" t="inlineStr">
+        <is>
+          <t>Unified Huntington's Disease Rating Scale 1999 Version Clinical Classification</t>
+        </is>
+      </c>
+      <c r="H358" s="9" t="inlineStr">
+        <is>
+          <t>UHDR1 | UHDRS 1999 | UHDRS 1999 Version</t>
+        </is>
+      </c>
+      <c r="I358" s="9" t="inlineStr">
+        <is>
+          <t>An updated and expanded version of the standardized clinician rating scale developed by the Huntington Study Group in 1996 for the assessment of motor function, cognitive function, behavioral abnormalities, and functional capacity in Huntington's Disease.</t>
+        </is>
+      </c>
       <c r="J358" s="9" t="inlineStr"/>
-      <c r="K358" s="9" t="inlineStr"/>
+      <c r="K358" s="9" t="inlineStr">
+        <is>
+          <t>CL555951</t>
+        </is>
+      </c>
       <c r="L358" s="9" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M358" s="10" t="inlineStr">
@@ -27569,7 +29663,7 @@
       <c r="K359" s="11" t="inlineStr"/>
       <c r="L359" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M359" s="11" t="inlineStr">
@@ -27649,7 +29743,7 @@
       </c>
       <c r="L360" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M360" s="10" t="inlineStr">
@@ -27729,7 +29823,7 @@
       </c>
       <c r="L361" s="11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M361" s="11" t="inlineStr">
@@ -27809,7 +29903,7 @@
       <c r="K362" s="9" t="inlineStr"/>
       <c r="L362" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M362" s="10" t="inlineStr"/>
@@ -27873,7 +29967,7 @@
       <c r="K363" s="11" t="inlineStr"/>
       <c r="L363" s="11" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M363" s="11" t="inlineStr">
@@ -27953,7 +30047,7 @@
       <c r="K364" s="9" t="inlineStr"/>
       <c r="L364" s="9" t="inlineStr">
         <is>
-          <t>suffix-strip</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="M364" s="10" t="inlineStr">

--- a/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
+++ b/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruments" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -533,272 +533,262 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PROVENANCE</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated:      2026-10-08 11:01:50</t>
+          <t>NCIt identity for every SDTM CT instrument codelist (QS, FT, RS), with the two NCIt anchors</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Pipeline:       SDTM_CT_Extract → SDTM_Instrument_Identity_Enrich</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SDTM CT source: NCI EVS SDTM Terminology (versionless URL, re-run to update)</t>
+          <t>(instrument C20993, question container C211913). The instrument layer of Instrument_Findings.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>NCIt source:    Thesaurus.txt from Thesaurus.FLAT.zip (NCI EVS)</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>CUI source:     nci_code_cui_map.dat (NCI EVS, NCIm release schedule)</t>
+          <t>Instrument codelists from SDTM CT non-extensible Test Code codelists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>One row per codelist. 363 codelists across QS / FT / RS.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SCOPE</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sibling file at test-within-codelist grain: SDTM_Instrument_Test_Identity.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Instrument codelists from SDTM CT non-extensible Test Code codelists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>One row per codelist. 363 codelists across QS / FT / RS.</t>
+          <t>Join key between the two files: Codelist_TESTCD</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Sibling file at test-within-codelist grain: SDTM_Instrument_Test_Identity.xlsx</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SOURCE VERSIONS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Join key between the two files: Codelist_TESTCD</t>
+          <t>SDTM CT 2026-09-25 (pinned in Reference_Versions.json at the repo root; the NCI EVS file carries no version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Generated:      2026-10-29 20:54:09</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN DESCRIPTIONS</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline:       SDTM_CT_Extract → SDTM_Instrument_Identity_Enrich</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Codelist_TESTCD                 Primary key. Submission value of the Test Code codelist (e.g. ADCTC)</t>
+          <t>SDTM CT source: NCI EVS SDTM Terminology (versionless URL, re-run to update)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Codelist_NCIt_Code              NCIt concept code for the codelist itself (CDISC Terminology branch)</t>
+          <t>NCIt source:    Thesaurus.txt from Thesaurus.FLAT.zip (NCI EVS)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Instrument_Label                Display name minus " Test Code" suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Domain                          QS / FT / RS (or ?? for TAUG-origin codelists outside SDTMIG v3.4)</t>
+          <t>CUI source:     nci_code_cui_map.dat (NCI EVS, NCIm release schedule)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Question_Count                  Number of TESTCDs in the codelist</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN GAPS</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>1. Where no class category term exists, instrument identity (C20993) is name-based —</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Code            NCIt code for the instrument-as-tool (C20993 branch)</t>
+          <t xml:space="preserve">   fragile for versioned variants, respondent forms, and disease-specific modules.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Preferred_Term  Preferred term from NCIt FLAT</t>
+          <t xml:space="preserve">   See Instrument_Match_Method.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Synonyms        Pipe-separated synonyms (undifferentiated) from NCIt FLAT</t>
+          <t>2. C211913 containers spanning multiple codelists (1:many) are excluded.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Definition      Plain-language definition from NCIt FLAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Instrument_UMLS_CUI             Standard UMLS CUI (C + digits)</t>
+          <t>3. Codelists with Domain == ?? are TAUG-origin (outside SDTMIG v3.4 scope).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Instrument_NCIm_CUI             NCI Metathesaurus CUI (CL + digits)</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SHEETS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Instrument_Match_Method         Resolution path: class-category-term / exact / suffix-strip / normalized / normalized-item-strip / UNMATCHED</t>
+          <t>ReadMe        this sheet</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Container_NCIt_Code             NCIt code for the question container (C211913 branch)</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Instruments   one row per instrument codelist (see SCOPE and COLUMN DESCRIPTIONS)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Container_NCIt_Preferred_Term   Preferred term from NCIt FLAT</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN DESCRIPTIONS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Synonyms         Pipe-separated synonyms from NCIt FLAT</t>
+          <t>Codelist_TESTCD                 Primary key. Submission value of the Test Code codelist (e.g. ADCTC)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Definition       Plain-language definition from NCIt FLAT</t>
+          <t>Codelist_NCIt_Code              NCIt concept code for the codelist itself (CDISC Terminology branch)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Container_UMLS_CUI              Standard UMLS CUI</t>
+          <t>Instrument_Label                Display name minus " Test Code" suffix</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIm_CUI              NCI Metathesaurus CUI</t>
+          <t>Domain                          QS / FT / RS (or ?? for TAUG-origin codelists outside SDTMIG v3.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Question_Count                  Number of TESTCDs in the codelist</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE STATISTICS</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Total codelists:                 363</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Instrument_NCIt_Code            NCIt code for the instrument-as-tool (C20993 branch)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Instrument NCIt populated:       363 (100.0%)</t>
+          <t>Instrument_NCIt_Preferred_Term  Preferred term from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Container  NCIt populated:       359 (98.9%)</t>
+          <t>Instrument_NCIt_Synonyms        Pipe-separated synonyms (undifferentiated) from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Both populated:                  359 (98.9%)</t>
+          <t>Instrument_NCIt_Definition      Plain-language definition from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Neither populated:               0 (0.0%)</t>
+          <t>Instrument_UMLS_CUI             Standard UMLS CUI (C + digits)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Instrument UMLS CUI populated:   155 (42.7%)</t>
+          <t>Instrument_NCIm_CUI             NCI Metathesaurus CUI (CL + digits)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Container  UMLS CUI populated:   140 (38.6%)</t>
+          <t>Instrument_Match_Method         Resolution path: class-category-term / exact / suffix-strip / normalized / normalized-item-strip / UNMATCHED</t>
         </is>
       </c>
     </row>
@@ -806,235 +796,294 @@
       <c r="A46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Instrument match method:</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Container_NCIt_Code             NCIt code for the question container (C211913 branch)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  class-category-term:    362</t>
+          <t>Container_NCIt_Preferred_Term   Preferred term from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  exact:                    1</t>
+          <t>Container_NCIt_Synonyms         Pipe-separated synonyms from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  suffix-strip:             0</t>
+          <t>Container_NCIt_Definition       Plain-language definition from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized:               0</t>
+          <t>Container_UMLS_CUI              Standard UMLS CUI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized-item-strip:    0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  UNMATCHED:                0</t>
+          <t>Container_NCIm_CUI              NCI Metathesaurus CUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>COVERAGE STATISTICS</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>DESIGN DECISIONS</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Total codelists:                 363</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
+          <t>Instrument NCIt populated:       363 (100.0%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
+          <t>Container  NCIt populated:       359 (98.9%)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
+          <t>Both populated:                  359 (98.9%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>column separation names the gap rather than hiding it.</t>
+          <t>Neither populated:               0 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Instrument UMLS CUI populated:   155 (42.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Class category term first. SDTM CT QSCAT / FTCAT / CCCAT carry one term per instrument;</t>
+          <t>Container  UMLS CUI populated:   140 (38.6%)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>its CDISC synonym + "TC" is the codelist submission value and its code the instrument</t>
-        </is>
-      </c>
+      <c r="A62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>concept. Name matching is the fallback.</t>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Instrument match method:</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class-category-term:    362</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
+          <t xml:space="preserve">  exact:                    1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
+          <t xml:space="preserve">  suffix-strip:             0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>normalized match get UNMATCHED with empty Instrument_NCIt_* columns.</t>
+          <t xml:space="preserve">  normalized:               0</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  normalized-item-strip:    0</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>SDTM_Instrument_Test_Identity.xlsx, joinable via Codelist_TESTCD.</t>
+          <t xml:space="preserve">  UNMATCHED:                0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DESIGN DECISIONS</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>COLOR CONVENTION</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
+          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
+          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
+          <t>column separation names the gap rather than hiding it.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Yellow (#FFD700)          — COSMoS Dataset Specialization layer (consumer files)</t>
+          <t>Class category term first. SDTM CT QSCAT / FTCAT / CCCAT carry one term per instrument;</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>its CDISC synonym + "TC" is the codelist submission value and its code the instrument</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>KNOWN LIMITATIONS</t>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>concept. Name matching is the fallback.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>1. Where no class category term exists, instrument identity (C20993) is name-based —</t>
-        </is>
-      </c>
+      <c r="A80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fragile for versioned variants, respondent forms, and disease-specific modules.</t>
+          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   See Instrument_Match_Method.</t>
+          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2. C211913 containers spanning multiple codelists (1:many) are excluded.</t>
+          <t>normalized match get UNMATCHED with empty Instrument_NCIt_* columns.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>3. Codelists with Domain == ?? are TAUG-origin (outside SDTMIG v3.4 scope).</t>
+      <c r="A84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>SDTM_Instrument_Test_Identity.xlsx, joinable via Codelist_TESTCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>COLOR CONVENTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Yellow (#FFD700)          — COSMoS Dataset Specialization layer (consumer files)</t>
         </is>
       </c>
     </row>

--- a/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
+++ b/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
@@ -603,7 +603,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Generated:      2026-10-29 20:54:09</t>
+          <t>Generated:      2026-10-30 11:38:33</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Synonyms        Pipe-separated synonyms (undifferentiated) from NCIt FLAT</t>
+          <t>Instrument_NCIt_Synonyms        Synonyms (undifferentiated) from NCIt FLAT, separated by | as in the FLAT file</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Synonyms         Pipe-separated synonyms from NCIt FLAT</t>
+          <t>Container_NCIt_Synonyms         Synonyms from NCIt FLAT, separated by | as in the FLAT file</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>4 Stair Ascend | 4-STAIR ASCEND | A4STR1</t>
+          <t>4 Stair Ascend|4-STAIR ASCEND|A4STR1</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>ADAS-COG 30JUN2015 | ADAS-COG Date 30th June 2015 Version | ADC1</t>
+          <t>ADAS-COG 30JUN2015|ADAS-COG Date 30th June 2015 Version|ADC1</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>ADAS-COG | ADC</t>
+          <t>ADAS-COG|ADC</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>ADNI-AVLT | AVL01 | AVLT</t>
+          <t>ADNI-AVLT|AVL01|AVLT</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>AVL02 | AVLT-REY | AVLT-REY</t>
+          <t>AVL02|AVLT-REY|AVLT-REY</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>BACS | BACS | BACS1</t>
+          <t>BACS|BACS|BACS1</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>COWA | COWAT | COWAT | COWAT1 | Controlled Oral Word Association</t>
+          <t>COWA|COWAT|COWAT|COWAT1|Controlled Oral Word Association</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>4 Stair Descend | 4-STAIR DESCEND | D4STR1</t>
+          <t>4 Stair Descend|4-STAIR DESCEND|D4STR1</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>EMO1 | EMOTION RECOGNITION | ERT</t>
+          <t>EMO1|EMOTION RECOGNITION|ERT</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>HAI | HAI01 | HAUSER AMBULATION INDEX</t>
+          <t>HAI|HAI01|HAUSER AMBULATION INDEX</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>HD-CAB | HD-CAB | HDCAB1</t>
+          <t>HD-CAB|HD-CAB|HDCAB1</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Folstein Mini-Mental Status Exam | MMS1 | MMSE | MMSE | Mini-Mental State Examination Questionnaire</t>
+          <t>Folstein Mini-Mental Status Exam|MMS1|MMSE|MMSE|Mini-Mental State Examination Questionnaire</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>MMS2 | MMSE-2 STANDARD VERSION | MMSE-2 Standard Version</t>
+          <t>MMS2|MMSE-2 STANDARD VERSION|MMSE-2 Standard Version</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>NHPT | NHPT | NHPT01</t>
+          <t>NHPT|NHPT|NHPT01</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>PASAT | PASAT | PASAT1</t>
+          <t>PASAT|PASAT|PASAT1</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>PACED TAPPING | PTAP1 | Paced Tapping</t>
+          <t>PACED TAPPING|PTAP1|Paced Tapping</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>PUL 1.2 | PUL V1.2 | PUL01</t>
+          <t>PUL 1.2|PUL V1.2|PUL01</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>PUL 2.0 | PUL V2.0 | PUL02</t>
+          <t>PUL 2.0|PUL V2.0|PUL02</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>RISEF1; Stand From Supine | RISING FROM FLOOR | Rising From Floor</t>
+          <t>RISEF1; Stand From Supine|RISING FROM FLOOR|Rising From Floor</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>RFWT Version 1 | ROCK01 | ROCKPORT ONE MILE WALK TEST V1.0</t>
+          <t>RFWT Version 1|ROCK01|ROCKPORT ONE MILE WALK TEST V1.0</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>SDMT | SDMT | SDMT01</t>
+          <t>SDMT|SDMT|SDMT01</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>6 Minute Walk Functional Test | 6MWT | SIX MINUTE WALK | SIXMW1 | Six Minute Walk 2008</t>
+          <t>6 Minute Walk Functional Test|6MWT|SIX MINUTE WALK|SIXMW1|Six Minute Walk 2008</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>SPPB V1.2 | SPPB Version 1.2 | SPPB1</t>
+          <t>SPPB V1.2|SPPB Version 1.2|SPPB1</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>T25FW | T25FW | T25FW1</t>
+          <t>T25FW|T25FW|T25FW1</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>10 Meter Walk/Run | 10-METER WALK/RUN | TENMW1 | Ten Meter Walk/Run</t>
+          <t>10 Meter Walk/Run|10-METER WALK/RUN|TENMW1|Ten Meter Walk/Run</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>TMT | TMT | TMT01</t>
+          <t>TMT|TMT|TMT01</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>TUG | TUG | TUG01</t>
+          <t>TUG|TUG|TUG01</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>ADCS-ADL | ADCS-ADL | ADL01</t>
+          <t>ADCS-ADL|ADCS-ADL|ADL01</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ADCS-ADL SEVERE DEMENTIA | ADCS-ADL Severe Dementia | ADL02</t>
+          <t>ADCS-ADL SEVERE DEMENTIA|ADCS-ADL Severe Dementia|ADL02</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>ADCS-ADL MCI | ADCS-ADL MCI | ADL03</t>
+          <t>ADCS-ADL MCI|ADCS-ADL MCI|ADL03</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>ADSD V1.0 | ADSD Version 1.0 | ADSD01</t>
+          <t>ADSD V1.0|ADSD Version 1.0|ADSD01</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>ADT01 | AUDIT | AUDIT-SR</t>
+          <t>ADT01|AUDIT|AUDIT-SR</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>ADTC01 | AUDIT-C | AUDIT-C</t>
+          <t>ADTC01|AUDIT-C|AUDIT-C</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>ADTC02 | AUDIT-C Self-Report Version | MODIFIED AUDIT-C FROM WHO AUDIT: SELF-REPORT VERSION 2001</t>
+          <t>ADTC02|AUDIT-C Self-Report Version|MODIFIED AUDIT-C FROM WHO AUDIT: SELF-REPORT VERSION 2001</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADTC03 | AUDIT-C Interview Version | MODIFIED AUDIT-C FROM WHO AUDIT: INTERVIEW VERSION 2001</t>
+          <t>ADTC03|AUDIT-C Interview Version|MODIFIED AUDIT-C FROM WHO AUDIT: INTERVIEW VERSION 2001</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>ANSD V1.0 | ANSD Version 1.0 | ANSD01</t>
+          <t>ANSD V1.0|ANSD Version 1.0|ANSD01</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>AQ01 | AQ20 | AQ20</t>
+          <t>AQ01|AQ20|AQ20</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>ARCI-49 1971 | ARCI-49 Check-list | ARCI01</t>
+          <t>ARCI-49 1971|ARCI-49 Check-list|ARCI01</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>ASEX-FEMALE | ASEX-Female Version | ASEX01</t>
+          <t>ASEX-FEMALE|ASEX-Female Version|ASEX01</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>ASEX-MALE | ASEX-Male Version | ASEX02</t>
+          <t>ASEX-MALE|ASEX-Male Version|ASEX02</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>BCR101 | BORG CR10 | Borg CR10</t>
+          <t>BCR101|BORG CR10|Borg CR10</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>BEBQ CONCURRENT | BEBQ Concurrent Version | BEBQ01</t>
+          <t>BEBQ CONCURRENT|BEBQ Concurrent Version|BEBQ01</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>BEBQ RETROSPECTIVE | BEBQ Retrospective Version | BEBQ02</t>
+          <t>BEBQ RETROSPECTIVE|BEBQ Retrospective Version|BEBQ02</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>BLCS | BLCS | BLCS01</t>
+          <t>BLCS|BLCS|BLCS01</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>BPI | BPI1 | Brief Pain Inventory</t>
+          <t>BPI|BPI1|Brief Pain Inventory</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>BPI SHORT FORM | BPI2 | Brief Pain Inventory Short Form</t>
+          <t>BPI SHORT FORM|BPI2|Brief Pain Inventory Short Form</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>BWCS | BWCS | BWCS01</t>
+          <t>BWCS|BWCS|BWCS01</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>CCQ 24 HOUR VERSION | CCQ 24 Hour Version | CCQ01</t>
+          <t>CCQ 24 HOUR VERSION|CCQ 24 Hour Version|CCQ01</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>CCQ 1 WEEK VERSION | CCQ 1 Week Version | CCQ02</t>
+          <t>CCQ 1 WEEK VERSION|CCQ 1 Week Version|CCQ02</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>CDAI V1 | CDAI Version 1 | CDAI01</t>
+          <t>CDAI V1|CDAI Version 1|CDAI01</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>CES | CES | CES01</t>
+          <t>CES|CES|CES01</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>CHART-SF | CHART-SF INTERVIEW VERSION | CHSF1</t>
+          <t>CHART-SF|CHART-SF INTERVIEW VERSION|CHSF1</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>CHART-SF PAPER VERSION | CHART-SF Paper Version | CHSF2</t>
+          <t>CHART-SF PAPER VERSION|CHART-SF Paper Version|CHSF2</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>COMM | COMM1</t>
+          <t>COMM|COMM1</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>COWS | COWS | COWS1</t>
+          <t>COWS|COWS|COWS1</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>CRQ-SAS FIRST ADMINISTRATION VERSION | CRQ-SAS First Administration Version | CRQ01</t>
+          <t>CRQ-SAS FIRST ADMINISTRATION VERSION|CRQ-SAS First Administration Version|CRQ01</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>CRQ-SAS FOLLOW-UP ADMINISTRATION VERSION | CRQ-SAS Follow-Up Administration Version | CRQ02</t>
+          <t>CRQ-SAS FOLLOW-UP ADMINISTRATION VERSION|CRQ-SAS Follow-Up Administration Version|CRQ02</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS BASELINE | C-SSRS Baseline | CSS01</t>
+          <t>C-SSRS BASELINE|C-SSRS Baseline|CSS01</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>C-SSRS SINCE LAST VISIT | C-SSRS Since Last Visit | CSS02</t>
+          <t>C-SSRS SINCE LAST VISIT|C-SSRS Since Last Visit|CSS02</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS BASELINE/SCREENING VERSION PHASE 1 STUDY | C-SSRS Baseline/Screening Version Phase 1 Study 1/14/09 | CSS03</t>
+          <t>C-SSRS BASELINE/SCREENING VERSION PHASE 1 STUDY|C-SSRS Baseline/Screening Version Phase 1 Study 1/14/09|CSS03</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>C-SSRS BASELINE/SCREENING VERSION | C-SSRS Baseline/Screening Version | CSS04</t>
+          <t>C-SSRS BASELINE/SCREENING VERSION|C-SSRS Baseline/Screening Version|CSS04</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS ALREADY ENROLLED SUBJECTS | C-SSRS Already Enrolled Subjects | CSS05</t>
+          <t>C-SSRS ALREADY ENROLLED SUBJECTS|C-SSRS Already Enrolled Subjects|CSS05</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>C-SSRS CHILDREN'S BASELINE | C-SSRS Children's Baseline | CSS06</t>
+          <t>C-SSRS CHILDREN'S BASELINE|C-SSRS Children's Baseline|CSS06</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS CHILDREN'S BASELINE/SCREENING | C-SSRS Children's Baseline/Screening | CSS07</t>
+          <t>C-SSRS CHILDREN'S BASELINE/SCREENING|C-SSRS Children's Baseline/Screening|CSS07</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>C-SSRS CHILDREN'S SINCE LAST VISIT | C-SSRS Children's Since Last Visit | CSS08</t>
+          <t>C-SSRS CHILDREN'S SINCE LAST VISIT|C-SSRS Children's Since Last Visit|CSS08</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS SCREENING | C-SSRS Screening | CSS09</t>
+          <t>C-SSRS SCREENING|C-SSRS Screening|CSS09</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>C-SSRS PEDIATRIC/COGNITIVELY IMPAIRED LIFETIME/RECENT | C-SSRS Pediatric/Cognitively Impaired Lifetime/Recent | CSS10</t>
+          <t>C-SSRS PEDIATRIC/COGNITIVELY IMPAIRED LIFETIME/RECENT|C-SSRS Pediatric/Cognitively Impaired Lifetime/Recent|CSS10</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>C-SSRS LIFETIME/RECENT VERSION | C-SSRS Lifetime/Recent Version | CSS11</t>
+          <t>C-SSRS LIFETIME/RECENT VERSION|C-SSRS Lifetime/Recent Version|CSS11</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>DAD | DAD | DAD01</t>
+          <t>DAD|DAD|DAD01</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>DDS01 | T1-DDS | T1-DDS</t>
+          <t>DDS01|T1-DDS|T1-DDS</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>DDS02 | PARENT-DDS | PARENT-DDS</t>
+          <t>DDS02|PARENT-DDS|PARENT-DDS</t>
         </is>
       </c>
       <c r="I72" s="9" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>DDS03 | PARTNER-DDS | PARTNER-DDS</t>
+          <t>DDS03|PARTNER-DDS|PARTNER-DDS</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>DIBC01 | DIBSS-C V1.0 | DIBSS-C Version 1.0</t>
+          <t>DIBC01|DIBSS-C V1.0|DIBSS-C Version 1.0</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>DLQI | DLQI | DLQI1</t>
+          <t>DLQI|DLQI|DLQI1</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>DRRI-2 | DRRI-2 | DRRI1</t>
+          <t>DRRI-2|DRRI-2|DRRI1</t>
         </is>
       </c>
       <c r="I76" s="9" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>DSQ-PEM 2018 | DSQ-PEM 2018 | DSQ1</t>
+          <t>DSQ-PEM 2018|DSQ-PEM 2018|DSQ1</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>ED1 | EXPANDED DRS-PI CAREGIVER VERSION | Expanded DRS-PI Caregiver Version</t>
+          <t>ED1|EXPANDED DRS-PI CAREGIVER VERSION|Expanded DRS-PI Caregiver Version</t>
         </is>
       </c>
       <c r="I78" s="9" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>ED2 | EXPANDED DRS-PI SURVIVOR VERSION | Expanded DRS-PI Survivor Version</t>
+          <t>ED2|EXPANDED DRS-PI SURVIVOR VERSION|Expanded DRS-PI Survivor Version</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>EOR01 | EORTC QLQ-C30 V3.0 | EORTC QLQ-C30 Version 3</t>
+          <t>EOR01|EORTC QLQ-C30 V3.0|EORTC QLQ-C30 Version 3</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>EOR02 | EORTC QLQ-C15-PAL V1.0 | EORTC QLQ-C15-PAL Version 1</t>
+          <t>EOR02|EORTC QLQ-C15-PAL V1.0|EORTC QLQ-C15-PAL Version 1</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>EOR03 | EORTC QLQ-BM22 | EORTC QLQ-BM22</t>
+          <t>EOR03|EORTC QLQ-BM22|EORTC QLQ-BM22</t>
         </is>
       </c>
       <c r="I82" s="9" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>EOR06 | EORTC QLQ-CR29 V2.1 | EORTC QLQ-CR29 Version 2.1</t>
+          <t>EOR06|EORTC QLQ-CR29 V2.1|EORTC QLQ-CR29 Version 2.1</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>EOR11 | EORTC QLQ-H and N35 Version 1 | EORTC QLQ-H&amp;N35 V1</t>
+          <t>EOR11|EORTC QLQ-H and N35 Version 1|EORTC QLQ-H&amp;N35 V1</t>
         </is>
       </c>
       <c r="I84" s="9" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>EOR12 | EORTC QLQ-LMC21 | EORTC QLQ-LMC21</t>
+          <t>EOR12|EORTC QLQ-LMC21|EORTC QLQ-LMC21</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>EOR17 | EORTC QLQ-INFO25 | EORTC QLQ-INFO25</t>
+          <t>EOR17|EORTC QLQ-INFO25|EORTC QLQ-INFO25</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>EOR18 | EORTC QLQ Lung Cancer Module | EORTC QLQ-LC13 | EORTC QLQ-LC13 | EORTC Study Group on Quality of Life 13-item Lung Cancer-Specific Questionnaire | European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Lung Cancer Module</t>
+          <t>EOR18|EORTC QLQ Lung Cancer Module|EORTC QLQ-LC13|EORTC QLQ-LC13|EORTC Study Group on Quality of Life 13-item Lung Cancer-Specific Questionnaire|European Organization for the Research and Treatment of Cancer Quality of Life Questionnaire - Lung Cancer Module</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>EOR19 | EORTC Multiple Myeloma Module | EORTC Multiple Myeloma Module (QLQ-MY20) | EORTC QLQ-MY20 | EORTC QLQ-MY20 | QLQ-MY20</t>
+          <t>EOR19|EORTC Multiple Myeloma Module|EORTC Multiple Myeloma Module (QLQ-MY20)|EORTC QLQ-MY20|EORTC QLQ-MY20|QLQ-MY20</t>
         </is>
       </c>
       <c r="I88" s="9" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>EOR20 | EORTC QLQ-OES18 | EORTC QLQ-OES18</t>
+          <t>EOR20|EORTC QLQ-OES18|EORTC QLQ-OES18</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>EOR21 | EORTC QLQ-OG25 PHASE IV MODULE | EORTC QLQ-OG25 Phase IV Module Version</t>
+          <t>EOR21|EORTC QLQ-OG25 PHASE IV MODULE|EORTC QLQ-OG25 Phase IV Module Version</t>
         </is>
       </c>
       <c r="I90" s="9" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>EOR24 | EORTC QLQ-BIL21 | EORTC QLQ-BIL21</t>
+          <t>EOR24|EORTC QLQ-BIL21|EORTC QLQ-BIL21</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>CIPN20 Questionnaire | EOR25 | EORTC QLQ-CIPN20 | EORTC QLQ-CIPN20</t>
+          <t>CIPN20 Questionnaire|EOR25|EORTC QLQ-CIPN20|EORTC QLQ-CIPN20</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>EOR28 | EORTC QLQ-NMIBC24 | EORTC QLQ-NMIBC24</t>
+          <t>EOR28|EORTC QLQ-NMIBC24|EORTC QLQ-NMIBC24</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>EOR29 | EORTC QLQ-CLL17 | EORTC QLQ-CLL17</t>
+          <t>EOR29|EORTC QLQ-CLL17|EORTC QLQ-CLL17</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>EOR30 | EORTC QLQ-ANL27 | EORTC QLQ-ANL27</t>
+          <t>EOR30|EORTC QLQ-ANL27|EORTC QLQ-ANL27</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>EOR35 | EORTC QLQ-BR42 | EORTC QLQ-BR42</t>
+          <t>EOR35|EORTC QLQ-BR42|EORTC QLQ-BR42</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>EOR36 | EORTC QLQ-H and N43 Phase IV Module Version | EORTC QLQ-H&amp;N43 PHASE IV MODULE</t>
+          <t>EOR36|EORTC QLQ-H and N43 Phase IV Module Version|EORTC QLQ-H&amp;N43 PHASE IV MODULE</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>EPDS | EPDS | EPDS01</t>
+          <t>EPDS|EPDS|EPDS01</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>EPIC-26 | EPIC-26 | EPIC-26 (Priority 1) | EPIC1</t>
+          <t>EPIC-26|EPIC-26|EPIC-26 (Priority 1)|EPIC1</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>EPIC-CP | EPIC-CP | EPIC2</t>
+          <t>EPIC-CP|EPIC-CP|EPIC2</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>EQ-5D-3L | EQ-5D-3L | EQ-5D-3L | EQ5D01 | European Quality of Life Five Dimension Three Level Scale Questionnaire</t>
+          <t>EQ-5D-3L|EQ-5D-3L|EQ-5D-3L|EQ5D01|European Quality of Life Five Dimension Three Level Scale Questionnaire</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>EQ-5D-5L | EQ-5D-5L | EQ-5D-5L | EQ5D02</t>
+          <t>EQ-5D-5L|EQ-5D-5L|EQ-5D-5L|EQ5D02</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>ESS | ESS | ESS01 | Epworth Sleepiness Scale</t>
+          <t>ESS|ESS|ESS01|Epworth Sleepiness Scale</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>EXACT | EXACT | EXACT1</t>
+          <t>EXACT|EXACT|EXACT1</t>
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>FAC001 | FACT-G V4 | FACT-G Version 4</t>
+          <t>FAC001|FACT-G V4|FACT-G Version 4</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>FAC005 | FACT-B V4 | FACT-B Version 4</t>
+          <t>FAC005|FACT-B V4|FACT-B Version 4</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>FAC006 | FACT-BL V4 | FACT-BL Version 4</t>
+          <t>FAC006|FACT-BL V4|FACT-BL Version 4</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>FAC008 | FACT-C V4 | FACT-C Version 4</t>
+          <t>FAC008|FACT-C V4|FACT-C Version 4</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>FAC015 | FACT-HEP V4 | FACT-HEP Version 4</t>
+          <t>FAC015|FACT-HEP V4|FACT-HEP Version 4</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>FAC016 | FACT-L V4 | FACT-L Version 4</t>
+          <t>FAC016|FACT-L V4|FACT-L Version 4</t>
         </is>
       </c>
       <c r="I110" s="9" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>FAC017 | FACT-LEU V4 | FACT-LEU Version 4</t>
+          <t>FAC017|FACT-LEU V4|FACT-LEU Version 4</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>FAC018 | FACT-LYM V4 | FACT-LYM Version 4</t>
+          <t>FAC018|FACT-LYM V4|FACT-LYM Version 4</t>
         </is>
       </c>
       <c r="I112" s="9" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>FAC019 | FACT-M V4 | FACT-M Version 4</t>
+          <t>FAC019|FACT-M V4|FACT-M Version 4</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>FAC023 | FACT-P V4 | FACT-P Version 4</t>
+          <t>FAC023|FACT-P V4|FACT-P Version 4</t>
         </is>
       </c>
       <c r="I114" s="9" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>FAC028 | NCCN-FACT FBLSI-18 V2 | NCCN-FACT FBLSI-18 Version 2</t>
+          <t>FAC028|NCCN-FACT FBLSI-18 V2|NCCN-FACT FBLSI-18 Version 2</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>FAC029 | FBRSI | FBRSI</t>
+          <t>FAC029|FBRSI|FBRSI</t>
         </is>
       </c>
       <c r="I116" s="9" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>FAC030 | NCCN-FACT FBRSI-24 V2 | NCCN-FACT FBRSI-24 Version 2</t>
+          <t>FAC030|NCCN-FACT FBRSI-24 V2|NCCN-FACT FBRSI-24 Version 2</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>FAC032 | NFBSI-16 V2 | NFBSI-16 Version 2</t>
+          <t>FAC032|NFBSI-16 V2|NFBSI-16 Version 2</t>
         </is>
       </c>
       <c r="I118" s="9" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>FAC036 | NCCN-FACT FHNSI-22 V2 | NCCN-FACT FHNSI-22 Version 2</t>
+          <t>FAC036|NCCN-FACT FHNSI-22 V2|NCCN-FACT FHNSI-22 Version 2</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>FAC039 | FKSI-15 | FKSI-15 | Functional Assessment for Cancer Therapy-Kidney Symptom Index</t>
+          <t>FAC039|FKSI-15|FKSI-15|Functional Assessment for Cancer Therapy-Kidney Symptom Index</t>
         </is>
       </c>
       <c r="I120" s="9" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>FAC041 | FKSI-DRS V4 | FKSI-DRS Version 4</t>
+          <t>FAC041|FKSI-DRS V4|FKSI-DRS Version 4</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>FAC042 | NCCN-FACT FKSI-19 V2 | NCCN-FACT FKSI-19 Version 2</t>
+          <t>FAC042|NCCN-FACT FKSI-19 V2|NCCN-FACT FKSI-19 Version 2</t>
         </is>
       </c>
       <c r="I122" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>FAC043 | FLSI | FLSI</t>
+          <t>FAC043|FLSI|FLSI</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>FAC049 | FOSI | FOSI</t>
+          <t>FAC049|FOSI|FOSI</t>
         </is>
       </c>
       <c r="I124" s="9" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>FAC050 | NCCN-FACT FOSI-18 V2 | NCCN-FACT FOSI-18 Version 2</t>
+          <t>FAC050|NCCN-FACT FOSI-18 V2|NCCN-FACT FOSI-18 Version 2</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>FAC052 | NCCN-FACT FPSI-17 V2 | NCCN-FACT-FPSI 17 Version 2</t>
+          <t>FAC052|NCCN-FACT FPSI-17 V2|NCCN-FACT-FPSI 17 Version 2</t>
         </is>
       </c>
       <c r="I126" s="9" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>FAC057 | FACT/GOG-NTX V4 | FACT/GOG-NTX Version 4</t>
+          <t>FAC057|FACT/GOG-NTX V4|FACT/GOG-NTX Version 4</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>FAC061 | FACT-BMT V4 | FACT-BMT Version 4</t>
+          <t>FAC061|FACT-BMT V4|FACT-BMT Version 4</t>
         </is>
       </c>
       <c r="I128" s="9" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>FAC062 | FACT-BRM V4 | FACT-BRM Version 4</t>
+          <t>FAC062|FACT-BRM V4|FACT-BRM Version 4</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>FAC063 | FACT-TAXANE V4 | FACT-Taxane Version 4</t>
+          <t>FAC063|FACT-TAXANE V4|FACT-Taxane Version 4</t>
         </is>
       </c>
       <c r="I130" s="9" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>FAACT V4 | FAACT Version 4 | FAC065</t>
+          <t>FAACT V4|FAACT Version 4|FAC065</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>FAC070 | FACIT-FATIGUE 13-ITEM V4 | FACIT-Fatigue 13-Item Version 4</t>
+          <t>FAC070|FACIT-FATIGUE 13-ITEM V4|FACIT-Fatigue 13-Item Version 4</t>
         </is>
       </c>
       <c r="I132" s="9" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>FAC071 | FACIT-F V4 | FACIT-F Version 4</t>
+          <t>FAC071|FACIT-F V4|FACIT-F Version 4</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>FAC074 | FACT-BP V4 | FACT-BP Version 4</t>
+          <t>FAC074|FACT-BP V4|FACT-BP Version 4</t>
         </is>
       </c>
       <c r="I134" s="9" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>FAC075 | FACT-COG | FACT-COG V3 | FACT-COG Version 3 | FACT-Cognitive Function v3 | Functional Assessment of Cancer Therapy-Cognitive Function Version 3</t>
+          <t>FAC075|FACT-COG|FACT-COG V3|FACT-COG Version 3|FACT-Cognitive Function v3|Functional Assessment of Cancer Therapy-Cognitive Function Version 3</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>FAC084 | FACIT-DYSPNEA SF | FACIT-Dyspnea | Functional Assessment of Chronic Illness Therapy-Dyspnea | Functional Assessment of Chronic Illness Therapy-Dyspnea 10 Item Short Form Questionnaire</t>
+          <t>FAC084|FACIT-DYSPNEA SF|FACIT-Dyspnea|Functional Assessment of Chronic Illness Therapy-Dyspnea|Functional Assessment of Chronic Illness Therapy-Dyspnea 10 Item Short Form Questionnaire</t>
         </is>
       </c>
       <c r="I136" s="9" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>FAC099 | PEDS-FACIT-F | Peds-FACIT-F</t>
+          <t>FAC099|PEDS-FACIT-F|Peds-FACIT-F</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>FAC100 | FACIT-DYSPNEA 33 ITEM BANK | FACIT-Dyspnea Scale 33 Item Bank Version</t>
+          <t>FAC100|FACIT-DYSPNEA 33 ITEM BANK|FACIT-Dyspnea Scale 33 Item Bank Version</t>
         </is>
       </c>
       <c r="I138" s="9" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>FAC101 | FACIT-ITEM GP5 V4 | FACIT-Item GP5 Version 4</t>
+          <t>FAC101|FACIT-ITEM GP5 V4|FACIT-Item GP5 Version 4</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>FAC102 | FACT/GOG-NTX SUBSCALE V4 | FACT/GOG-NTX Subscale Version 4</t>
+          <t>FAC102|FACT/GOG-NTX SUBSCALE V4|FACT/GOG-NTX Subscale Version 4</t>
         </is>
       </c>
       <c r="I140" s="9" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>FAC104 | FACT-ICM V4 | FACT-ICM Version 4</t>
+          <t>FAC104|FACT-ICM V4|FACT-ICM Version 4</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>FAMS | FAMS | FAMS | FAMS Questionnaire | FAMS01</t>
+          <t>FAMS|FAMS|FAMS|FAMS Questionnaire|FAMS01</t>
         </is>
       </c>
       <c r="I142" s="9" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>FES | FES | FES01</t>
+          <t>FES|FES|FES01</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>FIQR | FIQR | FIQR01</t>
+          <t>FIQR|FIQR|FIQR01</t>
         </is>
       </c>
       <c r="I144" s="9" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>FPSR | FPSR1</t>
+          <t>FPSR|FPSR1</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>FACIT-SEARCHABLE ITEM LIBRARY ADULT | FACIT-Searchable Item Library Adult Version | FSIL</t>
+          <t>FACIT-SEARCHABLE ITEM LIBRARY ADULT|FACIT-Searchable Item Library Adult Version|FSIL</t>
         </is>
       </c>
       <c r="I146" s="9" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>FACIT-SEARCHABLE ITEM LIBRARY PEDIATRIC | FACIT-Searchable Item Library Pediatric Version | FSLP</t>
+          <t>FACIT-SEARCHABLE ITEM LIBRARY PEDIATRIC|FACIT-Searchable Item Library Pediatric Version|FSLP</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>FSS | FSS | FSS01</t>
+          <t>FSS|FSS|FSS01</t>
         </is>
       </c>
       <c r="I148" s="9" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>FTCD | FTCD | FTCD01</t>
+          <t>FTCD|FTCD|FTCD01</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>GAD-7 | GAD-7 | GAD01 | General Anxiety Disorder-7 | General Anxiety Disorder-7 Questionnaire | Generalized Anxiety Disorder 7-item Scale (GAD-7)</t>
+          <t>GAD-7|GAD-7|GAD01|General Anxiety Disorder-7|General Anxiety Disorder-7 Questionnaire|Generalized Anxiety Disorder 7-item Scale (GAD-7)</t>
         </is>
       </c>
       <c r="I150" s="9" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>GAD-7 V2 | GAD-7 Version 2 | GAD02</t>
+          <t>GAD-7 V2|GAD-7 Version 2|GAD02</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>GDS | GDS | GDS01</t>
+          <t>GDS|GDS|GDS01</t>
         </is>
       </c>
       <c r="I152" s="9" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>GDS SHORT FORM | GDS-SF | GDS02</t>
+          <t>GDS SHORT FORM|GDS-SF|GDS02</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>GMSS VERSION TYPE 1 DIABETES | GMSS Version Type 1 Diabetes | GMSS01</t>
+          <t>GMSS VERSION TYPE 1 DIABETES|GMSS Version Type 1 Diabetes|GMSS01</t>
         </is>
       </c>
       <c r="I154" s="9" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>GOS-E | GOSE | GOSE | GOSE1 | Glasgow Outcome Scale (Extended)</t>
+          <t>GOS-E|GOSE|GOSE|GOSE1|Glasgow Outcome Scale (Extended)</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>GENERAL SELF-EFFICACY SCALE 1995 | GSE 1995 | GSE01</t>
+          <t>GENERAL SELF-EFFICACY SCALE 1995|GSE 1995|GSE01</t>
         </is>
       </c>
       <c r="I156" s="9" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>HADS | HADS | HADS Questionnaire | HADS01 | Hospital Anxiety and Depression Scale Questionnaire (HADS)</t>
+          <t>HADS|HADS|HADS Questionnaire|HADS01|Hospital Anxiety and Depression Scale Questionnaire (HADS)</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>HAM-D6 Self-Report Version | HAMD 6 SELF-REPORT VERSION | HAMDS1</t>
+          <t>HAM-D6 Self-Report Version|HAMD 6 SELF-REPORT VERSION|HAMDS1</t>
         </is>
       </c>
       <c r="I158" s="9" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>HAQ-DI WITH VAS | HAQ-DI With VAS | HAQ01</t>
+          <t>HAQ-DI WITH VAS|HAQ-DI With VAS|HAQ01</t>
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>HAQ-DI WITHOUT VAS | HAQ-DI Without VAS | HAQ02</t>
+          <t>HAQ-DI WITHOUT VAS|HAQ-DI Without VAS|HAQ02</t>
         </is>
       </c>
       <c r="I160" s="9" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>HCS | HCS | HCS01</t>
+          <t>HCS|HCS|HCS01</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>IBDQ | IBDQ | IBDQ01</t>
+          <t>IBDQ|IBDQ|IBDQ01</t>
         </is>
       </c>
       <c r="I162" s="9" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>IDS-SR | IDS-SR | IDSR1</t>
+          <t>IDS-SR|IDS-SR|IDSR1</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>IIEF | IIEF | IIEF01</t>
+          <t>IIEF|IIEF|IIEF01</t>
         </is>
       </c>
       <c r="I164" s="9" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>IPAQ Short Last 7 Days Telephone Format Version | IPAQ-SF PHONE VERSION | IPAQ01</t>
+          <t>IPAQ Short Last 7 Days Telephone Format Version|IPAQ-SF PHONE VERSION|IPAQ01</t>
         </is>
       </c>
       <c r="I165" s="11" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>IPAQ Long Last 7 Days Telephone Format Version | IPAQ-LF PHONE VERSION | IPAQ02</t>
+          <t>IPAQ Long Last 7 Days Telephone Format Version|IPAQ-LF PHONE VERSION|IPAQ02</t>
         </is>
       </c>
       <c r="I166" s="9" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>IPAQ Long Last 7 Days Self-Administered Format Version | IPAQ-LF SELF-ADMINISTERED VERSION | IPAQ03</t>
+          <t>IPAQ Long Last 7 Days Self-Administered Format Version|IPAQ-LF SELF-ADMINISTERED VERSION|IPAQ03</t>
         </is>
       </c>
       <c r="I167" s="11" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
-          <t>IPAQ Short Last 7 Days Self-administered Format Version | IPAQ-SF SELF-ADMINISTERED VERSION | IPAQ04</t>
+          <t>IPAQ Short Last 7 Days Self-administered Format Version|IPAQ-SF SELF-ADMINISTERED VERSION|IPAQ04</t>
         </is>
       </c>
       <c r="I168" s="9" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>I-PSS | I-PSS | IPS01 | IPSS</t>
+          <t>I-PSS|I-PSS|IPS01|IPSS</t>
         </is>
       </c>
       <c r="I169" s="11" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>IVIS | IVIS | IVIS01</t>
+          <t>IVIS|IVIS|IVIS01</t>
         </is>
       </c>
       <c r="I170" s="9" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>KDQ1 | KDQOL-36 V1 | KDQOL-36 Version 1</t>
+          <t>KDQ1|KDQOL-36 V1|KDQOL-36 Version 1</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>LEC-5 STANDARD VERSION | LEC-5 Standard Version | LEC01</t>
+          <t>LEC-5 STANDARD VERSION|LEC-5 Standard Version|LEC01</t>
         </is>
       </c>
       <c r="I172" s="9" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>LPPS SCALE | LPPSS1 | LPSS | PPSC | Play-Performance Status Scale</t>
+          <t>LPPS SCALE|LPPSS1|LPSS|PPSC|Play-Performance Status Scale</t>
         </is>
       </c>
       <c r="I173" s="11" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
-          <t>MCEQ | MCEQ | MCEQ01</t>
+          <t>MCEQ|MCEQ|MCEQ01</t>
         </is>
       </c>
       <c r="I174" s="9" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>MFIS | MFIS | MFIS01</t>
+          <t>MFIS|MFIS|MFIS01</t>
         </is>
       </c>
       <c r="I175" s="11" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>MHIS-NACC | MHIS-NACC | MHIS01</t>
+          <t>MHIS-NACC|MHIS-NACC|MHIS01</t>
         </is>
       </c>
       <c r="I176" s="9" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>MMRC | MMRC | MMRC01</t>
+          <t>MMRC|MMRC|MMRC01</t>
         </is>
       </c>
       <c r="I177" s="11" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
-          <t>MNSI | MNSI1</t>
+          <t>MNSI|MNSI1</t>
         </is>
       </c>
       <c r="I178" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>MPAI-4 | MPAI-4 | MPAI1</t>
+          <t>MPAI-4|MPAI-4|MPAI1</t>
         </is>
       </c>
       <c r="I179" s="11" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>MSQL1 | MSQOL-54 | MSQOL-54</t>
+          <t>MSQL1|MSQOL-54|MSQOL-54</t>
         </is>
       </c>
       <c r="I180" s="9" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>MTWS-R | MTWS-Revised Version | MTWSR1</t>
+          <t>MTWS-R|MTWS-Revised Version|MTWSR1</t>
         </is>
       </c>
       <c r="I181" s="11" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
-          <t>NPI | NPI-12 | NPI-Q | NPI1 | Neuropsychiatric Inventory-Questionnaire</t>
+          <t>NPI|NPI-12|NPI-Q|NPI1|Neuropsychiatric Inventory-Questionnaire</t>
         </is>
       </c>
       <c r="I182" s="9" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>NPS | NPS | NPS01</t>
+          <t>NPS|NPS|NPS01</t>
         </is>
       </c>
       <c r="I183" s="11" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
-          <t>NSCLC-SAQ V1.0 | NSCLC-SAQ Version 1.0 | NSCLC1</t>
+          <t>NSCLC-SAQ V1.0|NSCLC-SAQ Version 1.0|NSCLC1</t>
         </is>
       </c>
       <c r="I184" s="9" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>NY1 | NYTS 2022 | NYTS 2022 Version</t>
+          <t>NY1|NYTS 2022|NYTS 2022 Version</t>
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>OAB-Q | OAB-q | OABQ01</t>
+          <t>OAB-Q|OAB-q|OABQ01</t>
         </is>
       </c>
       <c r="I186" s="9" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>OAB-Q SHORT FORM | OAB-q Short Form | OABQ02</t>
+          <t>OAB-Q SHORT FORM|OAB-q Short Form|OABQ02</t>
         </is>
       </c>
       <c r="I187" s="11" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
-          <t>ODI V2.1A | ODI v2.1a | ODI01</t>
+          <t>ODI V2.1A|ODI v2.1a|ODI01</t>
         </is>
       </c>
       <c r="I188" s="9" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>OGI | OGI Generic Modification Version | OGI01</t>
+          <t>OGI|OGI Generic Modification Version|OGI01</t>
         </is>
       </c>
       <c r="I189" s="11" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>PA016 | PROMIS IB V2.0 COGNITIVE FUNCTION SF 6A | PROMIS IB Version 2.0 Cognitive Function SF 6a</t>
+          <t>PA016|PROMIS IB V2.0 COGNITIVE FUNCTION SF 6A|PROMIS IB Version 2.0 Cognitive Function SF 6a</t>
         </is>
       </c>
       <c r="I190" s="9" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>PA020 | PROMIS IB V2.0 COGNITIVE FUNCTION ABILITIES SF 6A | PROMIS IB Version 2.0 Cognitive Function Abilities Subset SF 6a</t>
+          <t>PA020|PROMIS IB V2.0 COGNITIVE FUNCTION ABILITIES SF 6A|PROMIS IB Version 2.0 Cognitive Function Abilities Subset SF 6a</t>
         </is>
       </c>
       <c r="I191" s="11" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
-          <t>PA136 | PROMIS IB V1.0 FATIGUE SF 7A | PROMIS IB Version 1.0 Fatigue SF 7a</t>
+          <t>PA136|PROMIS IB V1.0 FATIGUE SF 7A|PROMIS IB Version 1.0 Fatigue SF 7a</t>
         </is>
       </c>
       <c r="I192" s="9" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>PA215 | PROMIS IB V1.0 SLEEP DISTURBANCE SF 4A | PROMIS IB Version 1.0 Sleep Disturbance SF 4a</t>
+          <t>PA215|PROMIS IB V1.0 SLEEP DISTURBANCE SF 4A|PROMIS IB Version 1.0 Sleep Disturbance SF 4a</t>
         </is>
       </c>
       <c r="I193" s="11" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>PA261 | PROMIS-29 PROFILE V2.1 | PROMIS-29 Profile Version 2.1</t>
+          <t>PA261|PROMIS-29 PROFILE V2.1|PROMIS-29 Profile Version 2.1</t>
         </is>
       </c>
       <c r="I194" s="9" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>PCL-5 | PCL-5 | PCL01</t>
+          <t>PCL-5|PCL-5|PCL01</t>
         </is>
       </c>
       <c r="I195" s="11" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
-          <t>PDAI | PDAI | PDAI01</t>
+          <t>PDAI|PDAI|PDAI01</t>
         </is>
       </c>
       <c r="I196" s="9" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>PDDS | PDDS | PDDS01</t>
+          <t>PDDS|PDDS|PDDS01</t>
         </is>
       </c>
       <c r="I197" s="11" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>PGI | PGI Generic Modification Version | PGI01</t>
+          <t>PGI|PGI Generic Modification Version|PGI01</t>
         </is>
       </c>
       <c r="I198" s="9" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>PHQ-9 | PHQ-9 | PHQ01 | Patient Health Questionnaire (PHQ-9) | Patient Health Questionnaire-9</t>
+          <t>PHQ-9|PHQ-9|PHQ01|Patient Health Questionnaire (PHQ-9)|Patient Health Questionnaire-9</t>
         </is>
       </c>
       <c r="I199" s="11" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>PHQ-15 | PHQ-15 | PHQ02</t>
+          <t>PHQ-15|PHQ-15|PHQ02</t>
         </is>
       </c>
       <c r="I200" s="9" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H201" s="11" t="inlineStr">
         <is>
-          <t>PHQ SCREENER VERSION | PHQ Screener Version | PHQ03</t>
+          <t>PHQ SCREENER VERSION|PHQ Screener Version|PHQ03</t>
         </is>
       </c>
       <c r="I201" s="11" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>PHQ-2 | PHQ-2 | PHQ04 | Patient Health Questionnaire (PHQ-2) | Patient Health Questionnaire-2 (PHQ-2) | Patient Health Questionnaire-2 Item</t>
+          <t>PHQ-2|PHQ-2|PHQ04|Patient Health Questionnaire (PHQ-2)|Patient Health Questionnaire-2 (PHQ-2)|Patient Health Questionnaire-2 Item</t>
         </is>
       </c>
       <c r="I202" s="9" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>PHQ-8 | PHQ-8 | PHQ05</t>
+          <t>PHQ-8|PHQ-8|PHQ05</t>
         </is>
       </c>
       <c r="I203" s="11" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>PI | PI | PI01</t>
+          <t>PI|PI|PI01</t>
         </is>
       </c>
       <c r="I204" s="9" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>PODCI - PEDIATRIC PARENT REPORTED | PODCI Pediatric Parent-Reported Version | PODCI1</t>
+          <t>PODCI - PEDIATRIC PARENT REPORTED|PODCI Pediatric Parent-Reported Version|PODCI1</t>
         </is>
       </c>
       <c r="I205" s="11" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
-          <t>PODCI - ADOLESCENT PARENT REPORTED | PODCI Adolescent Parent-Reported Version | PODCI2</t>
+          <t>PODCI - ADOLESCENT PARENT REPORTED|PODCI Adolescent Parent-Reported Version|PODCI2</t>
         </is>
       </c>
       <c r="I206" s="9" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>PODCI - ADOLESCENT SELF REPORTED | PODCI Adolescent Self-Reported Version | PODCI3</t>
+          <t>PODCI - ADOLESCENT SELF REPORTED|PODCI Adolescent Self-Reported Version|PODCI3</t>
         </is>
       </c>
       <c r="I207" s="11" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT | PQL01 | PedsQL Neuromuscular Module Version 3.0 Young Adult Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT|PQL01|PedsQL Neuromuscular Module Version 3.0 Young Adult Report</t>
         </is>
       </c>
       <c r="I208" s="9" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT PARENT REPORT | PQL02 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Adults Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG ADULT PARENT REPORT|PQL02|PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Adults Report</t>
         </is>
       </c>
       <c r="I209" s="11" t="inlineStr">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN | PQL03 | PedsQL Neuromuscular Module Version 3.0 Teen Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN|PQL03|PedsQL Neuromuscular Module Version 3.0 Teen Report</t>
         </is>
       </c>
       <c r="I210" s="9" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN PARENT REPORT | PQL04 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Teen</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TEEN PARENT REPORT|PQL04|PedsQL Neuromuscular Module Version 3.0 Parent Report for Teen</t>
         </is>
       </c>
       <c r="I211" s="11" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD | PQL05 | PedsQL Neuromuscular Module Version 3.0 Child Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD|PQL05|PedsQL Neuromuscular Module Version 3.0 Child Report</t>
         </is>
       </c>
       <c r="I212" s="9" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD PARENT REPORT | PQL06 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Child</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 CHILD PARENT REPORT|PQL06|PedsQL Neuromuscular Module Version 3.0 Parent Report for Child</t>
         </is>
       </c>
       <c r="I213" s="11" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD | PQL07 | PedsQL Neuromuscular Module Version 3.0 Young Child Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD|PQL07|PedsQL Neuromuscular Module Version 3.0 Young Child Report</t>
         </is>
       </c>
       <c r="I214" s="9" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD PARENT REPORT | PQL08 | PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Child</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 YOUNG CHILD PARENT REPORT|PQL08|PedsQL Neuromuscular Module Version 3.0 Parent Report for Young Child</t>
         </is>
       </c>
       <c r="I215" s="11" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE V3 TODDLER PARENT REPORT | PQL09 | PedsQL Neuromuscular Module Version 3.0 Parent of Toddler</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE V3 TODDLER PARENT REPORT|PQL09|PedsQL Neuromuscular Module Version 3.0 Parent of Toddler</t>
         </is>
       </c>
       <c r="I216" s="9" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="H217" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT | PQL10 | PedsQL Neuromuscular Module Acute Version 3.0 Young Adult Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT|PQL10|PedsQL Neuromuscular Module Acute Version 3.0 Young Adult Report</t>
         </is>
       </c>
       <c r="I217" s="11" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT PARENT REPORT | PQL11 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Adults</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG ADULT PARENT REPORT|PQL11|PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Adults</t>
         </is>
       </c>
       <c r="I218" s="9" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN | PQL12 | PedsQL Neuromuscular Module Acute Version 3.0 Teen Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN|PQL12|PedsQL Neuromuscular Module Acute Version 3.0 Teen Report</t>
         </is>
       </c>
       <c r="I219" s="11" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="H220" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN PARENT REPORT | PQL13 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Teen</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TEEN PARENT REPORT|PQL13|PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Teen</t>
         </is>
       </c>
       <c r="I220" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD | PQL14 | PedsQL Neuromuscular Module Acute Version 3.0 Child Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD|PQL14|PedsQL Neuromuscular Module Acute Version 3.0 Child Report</t>
         </is>
       </c>
       <c r="I221" s="11" t="inlineStr">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="H222" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD PARENT REPORT | PQL15 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Child</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 CHILD PARENT REPORT|PQL15|PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Child</t>
         </is>
       </c>
       <c r="I222" s="9" t="inlineStr">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="H223" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD | PQL16 | PedsQL Neuromuscular Module Acute Version 3.0 Young Child Report</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD|PQL16|PedsQL Neuromuscular Module Acute Version 3.0 Young Child Report</t>
         </is>
       </c>
       <c r="I223" s="11" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD PARENT REPORT | PQL17 | PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Child</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 YOUNG CHILD PARENT REPORT|PQL17|PedsQL Neuromuscular Module Acute Version 3.0 Parent Report for Young Child</t>
         </is>
       </c>
       <c r="I224" s="9" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TODDLER PARENT REPORT | PQL18 | PedsQL Neuromuscular Module Acute Version 3.0 Parent of Toddler</t>
+          <t>PEDSQL NEUROMUSCULAR MODULE ACUTE V3 TODDLER PARENT REPORT|PQL18|PedsQL Neuromuscular Module Acute Version 3.0 Parent of Toddler</t>
         </is>
       </c>
       <c r="I225" s="11" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>PR | PR | PR01</t>
+          <t>PR|PR|PR01</t>
         </is>
       </c>
       <c r="I226" s="9" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>PROS01 | PROSQOLI | PROSQOLI</t>
+          <t>PROS01|PROSQOLI|PROSQOLI</t>
         </is>
       </c>
       <c r="I227" s="11" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>PSECD1 | PSECDI | PSECDI | Penn State Nicotine Dependence Index</t>
+          <t>PSECD1|PSECDI|PSECDI|Penn State Nicotine Dependence Index</t>
         </is>
       </c>
       <c r="I228" s="9" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>PRO-CTCAE V1.0 | PRO-CTCAE V1.0 Version | PT01</t>
+          <t>PRO-CTCAE V1.0|PRO-CTCAE V1.0 Version|PT01</t>
         </is>
       </c>
       <c r="I229" s="11" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>QIDS-SR | QIDS-SR | QIDSR1</t>
+          <t>QIDS-SR|QIDS-SR|QIDSR1</t>
         </is>
       </c>
       <c r="I230" s="9" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Q-LES-Q | Q-LES-Q | QLES1</t>
+          <t>Q-LES-Q|Q-LES-Q|QLES1</t>
         </is>
       </c>
       <c r="I231" s="11" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>Q-LES-Q-SF | Q-LES-Q-SF | QLES2</t>
+          <t>Q-LES-Q-SF|Q-LES-Q-SF|QLES2</t>
         </is>
       </c>
       <c r="I232" s="9" t="inlineStr">
@@ -19640,7 +19640,7 @@
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>QSU-BRIEF | QSU-Brief | QSUB01</t>
+          <t>QSU-BRIEF|QSU-Brief|QSUB01</t>
         </is>
       </c>
       <c r="I233" s="11" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
-          <t>R3601 | RAND-36 V1 | RAND-36 V1.0</t>
+          <t>R3601|RAND-36 V1|RAND-36 V1.0</t>
         </is>
       </c>
       <c r="I234" s="9" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="H235" s="11" t="inlineStr">
         <is>
-          <t>RDQ | RDQ01</t>
+          <t>RDQ|RDQ01</t>
         </is>
       </c>
       <c r="I235" s="11" t="inlineStr">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="H236" s="9" t="inlineStr">
         <is>
-          <t>RPQ | RPQ | RPQ01</t>
+          <t>RPQ|RPQ|RPQ01</t>
         </is>
       </c>
       <c r="I236" s="9" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="H237" s="11" t="inlineStr">
         <is>
-          <t>RAND SOCIAL SUPPORT SURVEY INSTRUMENT | RAND Social Support Survey | RSSS01</t>
+          <t>RAND SOCIAL SUPPORT SURVEY INSTRUMENT|RAND Social Support Survey|RSSS01</t>
         </is>
       </c>
       <c r="I237" s="11" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>SDS | SDS | SDS01</t>
+          <t>SDS|SDS|SDS01</t>
         </is>
       </c>
       <c r="I238" s="9" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="H239" s="11" t="inlineStr">
         <is>
-          <t>SF10 V1.0 CHILDREN STANDARD | SF10 v1.0 Children Standard | SF101</t>
+          <t>SF10 V1.0 CHILDREN STANDARD|SF10 v1.0 Children Standard|SF101</t>
         </is>
       </c>
       <c r="I239" s="11" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>SF10 V1.0 CHILDREN ACUTE | SF10 v1.0 Children Acute | SF102</t>
+          <t>SF10 V1.0 CHILDREN ACUTE|SF10 v1.0 Children Acute|SF102</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="H241" s="11" t="inlineStr">
         <is>
-          <t>SF12 V1.0 STANDARD | SF12 v1.0 Standard | SF121</t>
+          <t>SF12 V1.0 STANDARD|SF12 v1.0 Standard|SF121</t>
         </is>
       </c>
       <c r="I241" s="11" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
-          <t>SF12 V1.0 ACUTE | SF12 v1.0 Acute | SF122</t>
+          <t>SF12 V1.0 ACUTE|SF12 v1.0 Acute|SF122</t>
         </is>
       </c>
       <c r="I242" s="9" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="H243" s="11" t="inlineStr">
         <is>
-          <t>SF12 V2.0 STANDARD | SF12 v2.0 Standard | SF123</t>
+          <t>SF12 V2.0 STANDARD|SF12 v2.0 Standard|SF123</t>
         </is>
       </c>
       <c r="I243" s="11" t="inlineStr">
@@ -20520,7 +20520,7 @@
       </c>
       <c r="H244" s="9" t="inlineStr">
         <is>
-          <t>SF12 V2.0 ACUTE | SF12 v2.0 Acute | SF124</t>
+          <t>SF12 V2.0 ACUTE|SF12 v2.0 Acute|SF124</t>
         </is>
       </c>
       <c r="I244" s="9" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t>SF36 V1.0 STANDARD | SF36 v1.0 Standard | SF361</t>
+          <t>SF36 V1.0 STANDARD|SF36 v1.0 Standard|SF361</t>
         </is>
       </c>
       <c r="I245" s="11" t="inlineStr">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
-          <t>SF36 V1.0 ACUTE | SF36 v1.0 Acute | SF362</t>
+          <t>SF36 V1.0 ACUTE|SF36 v1.0 Acute|SF362</t>
         </is>
       </c>
       <c r="I246" s="9" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="H247" s="11" t="inlineStr">
         <is>
-          <t>Medical Outcomes Survey 36-Item Short-Form Health Survey | SF36 V2.0 STANDARD | SF36 v2.0 Standard | SF363 | Short Form 36 Health Survey</t>
+          <t>Medical Outcomes Survey 36-Item Short-Form Health Survey|SF36 V2.0 STANDARD|SF36 v2.0 Standard|SF363|Short Form 36 Health Survey</t>
         </is>
       </c>
       <c r="I247" s="11" t="inlineStr">
@@ -20840,7 +20840,7 @@
       </c>
       <c r="H248" s="9" t="inlineStr">
         <is>
-          <t>SF36 V2.0 ACUTE | SF36 v2.0 Acute | SF364</t>
+          <t>SF36 V2.0 ACUTE|SF36 v2.0 Acute|SF364</t>
         </is>
       </c>
       <c r="I248" s="9" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="H249" s="11" t="inlineStr">
         <is>
-          <t>SF6D V2.0 STANDARD | SF6D Version 2.0 Standard | SF6D1</t>
+          <t>SF6D V2.0 STANDARD|SF6D Version 2.0 Standard|SF6D1</t>
         </is>
       </c>
       <c r="I249" s="11" t="inlineStr">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="H250" s="9" t="inlineStr">
         <is>
-          <t>SF6D V2.0 ACUTE | SF6D Version 2.0 Acute | SF6D2</t>
+          <t>SF6D V2.0 ACUTE|SF6D Version 2.0 Acute|SF6D2</t>
         </is>
       </c>
       <c r="I250" s="9" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="H251" s="11" t="inlineStr">
         <is>
-          <t>SF8 V1.0 STANDARD | SF8 v1.0 Standard | SF81</t>
+          <t>SF8 V1.0 STANDARD|SF8 v1.0 Standard|SF81</t>
         </is>
       </c>
       <c r="I251" s="11" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="H252" s="9" t="inlineStr">
         <is>
-          <t>SF8 V1.0 ACUTE | SF8 v1.0 Acute | SF82</t>
+          <t>SF8 V1.0 ACUTE|SF8 v1.0 Acute|SF82</t>
         </is>
       </c>
       <c r="I252" s="9" t="inlineStr">
@@ -21240,7 +21240,7 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>SFMP2 | SHORT-FORM MPQ-2</t>
+          <t>SFMP2|SHORT-FORM MPQ-2</t>
         </is>
       </c>
       <c r="I253" s="11" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H254" s="9" t="inlineStr">
         <is>
-          <t>SGRQ PAST 3 MONTHS VERSION | SGRQ Past 3 Months Version | SGRQ01</t>
+          <t>SGRQ PAST 3 MONTHS VERSION|SGRQ Past 3 Months Version|SGRQ01</t>
         </is>
       </c>
       <c r="I254" s="9" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="H255" s="11" t="inlineStr">
         <is>
-          <t>SGRQ PAST 4 WEEKS VERSION | SGRQ Past 4 Weeks Version | SGRQ02</t>
+          <t>SGRQ PAST 4 WEEKS VERSION|SGRQ Past 4 Weeks Version|SGRQ02</t>
         </is>
       </c>
       <c r="I255" s="11" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
-          <t>SGRQ-C | SGRQ-C | SGRQC1</t>
+          <t>SGRQ-C|SGRQ-C|SGRQC1</t>
         </is>
       </c>
       <c r="I256" s="9" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="H257" s="11" t="inlineStr">
         <is>
-          <t>SIQ | SIQ | SIQ01</t>
+          <t>SIQ|SIQ|SIQ01</t>
         </is>
       </c>
       <c r="I257" s="11" t="inlineStr">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>SIQ-JR | SIQ-JR | SIQ02</t>
+          <t>SIQ-JR|SIQ-JR|SIQ02</t>
         </is>
       </c>
       <c r="I258" s="9" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H259" s="11" t="inlineStr">
         <is>
-          <t>SIQR | SIQR | SIQR01</t>
+          <t>SIQR|SIQR|SIQR01</t>
         </is>
       </c>
       <c r="I259" s="11" t="inlineStr">
@@ -21800,7 +21800,7 @@
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>SMDDS V1.0 | SMDDS Version 1.0 | SMDDS1</t>
+          <t>SMDDS V1.0|SMDDS Version 1.0|SMDDS1</t>
         </is>
       </c>
       <c r="I260" s="9" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="H261" s="11" t="inlineStr">
         <is>
-          <t>SOAPP-R | SOAPR1</t>
+          <t>SOAPP-R|SOAPR1</t>
         </is>
       </c>
       <c r="I261" s="11" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
-          <t>SOWS SUBJECTIVE | SOWS Subjective | SOWSA1</t>
+          <t>SOWS SUBJECTIVE|SOWS Subjective|SOWSA1</t>
         </is>
       </c>
       <c r="I262" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="H263" s="11" t="inlineStr">
         <is>
-          <t>SSS | SSS | SSS01</t>
+          <t>SSS|SSS|SSS01</t>
         </is>
       </c>
       <c r="I263" s="11" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>SWLS | SWLS | SWLS01</t>
+          <t>SWLS|SWLS|SWLS01</t>
         </is>
       </c>
       <c r="I264" s="9" t="inlineStr">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="H265" s="11" t="inlineStr">
         <is>
-          <t>TSCC | TSCC | TSCC01</t>
+          <t>TSCC|TSCC|TSCC01</t>
         </is>
       </c>
       <c r="I265" s="11" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>TSCYC | TSCYC | TSCYC1</t>
+          <t>TSCYC|TSCYC|TSCYC1</t>
         </is>
       </c>
       <c r="I266" s="9" t="inlineStr">
@@ -22360,7 +22360,7 @@
       </c>
       <c r="H267" s="11" t="inlineStr">
         <is>
-          <t>TSQM V1.4 | TSQM Version 1.4 | TSQM01</t>
+          <t>TSQM V1.4|TSQM Version 1.4|TSQM01</t>
         </is>
       </c>
       <c r="I267" s="11" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>MDS-UPDRS | UPD2</t>
+          <t>MDS-UPDRS|UPD2</t>
         </is>
       </c>
       <c r="I268" s="9" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="H269" s="11" t="inlineStr">
         <is>
-          <t>UPS | UPS01 | USP</t>
+          <t>UPS|UPS01|USP</t>
         </is>
       </c>
       <c r="I269" s="11" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>VFQ-25 INTERVIEWER ADMINISTERED | VFQ1 | VFQ25-Interviewer Administered Format</t>
+          <t>VFQ-25 INTERVIEWER ADMINISTERED|VFQ1|VFQ25-Interviewer Administered Format</t>
         </is>
       </c>
       <c r="I270" s="9" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="H271" s="11" t="inlineStr">
         <is>
-          <t>VFQ-25 SELF ADMINISTERED | VFQ2 | VFQ25-Self Administered Format</t>
+          <t>VFQ-25 SELF ADMINISTERED|VFQ2|VFQ25-Self Administered Format</t>
         </is>
       </c>
       <c r="I271" s="11" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="H272" s="9" t="inlineStr">
         <is>
-          <t>VHI | VHI | VHI01</t>
+          <t>VHI|VHI|VHI01</t>
         </is>
       </c>
       <c r="I272" s="9" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="H273" s="11" t="inlineStr">
         <is>
-          <t>WD1 | WHODAS 2.0 - 12-ITEM INTERVIEWER | WHODAS 2.0 12-item Version Interviewer-administered</t>
+          <t>WD1|WHODAS 2.0 - 12-ITEM INTERVIEWER|WHODAS 2.0 12-item Version Interviewer-administered</t>
         </is>
       </c>
       <c r="I273" s="11" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="H274" s="9" t="inlineStr">
         <is>
-          <t>WD2 | WHODAS 2.0 - 12-ITEM PROXY | WHODAS 2.0 12-item Version Proxy-administered</t>
+          <t>WD2|WHODAS 2.0 - 12-ITEM PROXY|WHODAS 2.0 12-item Version Proxy-administered</t>
         </is>
       </c>
       <c r="I274" s="9" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="H275" s="11" t="inlineStr">
         <is>
-          <t>WD3 | WHODAS 2.0 - 12-ITEM SELF | WHODAS 2.0 12-item Version Self-administered</t>
+          <t>WD3|WHODAS 2.0 - 12-ITEM SELF|WHODAS 2.0 12-item Version Self-administered</t>
         </is>
       </c>
       <c r="I275" s="11" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="H276" s="9" t="inlineStr">
         <is>
-          <t>WD4 | WHODAS 2.0 - 12 + 24-ITEM INTERVIEWER | WHODAS 2.0 12+24-item Version Interviewer-administered</t>
+          <t>WD4|WHODAS 2.0 - 12 + 24-ITEM INTERVIEWER|WHODAS 2.0 12+24-item Version Interviewer-administered</t>
         </is>
       </c>
       <c r="I276" s="9" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="H277" s="11" t="inlineStr">
         <is>
-          <t>WD5 | WHODAS 2.0 - 36-ITEM INTERVIEWER | WHODAS 2.0 36-item Version Interviewer-administered</t>
+          <t>WD5|WHODAS 2.0 - 36-ITEM INTERVIEWER|WHODAS 2.0 36-item Version Interviewer-administered</t>
         </is>
       </c>
       <c r="I277" s="11" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="H278" s="9" t="inlineStr">
         <is>
-          <t>WD6 | WHODAS 2.0 - 36-ITEM PROXY | WHODAS 2.0 36-item Version Proxy-administered</t>
+          <t>WD6|WHODAS 2.0 - 36-ITEM PROXY|WHODAS 2.0 36-item Version Proxy-administered</t>
         </is>
       </c>
       <c r="I278" s="9" t="inlineStr">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="H279" s="11" t="inlineStr">
         <is>
-          <t>WD7 | WHODAS 2.0 - 36-ITEM SELF | WHODAS 2.0 36-item Version Self-administered</t>
+          <t>WD7|WHODAS 2.0 - 36-ITEM SELF|WHODAS 2.0 36-item Version Self-administered</t>
         </is>
       </c>
       <c r="I279" s="11" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="H280" s="9" t="inlineStr">
         <is>
-          <t>WPAI-SHP V2.0 | WPAI01</t>
+          <t>WPAI-SHP V2.0|WPAI01</t>
         </is>
       </c>
       <c r="I280" s="9" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="H281" s="11" t="inlineStr">
         <is>
-          <t>WPAI-GH V2.0 | WPAI-GH Version 2 | WPAI02 | WPAI:GH | Work Productivity and Activity Impairment General Health V2.0 Questionnaire (WPAI:GH) | Work Productivity and Activity Impairment General Health Version 2.0 Questionnaire</t>
+          <t>WPAI-GH V2.0|WPAI-GH Version 2|WPAI02|WPAI:GH|Work Productivity and Activity Impairment General Health V2.0 Questionnaire (WPAI:GH)|Work Productivity and Activity Impairment General Health Version 2.0 Questionnaire</t>
         </is>
       </c>
       <c r="I281" s="11" t="inlineStr">
@@ -23560,7 +23560,7 @@
       </c>
       <c r="H282" s="9" t="inlineStr">
         <is>
-          <t>ACGC01 | ADCS-CGIC | ADCS-CGIC</t>
+          <t>ACGC01|ADCS-CGIC|ADCS-CGIC</t>
         </is>
       </c>
       <c r="I282" s="9" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="H283" s="11" t="inlineStr">
         <is>
-          <t>AIMS | AIMS | AIMS01</t>
+          <t>AIMS|AIMS|AIMS01</t>
         </is>
       </c>
       <c r="I283" s="11" t="inlineStr">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="H284" s="9" t="inlineStr">
         <is>
-          <t>7th | AJCC V7 | AJCC v7 | AJCC1 | AJCC7 | Seventh Edition (2010)</t>
+          <t>7th|AJCC V7|AJCC v7|AJCC1|AJCC7|Seventh Edition (2010)</t>
         </is>
       </c>
       <c r="I284" s="9" t="inlineStr">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="H285" s="11" t="inlineStr">
         <is>
-          <t>APACHE II | APACHE II | APCH1</t>
+          <t>APACHE II|APACHE II|APCH1</t>
         </is>
       </c>
       <c r="I285" s="11" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="H286" s="9" t="inlineStr">
         <is>
-          <t>APGAR SCORE V1 | APGAR Score Version 1 | APGR01</t>
+          <t>APGAR SCORE V1|APGAR Score Version 1|APGR01</t>
         </is>
       </c>
       <c r="I286" s="9" t="inlineStr">
@@ -23960,7 +23960,7 @@
       </c>
       <c r="H287" s="11" t="inlineStr">
         <is>
-          <t>ASCVD 10-YEAR RISK | ASCVD 10-Year Risk Estimator | ASCVD1</t>
+          <t>ASCVD 10-YEAR RISK|ASCVD 10-Year Risk Estimator|ASCVD1</t>
         </is>
       </c>
       <c r="I287" s="11" t="inlineStr">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="H288" s="9" t="inlineStr">
         <is>
-          <t>ASSG01 | ASSIGN CVD 10-YEAR RISK | ASSIGN Score</t>
+          <t>ASSG01|ASSIGN CVD 10-YEAR RISK|ASSIGN Score</t>
         </is>
       </c>
       <c r="I288" s="9" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="H289" s="11" t="inlineStr">
         <is>
-          <t>ATLAS | ATLAS | ATLAS1</t>
+          <t>ATLAS|ATLAS|ATLAS1</t>
         </is>
       </c>
       <c r="I289" s="11" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="H290" s="9" t="inlineStr">
         <is>
-          <t>AVPU | AVPU | AVPU01</t>
+          <t>AVPU|AVPU|AVPU01</t>
         </is>
       </c>
       <c r="I290" s="9" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>BARS | BARS | BARS01</t>
+          <t>BARS|BARS|BARS01</t>
         </is>
       </c>
       <c r="I291" s="11" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="H292" s="9" t="inlineStr">
         <is>
-          <t>BDI | BDI | BDI01</t>
+          <t>BDI|BDI|BDI01</t>
         </is>
       </c>
       <c r="I292" s="9" t="inlineStr">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="H293" s="11" t="inlineStr">
         <is>
-          <t>BODE INDEX | BODE Index | BODE01</t>
+          <t>BODE INDEX|BODE Index|BODE01</t>
         </is>
       </c>
       <c r="I293" s="11" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="H294" s="9" t="inlineStr">
         <is>
-          <t>BPRS 1988 VERSION | BPRS 1988 Version | BPRS01</t>
+          <t>BPRS 1988 VERSION|BPRS 1988 Version|BPRS01</t>
         </is>
       </c>
       <c r="I294" s="9" t="inlineStr">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="H295" s="11" t="inlineStr">
         <is>
-          <t>BPRS-A | BPRSA1 | Brief Psychiatric Rating Scale - Anchored</t>
+          <t>BPRS-A|BPRSA1|Brief Psychiatric Rating Scale - Anchored</t>
         </is>
       </c>
       <c r="I295" s="11" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="H296" s="9" t="inlineStr">
         <is>
-          <t>BUERS | BUERS | BUERS1</t>
+          <t>BUERS|BUERS|BUERS1</t>
         </is>
       </c>
       <c r="I296" s="9" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="H297" s="11" t="inlineStr">
         <is>
-          <t>CADG01 | NHLBI CAD GRADE | NHLBI CAD Grade</t>
+          <t>CADG01|NHLBI CAD GRADE|NHLBI CAD Grade</t>
         </is>
       </c>
       <c r="I297" s="11" t="inlineStr">
@@ -24840,7 +24840,7 @@
       </c>
       <c r="H298" s="9" t="inlineStr">
         <is>
-          <t>CAP01 | CAPS DSM-5 WITH DSM IV SCORING 2016 VERSION | CAPS DSM-5 With DSM IV Scoring 2016 Version | CAPS-5</t>
+          <t>CAP01|CAPS DSM-5 WITH DSM IV SCORING 2016 VERSION|CAPS DSM-5 With DSM IV Scoring 2016 Version|CAPS-5</t>
         </is>
       </c>
       <c r="I298" s="9" t="inlineStr">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="H299" s="11" t="inlineStr">
         <is>
-          <t>CBS01 | COMFORT-B SCALE | Comfort-B</t>
+          <t>CBS01|COMFORT-B SCALE|Comfort-B</t>
         </is>
       </c>
       <c r="I299" s="11" t="inlineStr">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="H300" s="9" t="inlineStr">
         <is>
-          <t>CANADIAN CV SOCIETY GRADING ANGINA | CCS Angina Classification | CCS Grading of Angina Pectoris | CCSGA1</t>
+          <t>CANADIAN CV SOCIETY GRADING ANGINA|CCS Angina Classification|CCS Grading of Angina Pectoris|CCSGA1</t>
         </is>
       </c>
       <c r="I300" s="9" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="H301" s="11" t="inlineStr">
         <is>
-          <t>CDR | CDR | CDR01</t>
+          <t>CDR|CDR|CDR01</t>
         </is>
       </c>
       <c r="I301" s="11" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="H302" s="9" t="inlineStr">
         <is>
-          <t>CDRS-R | CDRS-R | CDRS1</t>
+          <t>CDRS-R|CDRS-R|CDRS1</t>
         </is>
       </c>
       <c r="I302" s="9" t="inlineStr">
@@ -25240,7 +25240,7 @@
       </c>
       <c r="H303" s="11" t="inlineStr">
         <is>
-          <t>CGBP1 | CGI-BP 1997 | CGI-BP 1997</t>
+          <t>CGBP1|CGI-BP 1997|CGI-BP 1997</t>
         </is>
       </c>
       <c r="I303" s="11" t="inlineStr">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="H304" s="9" t="inlineStr">
         <is>
-          <t>CGI | CGI Generic Modification Version | CGI02</t>
+          <t>CGI|CGI Generic Modification Version|CGI02</t>
         </is>
       </c>
       <c r="I304" s="9" t="inlineStr">
@@ -25392,7 +25392,7 @@
       </c>
       <c r="H305" s="11" t="inlineStr">
         <is>
-          <t>CDC Classification System for HIV-Infected Adults and Adolescents | CDC HIV CLASSIFICATION FOR ADULTS AND ADOLESCENTS | CHIVC1</t>
+          <t>CDC Classification System for HIV-Infected Adults and Adolescents|CDC HIV CLASSIFICATION FOR ADULTS AND ADOLESCENTS|CHIVC1</t>
         </is>
       </c>
       <c r="I305" s="11" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="H306" s="9" t="inlineStr">
         <is>
-          <t>COVI | COVI | COVI01</t>
+          <t>COVI|COVI|COVI01</t>
         </is>
       </c>
       <c r="I306" s="9" t="inlineStr">
@@ -25552,7 +25552,7 @@
       </c>
       <c r="H307" s="11" t="inlineStr">
         <is>
-          <t>CHILD-PUGH CLASSIFICATION | CPS01 | Child-Pugh | Child-Pugh Classification | Child-Pugh Classification | Child-Pugh Score | child pugh classification | child_pugh_classification</t>
+          <t>CHILD-PUGH CLASSIFICATION|CPS01|Child-Pugh|Child-Pugh Classification|Child-Pugh Classification|Child-Pugh Score|child pugh classification|child_pugh_classification</t>
         </is>
       </c>
       <c r="I307" s="11" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="H308" s="9" t="inlineStr">
         <is>
-          <t>CRS-R | CRS-R | CRSR01</t>
+          <t>CRS-R|CRS-R|CRSR01</t>
         </is>
       </c>
       <c r="I308" s="9" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="H309" s="11" t="inlineStr">
         <is>
-          <t>DRS | DRS | DRS01</t>
+          <t>DRS|DRS|DRS01</t>
         </is>
       </c>
       <c r="I309" s="11" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="H310" s="9" t="inlineStr">
         <is>
-          <t>DISEASE STEPS | DS | DS01</t>
+          <t>DISEASE STEPS|DS|DS01</t>
         </is>
       </c>
       <c r="I310" s="9" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H311" s="11" t="inlineStr">
         <is>
-          <t>ECOG | ECOG | ECOG1</t>
+          <t>ECOG|ECOG|ECOG1</t>
         </is>
       </c>
       <c r="I311" s="11" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="H312" s="9" t="inlineStr">
         <is>
-          <t>EDSS | EDSS | EDSS01</t>
+          <t>EDSS|EDSS|EDSS01</t>
         </is>
       </c>
       <c r="I312" s="9" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="H313" s="11" t="inlineStr">
         <is>
-          <t>ESRS-A | ESRSA | ESRSA1</t>
+          <t>ESRS-A|ESRSA|ESRSA1</t>
         </is>
       </c>
       <c r="I313" s="11" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="H314" s="9" t="inlineStr">
         <is>
-          <t>E-TRIP | E-TRIP | ETRP01</t>
+          <t>E-TRIP|E-TRIP|ETRP01</t>
         </is>
       </c>
       <c r="I314" s="9" t="inlineStr">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="H315" s="11" t="inlineStr">
         <is>
-          <t>FAQ | FAQ | FAQ01</t>
+          <t>FAQ|FAQ|FAQ01</t>
         </is>
       </c>
       <c r="I315" s="11" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="H316" s="9" t="inlineStr">
         <is>
-          <t>FAQ-NACC UDS V2.0 | FAQ-NACC UDS Version 2.0 | FAQNA1</t>
+          <t>FAQ-NACC UDS V2.0|FAQ-NACC UDS Version 2.0|FAQNA1</t>
         </is>
       </c>
       <c r="I316" s="9" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H317" s="11" t="inlineStr">
         <is>
-          <t>FAS-NACC UDS V3.0 | FAS-NACC UDS Version 3.0 | FASNA1</t>
+          <t>FAS-NACC UDS V3.0|FAS-NACC UDS Version 3.0|FASNA1</t>
         </is>
       </c>
       <c r="I317" s="11" t="inlineStr">
@@ -26432,7 +26432,7 @@
       </c>
       <c r="H318" s="9" t="inlineStr">
         <is>
-          <t>FCVD1 | FHS CVD 10-YEAR RISK | FHS CVD 10-Year Risk Score</t>
+          <t>FCVD1|FHS CVD 10-YEAR RISK|FHS CVD 10-Year Risk Score</t>
         </is>
       </c>
       <c r="I318" s="9" t="inlineStr">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="H319" s="11" t="inlineStr">
         <is>
-          <t>GCGI | GCGI | GCGI01</t>
+          <t>GCGI|GCGI|GCGI01</t>
         </is>
       </c>
       <c r="I319" s="11" t="inlineStr">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="H320" s="9" t="inlineStr">
         <is>
-          <t>GCS NINDS V1.0 | GCS NINDS Version 1.0 | GCS01</t>
+          <t>GCS NINDS V1.0|GCS NINDS Version 1.0|GCS01</t>
         </is>
       </c>
       <c r="I320" s="9" t="inlineStr">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="H321" s="11" t="inlineStr">
         <is>
-          <t>HAM-A | HAMA | HAMA1</t>
+          <t>HAM-A|HAMA|HAMA1</t>
         </is>
       </c>
       <c r="I321" s="11" t="inlineStr">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="H322" s="9" t="inlineStr">
         <is>
-          <t>HAMD 17 | HAMD1</t>
+          <t>HAMD 17|HAMD1</t>
         </is>
       </c>
       <c r="I322" s="9" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="H323" s="11" t="inlineStr">
         <is>
-          <t>HAMD 21 | HAMD-21 | HAMD2</t>
+          <t>HAMD 21|HAMD-21|HAMD2</t>
         </is>
       </c>
       <c r="I323" s="11" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H324" s="9" t="inlineStr">
         <is>
-          <t>HAMD 24 | HAMD 24 | HAMD3</t>
+          <t>HAMD 24|HAMD 24|HAMD3</t>
         </is>
       </c>
       <c r="I324" s="9" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="H325" s="11" t="inlineStr">
         <is>
-          <t>HAM-D6 Clinician Version | HAMD 6 CLINICIAN VERSION | HAMD4</t>
+          <t>HAM-D6 Clinician Version|HAMD 6 CLINICIAN VERSION|HAMD4</t>
         </is>
       </c>
       <c r="I325" s="11" t="inlineStr">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="H326" s="9" t="inlineStr">
         <is>
-          <t>HBI | HBI | HBI01</t>
+          <t>HBI|HBI|HBI01</t>
         </is>
       </c>
       <c r="I326" s="9" t="inlineStr">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="H327" s="11" t="inlineStr">
         <is>
-          <t>HAS-BLED | HAS-BLED | HSB01</t>
+          <t>HAS-BLED|HAS-BLED|HSB01</t>
         </is>
       </c>
       <c r="I327" s="11" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="H328" s="9" t="inlineStr">
         <is>
-          <t>IDS-C | IDS-C | IDSC1</t>
+          <t>IDS-C|IDS-C|IDSC1</t>
         </is>
       </c>
       <c r="I328" s="9" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="H329" s="11" t="inlineStr">
         <is>
-          <t>KDIGO AKI | KDIGO-AKI | KDIGO1</t>
+          <t>KDIGO AKI|KDIGO-AKI|KDIGO1</t>
         </is>
       </c>
       <c r="I329" s="11" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="H330" s="9" t="inlineStr">
         <is>
-          <t>KDPI | KDPI | KDPI01</t>
+          <t>KDPI|KDPI|KDPI01</t>
         </is>
       </c>
       <c r="I330" s="9" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="H331" s="11" t="inlineStr">
         <is>
-          <t>KFSS | KFSS | KFSS1</t>
+          <t>KFSS|KFSS|KFSS1</t>
         </is>
       </c>
       <c r="I331" s="11" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="H332" s="9" t="inlineStr">
         <is>
-          <t>KPS SCALE | KPSS01</t>
+          <t>KPS SCALE|KPSS01</t>
         </is>
       </c>
       <c r="I332" s="9" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="H333" s="11" t="inlineStr">
         <is>
-          <t>MCHR01 | MONTREAL CLASSIFICATION CROHN'S | Montreal Classification</t>
+          <t>MCHR01|MONTREAL CLASSIFICATION CROHN'S|Montreal Classification</t>
         </is>
       </c>
       <c r="I333" s="11" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="H334" s="9" t="inlineStr">
         <is>
-          <t>MELD | MELD | MELD01</t>
+          <t>MELD|MELD|MELD01</t>
         </is>
       </c>
       <c r="I334" s="9" t="inlineStr">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="H335" s="11" t="inlineStr">
         <is>
-          <t>MELD02 | MELDNA 2008 | MELDNA 2008</t>
+          <t>MELD02|MELDNA 2008|MELDNA 2008</t>
         </is>
       </c>
       <c r="I335" s="11" t="inlineStr">
@@ -27856,7 +27856,7 @@
       </c>
       <c r="H336" s="9" t="inlineStr">
         <is>
-          <t>MRS | MRS | MRS01 | Modified Rankin Scale</t>
+          <t>MRS|MRS|MRS01|Modified Rankin Scale</t>
         </is>
       </c>
       <c r="I336" s="9" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="H337" s="11" t="inlineStr">
         <is>
-          <t>MVAI | MVAI | MVAI1</t>
+          <t>MVAI|MVAI|MVAI1</t>
         </is>
       </c>
       <c r="I337" s="11" t="inlineStr">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="H338" s="9" t="inlineStr">
         <is>
-          <t>NEWS1 | NEWS2 | NEWS2</t>
+          <t>NEWS1|NEWS2|NEWS2</t>
         </is>
       </c>
       <c r="I338" s="9" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="H339" s="11" t="inlineStr">
         <is>
-          <t>NSA-16 | NSA-16 | NSA01</t>
+          <t>NSA-16|NSA-16|NSA01</t>
         </is>
       </c>
       <c r="I339" s="11" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="H340" s="9" t="inlineStr">
         <is>
-          <t>NSAA | NSAA | NSAA1</t>
+          <t>NSAA|NSAA|NSAA1</t>
         </is>
       </c>
       <c r="I340" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="H341" s="11" t="inlineStr">
         <is>
-          <t>PANSS | PANSS | PANSS1</t>
+          <t>PANSS|PANSS|PANSS1</t>
         </is>
       </c>
       <c r="I341" s="11" t="inlineStr">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="H342" s="9" t="inlineStr">
         <is>
-          <t>PASI FELDMAN | PASI Feldman Version | PASI02</t>
+          <t>PASI FELDMAN|PASI Feldman Version|PASI02</t>
         </is>
       </c>
       <c r="I342" s="9" t="inlineStr">
@@ -28416,7 +28416,7 @@
       </c>
       <c r="H343" s="11" t="inlineStr">
         <is>
-          <t>PASI FREDRIKSSON | PASI Fredriksson Version | PASI03</t>
+          <t>PASI FREDRIKSSON|PASI Fredriksson Version|PASI03</t>
         </is>
       </c>
       <c r="I343" s="11" t="inlineStr">
@@ -28496,7 +28496,7 @@
       </c>
       <c r="H344" s="9" t="inlineStr">
         <is>
-          <t>PASI EMA | PASI EMA Version | PASI04</t>
+          <t>PASI EMA|PASI EMA Version|PASI04</t>
         </is>
       </c>
       <c r="I344" s="9" t="inlineStr">
@@ -28576,7 +28576,7 @@
       </c>
       <c r="H345" s="11" t="inlineStr">
         <is>
-          <t>PASI BOZEK | PASI Bozek Version | PASI05</t>
+          <t>PASI BOZEK|PASI Bozek Version|PASI05</t>
         </is>
       </c>
       <c r="I345" s="11" t="inlineStr">
@@ -28656,7 +28656,7 @@
       </c>
       <c r="H346" s="9" t="inlineStr">
         <is>
-          <t>QIDS-C | QIDS-C | QIDSC1</t>
+          <t>QIDS-C|QIDS-C|QIDSC1</t>
         </is>
       </c>
       <c r="I346" s="9" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="H347" s="11" t="inlineStr">
         <is>
-          <t>RASS | RASS | RASS01</t>
+          <t>RASS|RASS|RASS01</t>
         </is>
       </c>
       <c r="I347" s="11" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H348" s="9" t="inlineStr">
         <is>
-          <t>RCVD01 | REYNOLDS CVD 10-YEAR RISK | Reynolds CVD 10-Year Risk Score</t>
+          <t>RCVD01|REYNOLDS CVD 10-YEAR RISK|Reynolds CVD 10-Year Risk Score</t>
         </is>
       </c>
       <c r="I348" s="9" t="inlineStr">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="H349" s="11" t="inlineStr">
         <is>
-          <t>RUTG01 | RUTGEERTS SCORE | Rutgeerts Score</t>
+          <t>RUTG01|RUTGEERTS SCORE|Rutgeerts Score</t>
         </is>
       </c>
       <c r="I349" s="11" t="inlineStr">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="H350" s="9" t="inlineStr">
         <is>
-          <t>SAS | SAS | SAS01</t>
+          <t>SAS|SAS|SAS01</t>
         </is>
       </c>
       <c r="I350" s="9" t="inlineStr">
@@ -29056,7 +29056,7 @@
       </c>
       <c r="H351" s="11" t="inlineStr">
         <is>
-          <t>SES-CD V1 | SES-CD Version 1 | SES01</t>
+          <t>SES-CD V1|SES-CD Version 1|SES01</t>
         </is>
       </c>
       <c r="I351" s="11" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="H352" s="9" t="inlineStr">
         <is>
-          <t>SOFA 1996 | SOFA 1996 Version | SOFA01 | Sequential Organ Failure Assessment 1996</t>
+          <t>SOFA 1996|SOFA 1996 Version|SOFA01|Sequential Organ Failure Assessment 1996</t>
         </is>
       </c>
       <c r="I352" s="9" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="H353" s="11" t="inlineStr">
         <is>
-          <t>ARC STC GRADE | ARC STC Grade | STCG01</t>
+          <t>ARC STC GRADE|ARC STC Grade|STCG01</t>
         </is>
       </c>
       <c r="I353" s="11" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="H354" s="9" t="inlineStr">
         <is>
-          <t>TANN01 | TANNER SCALE GIRL | Tanner Scale-Girl</t>
+          <t>TANN01|TANNER SCALE GIRL|Tanner Scale-Girl</t>
         </is>
       </c>
       <c r="I354" s="9" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="H355" s="11" t="inlineStr">
         <is>
-          <t>TANN02 | TANNER SCALE BOY | Tanner Scale-Boy</t>
+          <t>TANN02|TANNER SCALE BOY|Tanner Scale-Boy</t>
         </is>
       </c>
       <c r="I355" s="11" t="inlineStr">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="H356" s="9" t="inlineStr">
         <is>
-          <t>TDI | TDI | TDI01</t>
+          <t>TDI|TDI|TDI01</t>
         </is>
       </c>
       <c r="I356" s="9" t="inlineStr">
@@ -29536,7 +29536,7 @@
       </c>
       <c r="H357" s="11" t="inlineStr">
         <is>
-          <t>TIMG01 | TIMI THROMBUS GRADE | TIMI Thrombus Grade</t>
+          <t>TIMG01|TIMI THROMBUS GRADE|TIMI Thrombus Grade</t>
         </is>
       </c>
       <c r="I357" s="11" t="inlineStr">
@@ -29616,7 +29616,7 @@
       </c>
       <c r="H358" s="9" t="inlineStr">
         <is>
-          <t>UHDR1 | UHDRS 1999 | UHDRS 1999 Version</t>
+          <t>UHDR1|UHDRS 1999|UHDRS 1999 Version</t>
         </is>
       </c>
       <c r="I358" s="9" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="H359" s="11" t="inlineStr">
         <is>
-          <t>UPD1 | UPDRS</t>
+          <t>UPD1|UPDRS</t>
         </is>
       </c>
       <c r="I359" s="11" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H360" s="9" t="inlineStr">
         <is>
-          <t>VALG | VALG | VALG01</t>
+          <t>VALG|VALG|VALG01</t>
         </is>
       </c>
       <c r="I360" s="9" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="H361" s="11" t="inlineStr">
         <is>
-          <t>VLERS | VLERS | VLERS1</t>
+          <t>VLERS|VLERS|VLERS1</t>
         </is>
       </c>
       <c r="I361" s="11" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="H362" s="9" t="inlineStr">
         <is>
-          <t>WEST HAVEN HEPATIC ENCEPHALOPATHY GRADE | WHEG01 | West Haven Criteria</t>
+          <t>WEST HAVEN HEPATIC ENCEPHALOPATHY GRADE|WHEG01|West Haven Criteria</t>
         </is>
       </c>
       <c r="I362" s="9" t="inlineStr">
@@ -30000,7 +30000,7 @@
       </c>
       <c r="H363" s="11" t="inlineStr">
         <is>
-          <t>WHIVS1 | WHO Clinical Staging of HIV/AIDS for Adults and Adolescents | WHO HIV STAGING FOR ADULTS AND ADOLESCENTS</t>
+          <t>WHIVS1|WHO Clinical Staging of HIV/AIDS for Adults and Adolescents|WHO HIV STAGING FOR ADULTS AND ADOLESCENTS</t>
         </is>
       </c>
       <c r="I363" s="11" t="inlineStr">
@@ -30080,7 +30080,7 @@
       </c>
       <c r="H364" s="9" t="inlineStr">
         <is>
-          <t>WHIVS2 | WHO Clinical Staging of HIV/AIDS for Children | WHO HIV STAGING FOR CHILDREN</t>
+          <t>WHIVS2|WHO Clinical Staging of HIV/AIDS for Children|WHO HIV STAGING FOR CHILDREN</t>
         </is>
       </c>
       <c r="I364" s="9" t="inlineStr">

--- a/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
+++ b/sdtm-test-codes/machine_actionable/SDTM_Instrument_Identity.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruments" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Instruments'!$A$1:$R$364</definedName>
@@ -56,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +99,11 @@
         <fgColor rgb="00FAEADC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -151,6 +157,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A93"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -603,7 +611,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Generated:      2026-10-30 11:38:33</t>
+          <t>Generated:      2026-10-30 12:05:18</t>
         </is>
       </c>
     </row>
@@ -698,390 +706,397 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Provenance — fixed keys for programs: source versions (SDTM_CT, COSMoS, SDTMIG, SDTM, NCIt), Generated, Notebook; per data sheet Rows, Columns, Content_SHA256 (equal hash = equal data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>COLUMN DESCRIPTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Codelist_TESTCD                 Primary key. Submission value of the Test Code codelist (e.g. ADCTC)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Codelist_NCIt_Code              NCIt concept code for the codelist itself (CDISC Terminology branch)</t>
+          <t>Codelist_TESTCD                 Primary key. Submission value of the Test Code codelist (e.g. ADCTC)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Instrument_Label                Display name minus " Test Code" suffix</t>
+          <t>Codelist_NCIt_Code              NCIt concept code for the codelist itself (CDISC Terminology branch)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Domain                          QS / FT / RS (or ?? for TAUG-origin codelists outside SDTMIG v3.4)</t>
+          <t>Instrument_Label                Display name minus " Test Code" suffix</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>Domain                          QS / FT / RS (or ?? for TAUG-origin codelists outside SDTMIG v3.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>Question_Count                  Number of TESTCDs in the codelist</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="n"/>
-    </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Instrument_NCIt_Code            NCIt code for the instrument-as-tool (C20993 branch)</t>
-        </is>
-      </c>
+      <c r="A39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Preferred_Term  Preferred term from NCIt FLAT</t>
+          <t>Instrument_NCIt_Code            NCIt code for the instrument-as-tool (C20993 branch)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Synonyms        Synonyms (undifferentiated) from NCIt FLAT, separated by | as in the FLAT file</t>
+          <t>Instrument_NCIt_Preferred_Term  Preferred term from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIt_Definition      Plain-language definition from NCIt FLAT</t>
+          <t>Instrument_NCIt_Synonyms        Synonyms (undifferentiated) from NCIt FLAT, separated by | as in the FLAT file</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Instrument_UMLS_CUI             Standard UMLS CUI (C + digits)</t>
+          <t>Instrument_NCIt_Definition      Plain-language definition from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Instrument_NCIm_CUI             NCI Metathesaurus CUI (CL + digits)</t>
+          <t>Instrument_UMLS_CUI             Standard UMLS CUI (C + digits)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>Instrument_NCIm_CUI             NCI Metathesaurus CUI (CL + digits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>Instrument_Match_Method         Resolution path: class-category-term / exact / suffix-strip / normalized / normalized-item-strip / UNMATCHED</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-    </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Container_NCIt_Code             NCIt code for the question container (C211913 branch)</t>
-        </is>
-      </c>
+      <c r="A47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Preferred_Term   Preferred term from NCIt FLAT</t>
+          <t>Container_NCIt_Code             NCIt code for the question container (C211913 branch)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Synonyms         Synonyms from NCIt FLAT, separated by | as in the FLAT file</t>
+          <t>Container_NCIt_Preferred_Term   Preferred term from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Container_NCIt_Definition       Plain-language definition from NCIt FLAT</t>
+          <t>Container_NCIt_Synonyms         Synonyms from NCIt FLAT, separated by | as in the FLAT file</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Container_UMLS_CUI              Standard UMLS CUI</t>
+          <t>Container_NCIt_Definition       Plain-language definition from NCIt FLAT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>Container_UMLS_CUI              Standard UMLS CUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
           <t>Container_NCIm_CUI              NCI Metathesaurus CUI</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>COVERAGE STATISTICS</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Total codelists:                 363</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Instrument NCIt populated:       363 (100.0%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Container  NCIt populated:       359 (98.9%)</t>
+          <t>Instrument NCIt populated:       363 (100.0%)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Both populated:                  359 (98.9%)</t>
+          <t>Container  NCIt populated:       359 (98.9%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Neither populated:               0 (0.0%)</t>
+          <t>Both populated:                  359 (98.9%)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Instrument UMLS CUI populated:   155 (42.7%)</t>
+          <t>Neither populated:               0 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>Instrument UMLS CUI populated:   155 (42.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
           <t>Container  UMLS CUI populated:   140 (38.6%)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="n"/>
-    </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Instrument match method:</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  class-category-term:    362</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  exact:                    1</t>
+          <t xml:space="preserve">  class-category-term:    362</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  suffix-strip:             0</t>
+          <t xml:space="preserve">  exact:                    1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized:               0</t>
+          <t xml:space="preserve">  suffix-strip:             0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  normalized-item-strip:    0</t>
+          <t xml:space="preserve">  normalized:               0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  normalized-item-strip:    0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  UNMATCHED:                0</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>DESIGN DECISIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
+          <t>Two NCIt anchors, explicitly prefixed. C20993 (Research or Clinical Assessment</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
+          <t>Tool) carries instrument identity. C211913 (CDISC QRS Instruments Questions) carries</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>question-container structure. The two branches are not linked in NCIt — explicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>column separation names the gap rather than hiding it.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="n"/>
-    </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Class category term first. SDTM CT QSCAT / FTCAT / CCCAT carry one term per instrument;</t>
-        </is>
-      </c>
+      <c r="A77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>its CDISC synonym + "TC" is the codelist submission value and its code the instrument</t>
+          <t>Class category term first. SDTM CT QSCAT / FTCAT / CCCAT carry one term per instrument;</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
+          <t>its CDISC synonym + "TC" is the codelist submission value and its code the instrument</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
           <t>concept. Name matching is the fallback.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="n"/>
-    </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
-        </is>
-      </c>
+      <c r="A81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
+          <t>Token-overlap fuzzy matching excluded. Exploratory work found wrong-version errors</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>(HAMD-17 → HAMD-21, SF-36 → SF-8). Rows without a clean exact / suffix /</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>normalized match get UNMATCHED with empty Instrument_NCIt_* columns.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="n"/>
-    </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
-        </is>
-      </c>
+      <c r="A85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
+          <t>Codelist grain. One row per codelist. Test-within-codelist grain lives in</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
           <t>SDTM_Instrument_Test_Identity.xlsx, joinable via Codelist_TESTCD.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>COLOR CONVENTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
+          <t>Dark chocolate (#5B3A29)  — Instrument identity columns (C20993, parent level)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
+          <t>Copper (#CC7A3E)          — Container / subscale columns (C211913, middle level)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
+          <t>Grey (#7F7F7F)            — codelist key columns + base identity</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Green (#548235)           — TESTCD identity (sibling Test_Identity files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Yellow (#FFD700)          — COSMoS Dataset Specialization layer (consumer files)</t>
         </is>
@@ -30126,4 +30141,166 @@
   <autoFilter ref="A1:R364"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>SDTM_CT</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>COSMoS</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>SDTMIG</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>NCIt</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>sdtm-test-codes/notebooks/SDTM_Instrument_Identity_Enrich.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Instruments.Rows</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Instruments.Columns</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Codelist_TESTCD|Codelist_NCIt_Code|Instrument_Label|Domain|Question_Count|Instrument_NCIt_Code|Instrument_NCIt_Preferred_Term|Instrument_NCIt_Synonyms|Instrument_NCIt_Definition|Instrument_UMLS_CUI|Instrument_NCIm_CUI|Instrument_Match_Method|Container_NCIt_Code|Container_NCIt_Preferred_Term|Container_NCIt_Synonyms|Container_NCIt_Definition|Container_UMLS_CUI|Container_NCIm_CUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Instruments.Content_SHA256</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>d48ca76b02e8da9062990c35cf16c7c29395ba46a5bfe0b344b9c6a40b4aa778</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Content_SHA256.Method</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>SHA-256 (UTF-8) of the sheet read as text, empty cells as "" (pandas read_excel, dtype=str): header and rows, cells joined by tab, rows by newline. Equal hash = equal data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>